--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59446C44-487D-4E4E-B4FA-4EABCED5635D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20F5ABA-26EB-4DC1-B614-3E028D67EA34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -5351,7 +5351,7 @@
         <v>535</v>
       </c>
       <c r="F3" s="429">
-        <v>46038</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="12.4">
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>116.64</v>
+        <v>116.25</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>171687.31056432001</v>
+        <v>171113.25319875</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.13157609767049624</v>
+        <v>0.132879388946781</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5555,13 +5555,13 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>78.946478897531932</v>
+        <v>73.121635714867196</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>404</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036601</v>
+        <v>0.32950289523458665</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5570,13 +5570,13 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>98.170331899821747</v>
+        <v>92.375891520070169</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>405</v>
       </c>
       <c r="E23" s="443">
-        <v>0.20075184365903001</v>
+        <v>0.22621703288100403</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5585,13 +5585,13 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>120.99944828862141</v>
+        <v>131.12448893172376</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>406</v>
       </c>
       <c r="E24" s="443">
-        <v>0.1174</v>
+        <v>8.6999999999999994E-2</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.6770790546884585E-2</v>
+        <v>7.7028344166783808E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.5432098765432102E-2</v>
+        <v>3.5550967741935488E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -6579,19 +6579,19 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>7.5624105937479049</v>
+        <v>7.2052832811602343</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>71.384068303784034</v>
+        <v>65.916352433706962</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>78.946478897531932</v>
+        <v>73.121635714867196</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.32950289523458665</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6600,19 +6600,19 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>8.6954275132736498</v>
+        <v>8.3604728249046811</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>89.47490438654809</v>
+        <v>84.015418695165494</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>98.170331899821747</v>
+        <v>92.375891520070169</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.22621703288100403</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6647,19 +6647,19 @@
       </c>
       <c r="C144" s="333">
         <f>Scenarios!C66</f>
-        <v>9.9708061988792505</v>
+        <v>10.517521633559475</v>
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>111.02864208974216</v>
+        <v>120.60696729816429</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>120.99944828862141</v>
+        <v>131.12448893172376</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
-        <v>0.1174</v>
+        <v>8.6999999999999994E-2</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5432098765432102E-2</v>
+        <v>3.5550967741935488E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5432098765432102E-2</v>
+        <v>3.5550967741935488E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.166726851851852E-2</v>
+        <v>4.1807055483870967E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.6770790546884585E-2</v>
+        <v>7.7028344166783808E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.481052626062816E-2</v>
+        <v>7.5061503510018654E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.2352349811366262E-2</v>
+        <v>7.2595080275249566E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8618382025579372E-2</v>
+        <v>7.8882134016890995E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7400362202258433E-2</v>
+        <v>7.7660027933517631E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>116.64</v>
+        <v>116.25</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.13157609767049624</v>
+        <v>0.132879388946781</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20032,23 +20032,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>7.5624105937479049</v>
+        <v>7.2052832811602343</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>71.384068303784034</v>
+        <v>65.916352433706962</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>78.946478897531932</v>
+        <v>73.121635714867196</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.32950289523458665</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.49035034404912614</v>
+        <v>0.52795340583818939</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20057,23 +20057,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>8.6954275132736498</v>
+        <v>8.3604728249046811</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>89.47490438654809</v>
+        <v>84.015418695165494</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>98.170331899821747</v>
+        <v>92.375891520070169</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.22621703288100403</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.36624816488311562</v>
+        <v>0.40365495727218781</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20103,23 +20103,23 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>9.9708061988792505</v>
+        <v>10.517521633559475</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>111.02864208974216</v>
+        <v>120.60696729816429</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>120.99944828862141</v>
+        <v>131.12448893172376</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
-        <v>0.1174</v>
+        <v>8.6999999999999994E-2</v>
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.21887172104810204</v>
+        <v>0.15350815382753724</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="F3" s="436">
         <f>Thesis!F3</f>
-        <v>46038</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>116.64</v>
+        <v>116.25</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>171687.31056432001</v>
+        <v>171113.25319875</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.13157609767049624</v>
+        <v>0.132879388946781</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20410,14 +20410,14 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>78.946478897531932</v>
+        <v>73.121635714867196</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>438</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.32950289523458665</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20426,14 +20426,14 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>98.170331899821747</v>
+        <v>92.375891520070169</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>439</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.22621703288100403</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20442,14 +20442,14 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>120.99944828862141</v>
+        <v>131.12448893172376</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>441</v>
       </c>
       <c r="E24" s="368">
         <f>Thesis!E24</f>
-        <v>0.1174</v>
+        <v>8.6999999999999994E-2</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.6770790546884585E-2</v>
+        <v>7.7028344166783808E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.5432098765432102E-2</v>
+        <v>3.5550967741935488E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -21445,19 +21445,19 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>7.5624105937479049</v>
+        <v>7.2052832811602343</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>71.384068303784034</v>
+        <v>65.916352433706962</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>78.946478897531932</v>
+        <v>73.121635714867196</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.32950289523458665</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21466,19 +21466,19 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>8.6954275132736498</v>
+        <v>8.3604728249046811</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>89.47490438654809</v>
+        <v>84.015418695165494</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>98.170331899821747</v>
+        <v>92.375891520070169</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.22621703288100403</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21506,19 +21506,19 @@
       </c>
       <c r="C144" s="409">
         <f>Scenarios!C66</f>
-        <v>9.9708061988792505</v>
+        <v>10.517521633559475</v>
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>111.02864208974216</v>
+        <v>120.60696729816429</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>120.99944828862141</v>
+        <v>131.12448893172376</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
-        <v>0.1174</v>
+        <v>8.6999999999999994E-2</v>
       </c>
     </row>
     <row r="145" spans="1:6">

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20F5ABA-26EB-4DC1-B614-3E028D67EA34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C986D875-59CB-DD40-8B7B-7A7679246570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -39,6 +39,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -3269,27 +3280,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="19">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.00\x"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="170" formatCode="#,##0_ "/>
-    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="176" formatCode="0.000_ "/>
-    <numFmt numFmtId="177" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="178" formatCode="0.0\x"/>
-    <numFmt numFmtId="179" formatCode="0\x"/>
-    <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
-    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.00\x"/>
+    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="171" formatCode="#,##0_ "/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="173" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="174" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="175" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="177" formatCode="0.000_ "/>
+    <numFmt numFmtId="178" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="179" formatCode="0.0\x"/>
+    <numFmt numFmtId="180" formatCode="0\x"/>
+    <numFmt numFmtId="181" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="182" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="72" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4041,7 +4052,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4083,17 +4094,17 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4102,7 +4113,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4176,10 +4187,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4190,7 +4201,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4228,7 +4239,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4238,7 +4249,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4249,19 +4260,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4269,8 +4280,8 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4293,29 +4304,29 @@
     </xf>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4332,15 +4343,15 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4351,11 +4362,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4416,14 +4427,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4436,7 +4447,7 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4473,7 +4484,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4490,7 +4501,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4536,7 +4547,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4551,13 +4562,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4573,53 +4584,53 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="182" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4636,7 +4647,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -4649,21 +4660,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="181" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4673,14 +4684,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4689,8 +4700,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4702,7 +4713,7 @@
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4710,7 +4721,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4749,7 +4760,7 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4763,39 +4774,39 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="173" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="180" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4806,7 +4817,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4817,10 +4828,10 @@
     <xf numFmtId="9" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4829,7 +4840,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4842,7 +4853,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4851,8 +4862,8 @@
     <xf numFmtId="40" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4860,10 +4871,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4872,10 +4883,10 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4892,16 +4903,16 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4922,7 +4933,7 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4940,7 +4951,7 @@
     <xf numFmtId="40" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4950,10 +4961,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4968,7 +4979,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4982,34 +4993,34 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5030,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,21 +5048,12 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5324,7 +5335,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:I167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -5333,7 +5344,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="13.9">
+    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="200" t="s">
         <v>225</v>
       </c>
@@ -5346,7 +5357,7 @@
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="E3" s="428" t="s">
         <v>535</v>
       </c>
@@ -5354,7 +5365,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="12.4">
+    <row r="4" spans="1:9" ht="14" x14ac:dyDescent="0.2">
       <c r="B4" s="421" t="s">
         <v>530</v>
       </c>
@@ -5368,7 +5379,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>347</v>
       </c>
@@ -5382,7 +5393,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
@@ -5392,7 +5403,7 @@
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>349</v>
       </c>
@@ -5402,7 +5413,7 @@
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B8" s="4" t="s">
         <v>348</v>
       </c>
@@ -5411,7 +5422,7 @@
       </c>
       <c r="E8" s="32"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>344</v>
       </c>
@@ -5419,7 +5430,7 @@
         <v>1471941963</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>350</v>
       </c>
@@ -5435,27 +5446,27 @@
         <v>0.132879388946781</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+    <row r="12" spans="1:9" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="460" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
         <v>1-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B15" s="1" t="s">
         <v>318</v>
       </c>
@@ -5470,7 +5481,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>319</v>
       </c>
@@ -5484,7 +5495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>529</v>
       </c>
@@ -5498,7 +5509,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B18" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C7&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -5514,7 +5525,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B19" s="2" t="s">
         <v>275</v>
       </c>
@@ -5530,11 +5541,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B21" s="42" t="s">
         <v>402</v>
       </c>
@@ -5549,7 +5560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B22" s="1" t="s">
         <v>311</v>
       </c>
@@ -5564,7 +5575,7 @@
         <v>0.32950289523458665</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>312</v>
       </c>
@@ -5579,7 +5590,7 @@
         <v>0.22621703288100403</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>314</v>
       </c>
@@ -5594,7 +5605,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B25" s="1" t="s">
         <v>313</v>
       </c>
@@ -5609,11 +5620,11 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:6" ht="13.9">
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A27" s="200" t="s">
         <v>280</v>
       </c>
@@ -5623,25 +5634,25 @@
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
     </row>
-    <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B29" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B32" s="192" t="s">
         <v>195</v>
       </c>
@@ -5650,16 +5661,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+    <row r="33" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
-    </row>
-    <row r="34" spans="2:6">
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="44" t="s">
         <v>197</v>
       </c>
@@ -5672,20 +5683,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B35" s="44"/>
       <c r="C35" s="73"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
-    </row>
-    <row r="37" spans="2:6">
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="44" t="s">
         <v>199</v>
       </c>
@@ -5698,7 +5709,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B38" s="49" t="s">
         <v>200</v>
       </c>
@@ -5711,16 +5722,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
-    </row>
-    <row r="41" spans="2:6">
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B41" s="44" t="s">
         <v>202</v>
       </c>
@@ -5733,16 +5744,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
-    </row>
-    <row r="44" spans="2:6">
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B44" s="44" t="s">
         <v>267</v>
       </c>
@@ -5757,7 +5768,7 @@
       <c r="E44" s="244"/>
       <c r="F44" s="244"/>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="44" t="s">
         <v>268</v>
       </c>
@@ -5772,7 +5783,7 @@
       <c r="E45" s="244"/>
       <c r="F45" s="244"/>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="44" t="s">
         <v>203</v>
       </c>
@@ -5785,12 +5796,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B49" s="44" t="s">
         <v>223</v>
       </c>
@@ -5803,16 +5814,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
-    </row>
-    <row r="52" spans="2:6">
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="44" t="s">
         <v>204</v>
       </c>
@@ -5825,8 +5836,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5834,7 +5845,7 @@
       <c r="E54" s="464"/>
       <c r="F54" s="464"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="44" t="s">
         <v>207</v>
       </c>
@@ -5847,25 +5858,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+    <row r="57" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
-    </row>
-    <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
+    </row>
+    <row r="58" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
-    </row>
-    <row r="60" spans="2:6">
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="44" t="s">
         <v>227</v>
       </c>
@@ -5878,7 +5889,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B61" s="44" t="s">
         <v>213</v>
       </c>
@@ -5891,7 +5902,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="204" t="s">
         <v>302</v>
       </c>
@@ -5901,7 +5912,7 @@
       </c>
       <c r="F62" s="257"/>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="204" t="s">
         <v>330</v>
       </c>
@@ -5917,7 +5928,7 @@
         <v>0.51281220823452245</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B65" s="192" t="s">
         <v>323</v>
       </c>
@@ -5928,7 +5939,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B66" s="44" t="s">
         <v>324</v>
       </c>
@@ -5941,7 +5952,7 @@
         <v>0.37652309539416257</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="229" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -5955,7 +5966,7 @@
         <v>0.563411673135921</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="229" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -5969,7 +5980,7 @@
         <v>0.44445275381950455</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="229" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -5983,7 +5994,7 @@
         <v>1.5036272168761813</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="13.9">
+    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A71" s="200" t="s">
         <v>475</v>
       </c>
@@ -5993,45 +6004,45 @@
       <c r="E71" s="34"/>
       <c r="F71" s="34"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A72" s="191"/>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A75" s="191"/>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
         <v>215</v>
@@ -6045,7 +6056,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
         <v>234</v>
@@ -6059,7 +6070,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
         <v>308</v>
@@ -6069,7 +6080,7 @@
         <v>5.8904840599867017E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
         <v>310</v>
@@ -6079,16 +6090,16 @@
         <v>0.15503078912543219</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A82" s="191"/>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
         <v>224</v>
@@ -6102,7 +6113,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
         <v>222</v>
@@ -6116,7 +6127,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
         <v>235</v>
@@ -6130,16 +6141,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A87" s="191"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
         <v>217</v>
@@ -6153,7 +6164,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
         <v>236</v>
@@ -6167,10 +6178,10 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A91" s="191"/>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
         <v>467</v>
@@ -6184,7 +6195,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="13.9">
+    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A94" s="200" t="s">
         <v>468</v>
       </c>
@@ -6194,42 +6205,42 @@
       <c r="E94" s="34"/>
       <c r="F94" s="34"/>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A95" s="191"/>
     </row>
-    <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+    <row r="96" spans="1:6" ht="11.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B96" s="460" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
-    </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
-    </row>
-    <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B98" s="462" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
-    </row>
-    <row r="100" spans="2:6">
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="101" spans="2:6">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B101" s="49" t="s">
         <v>465</v>
       </c>
@@ -6238,7 +6249,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="2:6">
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="229" t="s">
         <v>317</v>
       </c>
@@ -6247,7 +6258,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="229" t="s">
         <v>316</v>
       </c>
@@ -6256,7 +6267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="44" t="s">
         <v>214</v>
       </c>
@@ -6265,36 +6276,36 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="106" spans="2:6">
+    <row r="106" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B106" s="250" t="s">
         <v>281</v>
       </c>
       <c r="C106" s="116"/>
     </row>
-    <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
-    </row>
-    <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
-    </row>
-    <row r="110" spans="2:6">
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="192" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="111" spans="2:6">
+    <row r="111" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B111" s="49" t="s">
         <v>466</v>
       </c>
@@ -6307,7 +6318,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="44" t="s">
         <v>322</v>
       </c>
@@ -6320,21 +6331,21 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+    <row r="114" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B114" s="460" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
-    </row>
-    <row r="116" spans="2:6">
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B116" s="192" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="12.4">
+    <row r="117" spans="2:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B117" s="342" t="s">
         <v>101</v>
       </c>
@@ -6351,7 +6362,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="118" spans="2:6">
+    <row r="118" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
         <v>Snowball Scenario (5yrs)</v>
@@ -6373,7 +6384,7 @@
         <v>-8.5764377786937424E-3</v>
       </c>
     </row>
-    <row r="119" spans="2:6">
+    <row r="119" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
         <v>Optimistic (5yrs)</v>
@@ -6395,7 +6406,7 @@
         <v>1.7826766936537737E-2</v>
       </c>
     </row>
-    <row r="120" spans="2:6">
+    <row r="120" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
         <v>Base (5yrs)</v>
@@ -6417,7 +6428,7 @@
         <v>3.134800981224807E-2</v>
       </c>
     </row>
-    <row r="121" spans="2:6">
+    <row r="121" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
         <v>Pessimistic (5yrs)</v>
@@ -6439,7 +6450,7 @@
         <v>4.5083874550095666E-2</v>
       </c>
     </row>
-    <row r="122" spans="2:6">
+    <row r="122" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
         <v>Devil's advocate (5yrs)</v>
@@ -6461,16 +6472,16 @@
         <v>5.9035182400374427E-2</v>
       </c>
     </row>
-    <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+    <row r="124" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B124" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
-    </row>
-    <row r="125" spans="2:6">
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
+    </row>
+    <row r="125" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B125" s="193" t="s">
         <v>218</v>
       </c>
@@ -6483,7 +6494,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="24.5" customHeight="1">
+    <row r="127" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B127" s="465" t="s">
         <v>356</v>
       </c>
@@ -6492,7 +6503,7 @@
       <c r="E127" s="465"/>
       <c r="F127" s="465"/>
     </row>
-    <row r="129" spans="1:6" ht="13.9">
+    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A129" s="200" t="s">
         <v>472</v>
       </c>
@@ -6502,30 +6513,30 @@
       <c r="E129" s="34"/>
       <c r="F129" s="34"/>
     </row>
-    <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B132" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B134" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B135" s="1" t="s">
         <v>221</v>
       </c>
@@ -6534,7 +6545,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B136" s="194" t="s">
         <v>220</v>
       </c>
@@ -6547,14 +6558,14 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B138" s="192" t="s">
         <v>492</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
-    <row r="139" spans="1:6" ht="12.4">
+    <row r="139" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B139" s="340" t="s">
         <v>460</v>
       </c>
@@ -6573,7 +6584,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="336" t="s">
         <v>311</v>
       </c>
@@ -6594,7 +6605,7 @@
         <v>0.32950289523458665</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="336" t="s">
         <v>312</v>
       </c>
@@ -6615,14 +6626,14 @@
         <v>0.22621703288100403</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="194"/>
       <c r="C142" s="194"/>
       <c r="D142" s="194"/>
       <c r="E142" s="194"/>
       <c r="F142" s="194"/>
     </row>
-    <row r="143" spans="1:6" ht="12.4">
+    <row r="143" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B143" s="340" t="s">
         <v>461</v>
       </c>
@@ -6641,7 +6652,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B144" s="336" t="s">
         <v>314</v>
       </c>
@@ -6662,7 +6673,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B145" s="336" t="s">
         <v>313</v>
       </c>
@@ -6683,7 +6694,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="13.9">
+    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A147" s="200" t="s">
         <v>473</v>
       </c>
@@ -6693,21 +6704,21 @@
       <c r="E147" s="34"/>
       <c r="F147" s="34"/>
     </row>
-    <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B149" s="467" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B151" s="192" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B152" s="464" t="s">
         <v>293</v>
       </c>
@@ -6716,80 +6727,92 @@
       <c r="E152" s="464"/>
       <c r="F152" s="464"/>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B153" s="196" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B154" s="196" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B155" s="196" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B157" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+    <row r="158" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B158" s="461" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
-    </row>
-    <row r="160" spans="1:6">
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B160" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+    <row r="161" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
-    </row>
-    <row r="164" spans="2:6">
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B164" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="165" spans="2:6">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B165" s="196" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B166" s="196" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B167" s="196" t="s">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6829,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6845,15 +6856,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
         <v>CNY</v>
@@ -6902,7 +6913,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>93</v>
       </c>
@@ -6918,7 +6929,7 @@
       <c r="L2" s="35"/>
       <c r="M2" s="35"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>25</v>
       </c>
@@ -6926,7 +6937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="31" t="s">
         <v>0</v>
       </c>
@@ -6946,7 +6957,7 @@
       <c r="L4" s="287"/>
       <c r="M4" s="287"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="38" t="s">
         <v>40</v>
       </c>
@@ -6968,7 +6979,7 @@
       <c r="L5" s="287"/>
       <c r="M5" s="287"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="38" t="s">
         <v>51</v>
       </c>
@@ -6990,7 +7001,7 @@
       <c r="L6" s="287"/>
       <c r="M6" s="287"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="66" t="s">
         <v>58</v>
       </c>
@@ -7010,7 +7021,7 @@
       <c r="L7" s="288"/>
       <c r="M7" s="288"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="38" t="s">
         <v>46</v>
       </c>
@@ -7030,7 +7041,7 @@
       <c r="L8" s="287"/>
       <c r="M8" s="287"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="38" t="s">
         <v>134</v>
       </c>
@@ -7046,7 +7057,7 @@
       <c r="L9" s="287"/>
       <c r="M9" s="287"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="38" t="s">
         <v>138</v>
       </c>
@@ -7062,7 +7073,7 @@
       <c r="L10" s="287"/>
       <c r="M10" s="287"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="38" t="s">
         <v>133</v>
       </c>
@@ -7078,7 +7089,7 @@
       <c r="L11" s="287"/>
       <c r="M11" s="287"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="38" t="s">
         <v>37</v>
       </c>
@@ -7098,7 +7109,7 @@
       <c r="L12" s="287"/>
       <c r="M12" s="287"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="38" t="s">
         <v>64</v>
       </c>
@@ -7118,7 +7129,7 @@
       <c r="L13" s="287"/>
       <c r="M13" s="287"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="38" t="s">
         <v>47</v>
       </c>
@@ -7138,7 +7149,7 @@
       <c r="L14" s="287"/>
       <c r="M14" s="287"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="41" t="s">
         <v>39</v>
       </c>
@@ -7158,7 +7169,7 @@
       <c r="L15" s="289"/>
       <c r="M15" s="289"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="27" t="s">
         <v>41</v>
       </c>
@@ -7178,13 +7189,13 @@
       <c r="L16" s="287"/>
       <c r="M16" s="287"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="26" t="s">
         <v>44</v>
       </c>
@@ -7200,7 +7211,7 @@
       <c r="L19" s="287"/>
       <c r="M19" s="287"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="26" t="s">
         <v>50</v>
       </c>
@@ -7216,7 +7227,7 @@
       <c r="L20" s="287"/>
       <c r="M20" s="287"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="26" t="s">
         <v>49</v>
       </c>
@@ -7232,7 +7243,7 @@
       <c r="L21" s="287"/>
       <c r="M21" s="287"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="26" t="s">
         <v>286</v>
       </c>
@@ -7252,7 +7263,7 @@
       <c r="L22" s="287"/>
       <c r="M22" s="287"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="26" t="s">
         <v>288</v>
       </c>
@@ -7272,7 +7283,7 @@
       <c r="L23" s="287"/>
       <c r="M23" s="287"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="26" t="s">
         <v>287</v>
       </c>
@@ -7292,7 +7303,7 @@
       <c r="L24" s="287"/>
       <c r="M24" s="287"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="23" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -7315,7 +7326,7 @@
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>26</v>
       </c>
@@ -7323,7 +7334,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="25" t="s">
         <v>22</v>
       </c>
@@ -7345,7 +7356,7 @@
       <c r="L28" s="287"/>
       <c r="M28" s="287"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="25" t="s">
         <v>30</v>
       </c>
@@ -7366,7 +7377,7 @@
       <c r="L29" s="287"/>
       <c r="M29" s="287"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="28" t="s">
         <v>38</v>
       </c>
@@ -7387,7 +7398,7 @@
       <c r="L30" s="289"/>
       <c r="M30" s="289"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="28" t="s">
         <v>28</v>
       </c>
@@ -7408,7 +7419,7 @@
       <c r="L31" s="289"/>
       <c r="M31" s="289"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="25" t="s">
         <v>143</v>
       </c>
@@ -7429,7 +7440,7 @@
       <c r="L32" s="287"/>
       <c r="M32" s="287"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
         <v>78</v>
       </c>
@@ -7445,12 +7456,12 @@
       <c r="L34" s="35"/>
       <c r="M34" s="35"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="31" t="s">
         <v>0</v>
       </c>
@@ -7499,7 +7510,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="38" t="s">
         <v>40</v>
       </c>
@@ -7548,7 +7559,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="30" t="s">
         <v>55</v>
       </c>
@@ -7597,7 +7608,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="38" t="s">
         <v>51</v>
       </c>
@@ -7646,7 +7657,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="66" t="s">
         <v>58</v>
       </c>
@@ -7695,7 +7706,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="66" t="s">
         <v>61</v>
       </c>
@@ -7744,7 +7755,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="38" t="s">
         <v>46</v>
       </c>
@@ -7793,7 +7804,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="41" t="s">
         <v>127</v>
       </c>
@@ -7842,7 +7853,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="41" t="s">
         <v>139</v>
       </c>
@@ -7891,7 +7902,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="38" t="s">
         <v>65</v>
       </c>
@@ -7940,7 +7951,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="38" t="s">
         <v>47</v>
       </c>
@@ -7989,7 +8000,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="41" t="s">
         <v>39</v>
       </c>
@@ -8038,7 +8049,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="27" t="s">
         <v>41</v>
       </c>
@@ -8087,12 +8098,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="38" t="s">
         <v>37</v>
       </c>
@@ -8141,7 +8152,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="38" t="s">
         <v>64</v>
       </c>
@@ -8190,12 +8201,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="156" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="38" t="s">
         <v>134</v>
       </c>
@@ -8244,7 +8255,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="38" t="s">
         <v>138</v>
       </c>
@@ -8293,7 +8304,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="38" t="s">
         <v>133</v>
       </c>
@@ -8342,7 +8353,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="38" t="s">
         <v>135</v>
       </c>
@@ -8391,13 +8402,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="26" t="s">
         <v>44</v>
       </c>
@@ -8446,7 +8457,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="26" t="s">
         <v>50</v>
       </c>
@@ -8495,7 +8506,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="26" t="s">
         <v>49</v>
       </c>
@@ -8544,7 +8555,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="26" t="s">
         <v>305</v>
       </c>
@@ -8593,7 +8604,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="23" t="s">
         <v>34</v>
       </c>
@@ -8642,12 +8653,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8697,7 +8708,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="30" t="s">
         <v>55</v>
       </c>
@@ -8746,7 +8757,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="77" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8796,7 +8807,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="41" t="s">
         <v>139</v>
       </c>
@@ -8845,7 +8856,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="77" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8895,7 +8906,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="34" t="s">
         <v>79</v>
       </c>
@@ -8911,13 +8922,13 @@
       <c r="L74" s="35"/>
       <c r="M74" s="35"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="25" t="s">
         <v>1</v>
       </c>
@@ -8966,7 +8977,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="90" t="s">
         <v>82</v>
       </c>
@@ -9000,7 +9011,7 @@
       <c r="L77" s="291"/>
       <c r="M77" s="291"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="90" t="s">
         <v>83</v>
       </c>
@@ -9034,7 +9045,7 @@
       <c r="L78" s="291"/>
       <c r="M78" s="291"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="25" t="s">
         <v>38</v>
       </c>
@@ -9083,7 +9094,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="25" t="s">
         <v>28</v>
       </c>
@@ -9164,7 +9175,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -9175,7 +9186,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="17" t="s">
         <v>35</v>
       </c>
@@ -9191,7 +9202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="76" t="s">
         <v>131</v>
       </c>
@@ -9202,7 +9213,7 @@
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>154</v>
       </c>
@@ -9222,7 +9233,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
@@ -9244,7 +9255,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -9265,7 +9276,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
@@ -9286,7 +9297,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>66</v>
       </c>
@@ -9307,7 +9318,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>144</v>
       </c>
@@ -9328,7 +9339,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9349,7 +9360,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -9369,7 +9380,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
@@ -9381,7 +9392,7 @@
       </c>
       <c r="H11" s="232"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="77" t="s">
         <v>69</v>
       </c>
@@ -9405,12 +9416,12 @@
         <v>32872308844.689007</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="77"/>
       <c r="G13" s="78"/>
       <c r="H13" s="19"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>153</v>
       </c>
@@ -9430,7 +9441,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>327</v>
       </c>
@@ -9450,7 +9461,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
@@ -9470,7 +9481,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>66</v>
       </c>
@@ -9490,7 +9501,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>144</v>
       </c>
@@ -9510,7 +9521,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
@@ -9532,7 +9543,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>16</v>
       </c>
@@ -9552,7 +9563,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
@@ -9572,7 +9583,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
@@ -9584,7 +9595,7 @@
       </c>
       <c r="H22" s="232"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>19</v>
       </c>
@@ -9597,7 +9608,7 @@
       </c>
       <c r="H23" s="232"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="77" t="s">
         <v>70</v>
       </c>
@@ -9621,7 +9632,7 @@
         <v>332369284.89399999</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>169</v>
       </c>
@@ -9638,7 +9649,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
@@ -9657,7 +9668,7 @@
         <v>18874553188.800007</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>4</v>
       </c>
@@ -9672,7 +9683,7 @@
       </c>
       <c r="H28" s="170"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
@@ -9691,7 +9702,7 @@
         <v>18734486685.410007</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
@@ -9707,7 +9718,7 @@
       </c>
       <c r="H30" s="170"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="77" t="s">
         <v>172</v>
       </c>
@@ -9724,7 +9735,7 @@
       </c>
       <c r="H31" s="170"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
@@ -9744,7 +9755,7 @@
         <v>42384182398.360008</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="80" t="s">
         <v>2</v>
       </c>
@@ -9755,7 +9766,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="177"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
@@ -9768,7 +9779,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>170</v>
       </c>
@@ -9787,7 +9798,7 @@
         <v>9179504268.7770004</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
@@ -9803,7 +9814,7 @@
       </c>
       <c r="H36" s="177"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
@@ -9819,7 +9830,7 @@
       </c>
       <c r="H37" s="177"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>13</v>
       </c>
@@ -9835,7 +9846,7 @@
       </c>
       <c r="H38" s="177"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
@@ -9854,7 +9865,7 @@
         <v>1000531628.572</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="77" t="s">
         <v>173</v>
       </c>
@@ -9874,7 +9885,7 @@
         <v>33204678129.583008</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>15</v>
       </c>
@@ -9894,7 +9905,7 @@
         <v>31905972294.345009</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="80" t="s">
         <v>20</v>
       </c>
@@ -9913,7 +9924,7 @@
         <v>1298705835.2379999</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="76" t="s">
         <v>92</v>
       </c>
@@ -9924,7 +9935,7 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>228</v>
       </c>
@@ -9938,7 +9949,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>230</v>
       </c>
@@ -9952,7 +9963,7 @@
       </c>
       <c r="F46" s="223"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9967,10 +9978,10 @@
       </c>
       <c r="F47" s="223"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="223"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="143" t="s">
         <v>120</v>
       </c>
@@ -9983,7 +9994,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>90</v>
       </c>
@@ -9997,7 +10008,7 @@
       </c>
       <c r="F50" s="223"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>146</v>
       </c>
@@ -10008,10 +10019,10 @@
       </c>
       <c r="F51" s="223"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="223"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="143" t="s">
         <v>119</v>
       </c>
@@ -10023,7 +10034,7 @@
       </c>
       <c r="F53" s="223"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>116</v>
       </c>
@@ -10037,7 +10048,7 @@
       </c>
       <c r="F54" s="223"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>118</v>
       </c>
@@ -10051,10 +10062,10 @@
       </c>
       <c r="F55" s="223"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="223"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="143" t="s">
         <v>145</v>
       </c>
@@ -10066,7 +10077,7 @@
       </c>
       <c r="F57" s="223"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>86</v>
       </c>
@@ -10077,7 +10088,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>89</v>
       </c>
@@ -10088,10 +10099,10 @@
       </c>
       <c r="F59" s="223"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="223"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="143" t="s">
         <v>231</v>
       </c>
@@ -10103,7 +10114,7 @@
       </c>
       <c r="F61" s="223"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>210</v>
       </c>
@@ -10119,7 +10130,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="76" t="s">
         <v>162</v>
       </c>
@@ -10130,7 +10141,7 @@
       <c r="G64" s="35"/>
       <c r="H64" s="35"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>158</v>
       </c>
@@ -10144,7 +10155,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="102" t="s">
         <v>157</v>
       </c>
@@ -10160,7 +10171,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="102" t="s">
         <v>147</v>
       </c>
@@ -10170,7 +10181,7 @@
       </c>
       <c r="F67" s="223"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="102" t="s">
         <v>151</v>
       </c>
@@ -10180,7 +10191,7 @@
       </c>
       <c r="F68" s="223"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="102" t="s">
         <v>149</v>
       </c>
@@ -10190,7 +10201,7 @@
       </c>
       <c r="F69" s="223"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="77" t="s">
         <v>158</v>
       </c>
@@ -10200,10 +10211,10 @@
       </c>
       <c r="F70" s="223"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="223"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="225" t="s">
         <v>256</v>
       </c>
@@ -10215,7 +10226,7 @@
       </c>
       <c r="F72" s="223"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="102" t="s">
         <v>255</v>
       </c>
@@ -10231,7 +10242,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="227" t="s">
         <v>259</v>
       </c>
@@ -10247,7 +10258,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="77" t="s">
         <v>258</v>
       </c>
@@ -10260,7 +10271,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="229" t="s">
         <v>260</v>
       </c>
@@ -10273,10 +10284,10 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="223"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>159</v>
       </c>
@@ -10288,7 +10299,7 @@
       </c>
       <c r="F78" s="223"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="102" t="s">
         <v>148</v>
       </c>
@@ -10302,7 +10313,7 @@
       </c>
       <c r="F79" s="223"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="102" t="s">
         <v>152</v>
       </c>
@@ -10316,7 +10327,7 @@
       </c>
       <c r="F80" s="223"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="102" t="s">
         <v>150</v>
       </c>
@@ -10330,7 +10341,7 @@
       </c>
       <c r="F81" s="223"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="77" t="s">
         <v>159</v>
       </c>
@@ -10344,7 +10355,7 @@
       </c>
       <c r="F82" s="223"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="76" t="s">
         <v>241</v>
       </c>
@@ -10355,7 +10366,7 @@
       <c r="G84" s="35"/>
       <c r="H84" s="35"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>242</v>
       </c>
@@ -10363,7 +10374,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="212" t="s">
         <v>239</v>
       </c>
@@ -10380,7 +10391,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="212" t="s">
         <v>240</v>
       </c>
@@ -10397,7 +10408,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="213" t="s">
         <v>159</v>
       </c>
@@ -10414,7 +10425,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="77" t="s">
         <v>244</v>
       </c>
@@ -10450,19 +10461,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q807"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
@@ -10519,7 +10530,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
         <v>95</v>
@@ -10542,7 +10553,7 @@
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>391</v>
@@ -10562,7 +10573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -10619,7 +10630,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>43</v>
@@ -10674,7 +10685,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
         <v>45</v>
@@ -10729,7 +10740,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>42</v>
@@ -10784,7 +10795,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
         <v>127</v>
@@ -10841,7 +10852,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
         <v>413</v>
@@ -10898,7 +10909,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>65</v>
@@ -10953,7 +10964,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
         <v>137</v>
@@ -11008,7 +11019,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>60</v>
@@ -11063,7 +11074,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
         <v>208</v>
@@ -11120,7 +11131,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
         <v>129</v>
@@ -11177,7 +11188,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -11232,7 +11243,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
         <v>396</v>
@@ -11287,7 +11298,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
         <v>49</v>
@@ -11313,7 +11324,7 @@
       <c r="P17" s="272"/>
       <c r="Q17" s="272"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
         <v>94</v>
@@ -11338,7 +11349,7 @@
       <c r="P18" s="273"/>
       <c r="Q18" s="273"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
         <v>63</v>
@@ -11395,7 +11406,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="26"/>
       <c r="C20" s="59"/>
@@ -11414,7 +11425,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
         <v>174</v>
@@ -11437,7 +11448,7 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
         <v>43</v>
@@ -11458,7 +11469,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
         <v>40</v>
@@ -11515,7 +11526,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
         <v>59</v>
@@ -11572,7 +11583,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
         <v>46</v>
@@ -11629,7 +11640,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
         <v>43</v>
@@ -11686,18 +11697,18 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="E27" s="237"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
         <v>175</v>
       </c>
       <c r="E28" s="237"/>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
         <v>40</v>
@@ -11754,7 +11765,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="10"/>
       <c r="B30" s="65" t="str">
         <f>B24</f>
@@ -11812,7 +11823,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="B31" s="26" t="str">
         <f>B25</f>
@@ -11870,7 +11881,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
         <v>43</v>
@@ -11925,18 +11936,18 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="E33" s="237"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
         <v>42</v>
       </c>
       <c r="E34" s="237"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
         <v>394</v>
@@ -11993,18 +12004,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="237"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
         <v>176</v>
       </c>
       <c r="E37" s="237"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
         <v>394</v>
@@ -12059,18 +12070,18 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="E39" s="237"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
         <v>177</v>
       </c>
       <c r="E40" s="237"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
         <v>142</v>
@@ -12128,10 +12139,10 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
         <v>178</v>
@@ -12154,14 +12165,14 @@
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
         <v>57</v>
       </c>
       <c r="E44" s="237"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
         <v>37</v>
@@ -12216,7 +12227,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
         <v>272</v>
@@ -12271,7 +12282,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
         <v>269</v>
@@ -12328,7 +12339,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
         <v>65</v>
@@ -12383,11 +12394,11 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="E49" s="237"/>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
         <v>130</v>
@@ -12397,7 +12408,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
         <v>85</v>
@@ -12421,7 +12432,7 @@
       <c r="P51" s="151"/>
       <c r="Q51" s="151"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
         <v>84</v>
@@ -12445,7 +12456,7 @@
       <c r="P52" s="151"/>
       <c r="Q52" s="151"/>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
         <v>87</v>
@@ -12500,11 +12511,11 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="E54" s="237"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
         <v>139</v>
@@ -12514,7 +12525,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
         <v>138</v>
@@ -12569,7 +12580,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
         <v>134</v>
@@ -12624,7 +12635,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
         <v>133</v>
@@ -12679,7 +12690,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
         <v>163</v>
@@ -12734,7 +12745,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
         <v>135</v>
@@ -12790,7 +12801,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
         <v>164</v>
@@ -12845,11 +12856,11 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="E62" s="237"/>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
         <v>140</v>
@@ -12859,7 +12870,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
         <v>138</v>
@@ -12884,7 +12895,7 @@
       <c r="P64" s="157"/>
       <c r="Q64" s="157"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
         <v>132</v>
@@ -12909,7 +12920,7 @@
       <c r="P65" s="157"/>
       <c r="Q65" s="157"/>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
         <v>133</v>
@@ -12934,7 +12945,7 @@
       <c r="P66" s="157"/>
       <c r="Q66" s="157"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
         <v>163</v>
@@ -12961,10 +12972,10 @@
       <c r="P67" s="157"/>
       <c r="Q67" s="157"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
         <v>181</v>
@@ -12987,7 +12998,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
         <v>185</v>
@@ -13008,7 +13019,7 @@
       <c r="P70" s="12"/>
       <c r="Q70" s="12"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
         <v>43</v>
@@ -13065,7 +13076,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
         <v>45</v>
@@ -13122,7 +13133,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
         <v>42</v>
@@ -13179,7 +13190,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
         <v>127</v>
@@ -13236,7 +13247,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
         <v>128</v>
@@ -13293,7 +13304,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
         <v>65</v>
@@ -13350,7 +13361,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
         <v>137</v>
@@ -13407,7 +13418,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>60</v>
@@ -13464,7 +13475,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="38" t="str">
         <f>B13</f>
@@ -13522,7 +13533,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
         <v>129</v>
@@ -13579,7 +13590,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
         <v>62</v>
@@ -13636,7 +13647,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>77</v>
@@ -13695,7 +13706,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
         <v>49</v>
@@ -13721,7 +13732,7 @@
       <c r="P83" s="203"/>
       <c r="Q83" s="203"/>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
         <v>94</v>
@@ -13745,7 +13756,7 @@
       <c r="P84" s="151"/>
       <c r="Q84" s="151"/>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
         <v>117</v>
@@ -13802,18 +13813,18 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="E86" s="237"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
         <v>183</v>
       </c>
       <c r="E87" s="237"/>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="B88" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13869,7 +13880,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13925,7 +13936,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
         <v>182</v>
@@ -13980,7 +13991,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
         <v>329</v>
@@ -14001,7 +14012,7 @@
       <c r="P91" s="293"/>
       <c r="Q91" s="293"/>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>328</v>
@@ -14056,11 +14067,11 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="E93" s="237"/>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
         <v>81</v>
@@ -14081,7 +14092,7 @@
       <c r="P94" s="12"/>
       <c r="Q94" s="12"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
         <v>121</v>
@@ -14138,7 +14149,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
         <v>137</v>
@@ -14195,10 +14206,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
         <v>184</v>
@@ -14221,7 +14232,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
         <v>26</v>
@@ -14231,7 +14242,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="25" t="s">
         <v>1</v>
@@ -14288,7 +14299,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
         <v>179</v>
@@ -14345,7 +14356,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
         <v>180</v>
@@ -14402,7 +14413,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
         <v>38</v>
@@ -14459,7 +14470,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
         <v>28</v>
@@ -14516,11 +14527,11 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="E105" s="237"/>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
         <v>189</v>
@@ -14543,7 +14554,7 @@
       <c r="P106" s="12"/>
       <c r="Q106" s="12"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
         <v>186</v>
@@ -14600,7 +14611,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
         <v>187</v>
@@ -14657,7 +14668,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
         <v>66</v>
@@ -14684,18 +14695,18 @@
       <c r="P109" s="186"/>
       <c r="Q109" s="186"/>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="E110" s="237"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
         <v>48</v>
       </c>
       <c r="E111" s="237"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
         <v>303</v>
@@ -14749,7 +14760,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>304</v>
@@ -14804,11 +14815,11 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="E114" s="237"/>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
         <v>36</v>
@@ -14867,7 +14878,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
         <v>190</v>
@@ -14925,7 +14936,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B117" s="7" t="s">
         <v>80</v>
       </c>
@@ -14982,7 +14993,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>88</v>
       </c>
@@ -15041,7 +15052,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
         <v>191</v>
@@ -15101,7 +15112,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="26"/>
       <c r="C120" s="59"/>
@@ -15120,7 +15131,7 @@
       <c r="P120" s="12"/>
       <c r="Q120" s="12"/>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
         <v>192</v>
@@ -15143,7 +15154,7 @@
       <c r="P121" s="35"/>
       <c r="Q121" s="35"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
         <v>141</v>
@@ -15164,7 +15175,7 @@
       <c r="P122" s="12"/>
       <c r="Q122" s="12"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="26" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -15222,7 +15233,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
         <v>226</v>
@@ -15279,7 +15290,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B125" s="2" t="s">
         <v>306</v>
       </c>
@@ -15329,688 +15340,688 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q11 G13:Q16 G23:Q25">
@@ -16032,16 +16043,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:U118"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
     <col min="2" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="11" width="11.1328125" customWidth="1"/>
+    <col min="10" max="11" width="11.1640625" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
     <col min="13" max="13" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="13.9">
+    <row r="2" spans="2:15" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>52</v>
       </c>
@@ -16056,7 +16067,7 @@
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
     </row>
-    <row r="3" spans="2:15" ht="13.15">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B3" s="106" t="s">
         <v>136</v>
       </c>
@@ -16071,7 +16082,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="4" spans="2:15">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B4" s="97" t="s">
         <v>391</v>
       </c>
@@ -16103,7 +16114,7 @@
       </c>
       <c r="J4" s="305"/>
     </row>
-    <row r="5" spans="2:15">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B5" s="187" t="s">
         <v>105</v>
       </c>
@@ -16131,7 +16142,7 @@
       </c>
       <c r="J5" s="305"/>
     </row>
-    <row r="6" spans="2:15" ht="13.25" customHeight="1">
+    <row r="6" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="136" t="s">
         <v>194</v>
       </c>
@@ -16164,7 +16175,7 @@
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
     </row>
-    <row r="7" spans="2:15" ht="12.75" customHeight="1">
+    <row r="7" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="318" t="s">
         <v>428</v>
       </c>
@@ -16194,7 +16205,7 @@
       <c r="N7" s="304"/>
       <c r="O7" s="304"/>
     </row>
-    <row r="8" spans="2:15" ht="13.15">
+    <row r="8" spans="2:15" ht="14" x14ac:dyDescent="0.15">
       <c r="B8" s="136" t="s">
         <v>424</v>
       </c>
@@ -16229,7 +16240,7 @@
       <c r="N8" s="304"/>
       <c r="O8" s="304"/>
     </row>
-    <row r="9" spans="2:15" ht="13.15" thickBot="1">
+    <row r="9" spans="2:15" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B9" s="189" t="str">
         <f>"*"&amp;Thesis!E15</f>
         <v>*CNY</v>
@@ -16255,7 +16266,7 @@
       <c r="N9" s="304"/>
       <c r="O9" s="304"/>
     </row>
-    <row r="10" spans="2:15" ht="13.5" thickTop="1">
+    <row r="10" spans="2:15" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B10" s="107" t="s">
         <v>425</v>
       </c>
@@ -16277,7 +16288,7 @@
       <c r="N10" s="304"/>
       <c r="O10" s="304"/>
     </row>
-    <row r="11" spans="2:15" ht="13.15">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B11" s="136" t="s">
         <v>423</v>
       </c>
@@ -16293,7 +16304,7 @@
       <c r="I11" s="307"/>
       <c r="J11" s="307"/>
     </row>
-    <row r="13" spans="2:15" ht="13.9">
+    <row r="13" spans="2:15" ht="16" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
         <v>426</v>
       </c>
@@ -16308,7 +16319,7 @@
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
     </row>
-    <row r="14" spans="2:15" ht="13.15">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B14" s="106" t="s">
         <v>397</v>
       </c>
@@ -16326,7 +16337,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="15" spans="2:15">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B15" s="139" t="s">
         <v>419</v>
       </c>
@@ -16351,7 +16362,7 @@
       </c>
       <c r="J15" s="126"/>
     </row>
-    <row r="16" spans="2:15" ht="13.25" customHeight="1">
+    <row r="16" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="114" t="s">
         <v>420</v>
       </c>
@@ -16367,7 +16378,7 @@
         <v>2.38559171477595E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.25" customHeight="1">
+    <row r="17" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="308" t="s">
         <v>547</v>
       </c>
@@ -16386,7 +16397,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="13.25" customHeight="1">
+    <row r="18" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="308" t="s">
         <v>421</v>
       </c>
@@ -16413,10 +16424,10 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
       <c r="L19" s="275"/>
     </row>
-    <row r="20" spans="1:21" ht="13.15">
+    <row r="20" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A20" s="121" t="s">
         <v>397</v>
       </c>
@@ -16455,7 +16466,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A21" s="302" t="str">
         <f t="shared" ref="A21:A50" si="0">IF($C$15&lt;B21,"",IF(B21&gt;=$F$15,"II","I"))</f>
         <v>I</v>
@@ -16504,7 +16515,7 @@
         <v>12582755392.17198</v>
       </c>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A22" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16553,7 +16564,7 @@
         <v>12012054603.541407</v>
       </c>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A23" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16610,7 +16621,7 @@
       <c r="T23" s="275"/>
       <c r="U23" s="275"/>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A24" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16667,7 +16678,7 @@
       <c r="T24" s="275"/>
       <c r="U24" s="275"/>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16724,7 +16735,7 @@
       <c r="T25" s="275"/>
       <c r="U25" s="275"/>
     </row>
-    <row r="26" spans="1:21">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16773,7 +16784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:21">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16822,7 +16833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:21">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16871,7 +16882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:21">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16920,7 +16931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:21">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16969,7 +16980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:21">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17018,7 +17029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17067,7 +17078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:21">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17124,7 +17135,7 @@
       <c r="T33" s="275"/>
       <c r="U33" s="275"/>
     </row>
-    <row r="34" spans="1:21">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17181,7 +17192,7 @@
       <c r="T34" s="275"/>
       <c r="U34" s="275"/>
     </row>
-    <row r="35" spans="1:21">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17238,7 +17249,7 @@
       <c r="T35" s="275"/>
       <c r="U35" s="275"/>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A36" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17287,7 +17298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:21">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A37" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17336,7 +17347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A38" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17385,7 +17396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:21">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A39" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17434,7 +17445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A40" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17483,7 +17494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:21">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A41" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17532,7 +17543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A42" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17581,7 +17592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A43" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17630,7 +17641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A44" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17679,7 +17690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A45" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17728,7 +17739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A46" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17777,7 +17788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A47" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17834,7 +17845,7 @@
       <c r="T47" s="275"/>
       <c r="U47" s="275"/>
     </row>
-    <row r="48" spans="1:21">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A48" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17891,7 +17902,7 @@
       <c r="T48" s="275"/>
       <c r="U48" s="275"/>
     </row>
-    <row r="49" spans="1:21">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A49" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17948,7 +17959,7 @@
       <c r="T49" s="275"/>
       <c r="U49" s="275"/>
     </row>
-    <row r="50" spans="1:21">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A50" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18005,7 +18016,7 @@
       <c r="T50" s="275"/>
       <c r="U50" s="275"/>
     </row>
-    <row r="51" spans="1:21">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A51" s="315" t="s">
         <v>416</v>
       </c>
@@ -18051,7 +18062,7 @@
         <v>147029369191.0303</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="13.15">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
@@ -18064,10 +18075,10 @@
         <v>204489167276.40967</v>
       </c>
     </row>
-    <row r="53" spans="1:21">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.15">
       <c r="C53" s="111"/>
     </row>
-    <row r="54" spans="1:21" ht="13.15">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B54" s="115" t="s">
         <v>108</v>
       </c>
@@ -18082,7 +18093,7 @@
       <c r="K54" s="113"/>
       <c r="L54" s="113"/>
     </row>
-    <row r="55" spans="1:21" ht="13.15">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A55" s="125">
         <f>L52</f>
         <v>204489167276.40967</v>
@@ -18114,7 +18125,7 @@
       <c r="K55" s="123"/>
       <c r="L55" s="123"/>
     </row>
-    <row r="56" spans="1:21" ht="13.15">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A56" s="131">
         <v>1</v>
       </c>
@@ -18141,7 +18152,7 @@
       <c r="K56" s="295"/>
       <c r="L56" s="295"/>
     </row>
-    <row r="57" spans="1:21" ht="13.15">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A57" s="131">
         <v>2</v>
       </c>
@@ -18167,7 +18178,7 @@
       <c r="K57" s="295"/>
       <c r="L57" s="295"/>
     </row>
-    <row r="58" spans="1:21" ht="13.15">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A58" s="131">
         <v>3</v>
       </c>
@@ -18193,7 +18204,7 @@
       <c r="K58" s="295"/>
       <c r="L58" s="295"/>
     </row>
-    <row r="59" spans="1:21" ht="13.15">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A59" s="131">
         <v>4</v>
       </c>
@@ -18219,7 +18230,7 @@
       <c r="K59" s="295"/>
       <c r="L59" s="295"/>
     </row>
-    <row r="60" spans="1:21" ht="13.15">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A60" s="131">
         <v>5</v>
       </c>
@@ -18245,7 +18256,7 @@
       <c r="K60" s="295"/>
       <c r="L60" s="295"/>
     </row>
-    <row r="61" spans="1:21" ht="13.15">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A61" s="131">
         <v>6</v>
       </c>
@@ -18271,7 +18282,7 @@
       <c r="K61" s="295"/>
       <c r="L61" s="295"/>
     </row>
-    <row r="62" spans="1:21" ht="13.15">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A62" s="131">
         <v>7</v>
       </c>
@@ -18297,7 +18308,7 @@
       <c r="K62" s="295"/>
       <c r="L62" s="295"/>
     </row>
-    <row r="63" spans="1:21" ht="13.15">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A63" s="131">
         <v>8</v>
       </c>
@@ -18323,7 +18334,7 @@
       <c r="K63" s="295"/>
       <c r="L63" s="295"/>
     </row>
-    <row r="64" spans="1:21" ht="13.15">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A64" s="131">
         <v>9</v>
       </c>
@@ -18349,7 +18360,7 @@
       <c r="K64" s="295"/>
       <c r="L64" s="295"/>
     </row>
-    <row r="65" spans="1:21" ht="13.15">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A65" s="131">
         <v>10</v>
       </c>
@@ -18375,7 +18386,7 @@
       <c r="K65" s="295"/>
       <c r="L65" s="295"/>
     </row>
-    <row r="66" spans="1:21" ht="13.15">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A66" s="131">
         <v>15</v>
       </c>
@@ -18410,7 +18421,7 @@
       <c r="T66" s="275"/>
       <c r="U66" s="275"/>
     </row>
-    <row r="67" spans="1:21" ht="13.15">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A67" s="132">
         <v>20</v>
       </c>
@@ -18445,7 +18456,7 @@
       <c r="T67" s="275"/>
       <c r="U67" s="275"/>
     </row>
-    <row r="68" spans="1:21" ht="13.15">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A68" s="132">
         <v>25</v>
       </c>
@@ -18480,7 +18491,7 @@
       <c r="T68" s="275"/>
       <c r="U68" s="275"/>
     </row>
-    <row r="69" spans="1:21" ht="13.15">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A69" s="132">
         <v>30</v>
       </c>
@@ -18515,7 +18526,7 @@
       <c r="T69" s="275"/>
       <c r="U69" s="275"/>
     </row>
-    <row r="70" spans="1:21">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.15">
       <c r="C70" s="275"/>
       <c r="D70" s="111"/>
       <c r="E70" s="111"/>
@@ -18536,7 +18547,7 @@
       <c r="T70" s="275"/>
       <c r="U70" s="275"/>
     </row>
-    <row r="71" spans="1:21" ht="13.15">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B71" s="115" t="s">
         <v>109</v>
       </c>
@@ -18560,7 +18571,7 @@
       <c r="T71" s="275"/>
       <c r="U71" s="275"/>
     </row>
-    <row r="72" spans="1:21" ht="13.15">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B72" s="124">
         <f>B55</f>
         <v>0</v>
@@ -18588,7 +18599,7 @@
       <c r="K72" s="124"/>
       <c r="L72" s="124"/>
     </row>
-    <row r="73" spans="1:21" ht="13.15">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A73" s="131">
         <v>0</v>
       </c>
@@ -18619,7 +18630,7 @@
       <c r="K73" s="296"/>
       <c r="L73" s="296"/>
     </row>
-    <row r="74" spans="1:21" ht="13.15">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A74" s="131">
         <v>1</v>
       </c>
@@ -18650,7 +18661,7 @@
       <c r="K74" s="296"/>
       <c r="L74" s="296"/>
     </row>
-    <row r="75" spans="1:21" ht="13.15">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A75" s="131">
         <v>2</v>
       </c>
@@ -18681,7 +18692,7 @@
       <c r="K75" s="296"/>
       <c r="L75" s="296"/>
     </row>
-    <row r="76" spans="1:21" ht="13.15">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A76" s="131">
         <v>3</v>
       </c>
@@ -18712,7 +18723,7 @@
       <c r="K76" s="296"/>
       <c r="L76" s="296"/>
     </row>
-    <row r="77" spans="1:21" ht="13.15">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A77" s="131">
         <v>4</v>
       </c>
@@ -18743,7 +18754,7 @@
       <c r="K77" s="296"/>
       <c r="L77" s="296"/>
     </row>
-    <row r="78" spans="1:21" ht="13.15">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A78" s="131">
         <v>5</v>
       </c>
@@ -18774,7 +18785,7 @@
       <c r="K78" s="296"/>
       <c r="L78" s="296"/>
     </row>
-    <row r="79" spans="1:21" ht="13.15">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A79" s="131">
         <v>6</v>
       </c>
@@ -18805,7 +18816,7 @@
       <c r="K79" s="296"/>
       <c r="L79" s="296"/>
     </row>
-    <row r="80" spans="1:21" ht="13.15">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A80" s="131">
         <f t="shared" ref="A80" si="12">A62</f>
         <v>7</v>
@@ -18837,7 +18848,7 @@
       <c r="K80" s="296"/>
       <c r="L80" s="296"/>
     </row>
-    <row r="81" spans="1:12" ht="13.15">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A81" s="131">
         <v>8</v>
       </c>
@@ -18868,7 +18879,7 @@
       <c r="K81" s="296"/>
       <c r="L81" s="296"/>
     </row>
-    <row r="82" spans="1:12" ht="13.15">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A82" s="131">
         <f t="shared" ref="A82" si="13">A64</f>
         <v>9</v>
@@ -18900,7 +18911,7 @@
       <c r="K82" s="296"/>
       <c r="L82" s="296"/>
     </row>
-    <row r="83" spans="1:12" ht="13.15">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A83" s="131">
         <f t="shared" ref="A83:A87" si="14">A65</f>
         <v>10</v>
@@ -18932,7 +18943,7 @@
       <c r="K83" s="296"/>
       <c r="L83" s="296"/>
     </row>
-    <row r="84" spans="1:12" ht="13.15">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A84" s="131">
         <f t="shared" si="14"/>
         <v>15</v>
@@ -18964,7 +18975,7 @@
       <c r="K84" s="296"/>
       <c r="L84" s="296"/>
     </row>
-    <row r="85" spans="1:12" ht="13.15">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A85" s="132">
         <f t="shared" si="14"/>
         <v>20</v>
@@ -18996,7 +19007,7 @@
       <c r="K85" s="296"/>
       <c r="L85" s="296"/>
     </row>
-    <row r="86" spans="1:12" ht="13.15">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A86" s="132">
         <f t="shared" si="14"/>
         <v>25</v>
@@ -19028,7 +19039,7 @@
       <c r="K86" s="296"/>
       <c r="L86" s="296"/>
     </row>
-    <row r="87" spans="1:12" ht="13.15">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A87" s="132">
         <f t="shared" si="14"/>
         <v>30</v>
@@ -19060,7 +19071,7 @@
       <c r="K87" s="296"/>
       <c r="L87" s="296"/>
     </row>
-    <row r="89" spans="1:12" ht="13.15">
+    <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="B89" s="153" t="s">
         <v>101</v>
       </c>
@@ -19083,7 +19094,7 @@
       <c r="K89" s="323"/>
       <c r="L89" s="323"/>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B90" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
@@ -19111,7 +19122,7 @@
       <c r="K90" s="297"/>
       <c r="L90" s="297"/>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B91" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
@@ -19139,7 +19150,7 @@
       <c r="K91" s="297"/>
       <c r="L91" s="297"/>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B92" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
@@ -19167,7 +19178,7 @@
       <c r="K92" s="297"/>
       <c r="L92" s="297"/>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B93" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
@@ -19195,7 +19206,7 @@
       <c r="K93" s="297"/>
       <c r="L93" s="297"/>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B94" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
@@ -19223,7 +19234,7 @@
       <c r="K94" s="297"/>
       <c r="L94" s="297"/>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B95" s="141"/>
       <c r="C95" s="141"/>
       <c r="D95" s="141"/>
@@ -19236,16 +19247,16 @@
       <c r="K95" s="142"/>
       <c r="L95" s="142"/>
     </row>
-    <row r="105" spans="3:3">
+    <row r="105" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C105" s="112"/>
     </row>
-    <row r="106" spans="3:3">
+    <row r="106" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C106" s="112"/>
     </row>
-    <row r="107" spans="3:3">
+    <row r="107" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C107" s="112"/>
     </row>
-    <row r="114" spans="3:21">
+    <row r="114" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C114" s="275"/>
       <c r="M114" s="275"/>
       <c r="N114" s="275"/>
@@ -19257,7 +19268,7 @@
       <c r="T114" s="275"/>
       <c r="U114" s="275"/>
     </row>
-    <row r="115" spans="3:21">
+    <row r="115" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C115" s="275"/>
       <c r="M115" s="275"/>
       <c r="N115" s="275"/>
@@ -19269,7 +19280,7 @@
       <c r="T115" s="275"/>
       <c r="U115" s="275"/>
     </row>
-    <row r="116" spans="3:21">
+    <row r="116" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C116" s="275"/>
       <c r="M116" s="275"/>
       <c r="N116" s="275"/>
@@ -19281,7 +19292,7 @@
       <c r="T116" s="275"/>
       <c r="U116" s="275"/>
     </row>
-    <row r="117" spans="3:21">
+    <row r="117" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C117" s="275"/>
       <c r="M117" s="275"/>
       <c r="N117" s="275"/>
@@ -19293,7 +19304,7 @@
       <c r="T117" s="275"/>
       <c r="U117" s="275"/>
     </row>
-    <row r="118" spans="3:21">
+    <row r="118" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C118" s="275"/>
       <c r="M118" s="275"/>
       <c r="N118" s="275"/>
@@ -19333,14 +19344,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:G67"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="13.9">
+    <row r="2" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>122</v>
       </c>
@@ -19350,7 +19361,7 @@
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" spans="2:7" ht="13.15">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B3" s="145" t="s">
         <v>125</v>
       </c>
@@ -19359,7 +19370,7 @@
       </c>
       <c r="E3" s="97"/>
     </row>
-    <row r="4" spans="2:7" ht="12.75" customHeight="1">
+    <row r="4" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="139" t="s">
         <v>123</v>
       </c>
@@ -19380,14 +19391,14 @@
       <c r="F4" s="469"/>
       <c r="G4" s="469"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.15">
       <c r="C5" s="445"/>
       <c r="D5" s="469"/>
       <c r="E5" s="469"/>
       <c r="F5" s="469"/>
       <c r="G5" s="469"/>
     </row>
-    <row r="6" spans="2:7" ht="13.15">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B6" s="145" t="s">
         <v>91</v>
       </c>
@@ -19400,7 +19411,7 @@
       <c r="F6" s="469"/>
       <c r="G6" s="469"/>
     </row>
-    <row r="7" spans="2:7" ht="12.75" customHeight="1">
+    <row r="7" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="97" t="s">
         <v>232</v>
       </c>
@@ -19413,7 +19424,7 @@
       <c r="F7" s="469"/>
       <c r="G7" s="469"/>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B8" s="97" t="s">
         <v>63</v>
       </c>
@@ -19426,7 +19437,7 @@
       <c r="F8" s="469"/>
       <c r="G8" s="469"/>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B9" s="97" t="s">
         <v>54</v>
       </c>
@@ -19439,14 +19450,14 @@
       <c r="F9" s="469"/>
       <c r="G9" s="469"/>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
       <c r="C10" s="448"/>
       <c r="D10" s="469"/>
       <c r="E10" s="469"/>
       <c r="F10" s="469"/>
       <c r="G10" s="469"/>
     </row>
-    <row r="11" spans="2:7" ht="13.15">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B11" s="145" t="s">
         <v>320</v>
       </c>
@@ -19456,7 +19467,7 @@
       <c r="F11" s="469"/>
       <c r="G11" s="469"/>
     </row>
-    <row r="12" spans="2:7">
+    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="114" t="s">
         <v>121</v>
       </c>
@@ -19469,7 +19480,7 @@
       <c r="F12" s="469"/>
       <c r="G12" s="469"/>
     </row>
-    <row r="13" spans="2:7">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B13" s="135" t="s">
         <v>127</v>
       </c>
@@ -19482,7 +19493,7 @@
       <c r="F13" s="469"/>
       <c r="G13" s="469"/>
     </row>
-    <row r="14" spans="2:7">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B14" s="97" t="s">
         <v>63</v>
       </c>
@@ -19495,7 +19506,7 @@
       <c r="F14" s="469"/>
       <c r="G14" s="469"/>
     </row>
-    <row r="16" spans="2:7" ht="13.9">
+    <row r="16" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
         <v>451</v>
       </c>
@@ -19505,7 +19516,7 @@
       <c r="F16" s="35"/>
       <c r="G16" s="35"/>
     </row>
-    <row r="17" spans="2:7" ht="13.15">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B17" s="106" t="s">
         <v>126</v>
       </c>
@@ -19513,7 +19524,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="12.75" customHeight="1">
+    <row r="18" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="139" t="s">
         <v>111</v>
       </c>
@@ -19525,18 +19536,18 @@
       </c>
       <c r="F18" s="319"/>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.15">
       <c r="E19" s="319"/>
       <c r="F19" s="319"/>
     </row>
-    <row r="20" spans="2:7" ht="13.15">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B20" s="106" t="s">
         <v>448</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
-    <row r="21" spans="2:7" ht="13.15">
+    <row r="21" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B21" s="153" t="s">
         <v>434</v>
       </c>
@@ -19557,7 +19568,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B22" s="302" t="s">
         <v>443</v>
       </c>
@@ -19581,7 +19592,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B23" s="302" t="s">
         <v>435</v>
       </c>
@@ -19604,7 +19615,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B24" s="302" t="s">
         <v>444</v>
       </c>
@@ -19627,7 +19638,7 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B25" s="141" t="s">
         <v>449</v>
       </c>
@@ -19641,12 +19652,12 @@
       </c>
       <c r="G25" s="149"/>
     </row>
-    <row r="27" spans="2:7" ht="13.15">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B27" s="106" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="13.15">
+    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B28" s="153" t="s">
         <v>434</v>
       </c>
@@ -19667,7 +19678,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B29" s="302" t="s">
         <v>442</v>
       </c>
@@ -19690,7 +19701,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B30" s="315" t="s">
         <v>445</v>
       </c>
@@ -19713,16 +19724,16 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.15">
       <c r="E31" s="329"/>
       <c r="F31" s="329"/>
     </row>
-    <row r="32" spans="2:7" ht="13.15">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B32" s="145" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="33" spans="2:7">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B33" s="97" t="s">
         <v>456</v>
       </c>
@@ -19742,7 +19753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:7">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B34" s="97" t="s">
         <v>233</v>
       </c>
@@ -19762,7 +19773,7 @@
         <v>0.132879388946781</v>
       </c>
     </row>
-    <row r="35" spans="2:7">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B35" s="97" t="s">
         <v>432</v>
       </c>
@@ -19782,7 +19793,7 @@
         <v>-4.2866666015237087E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:7">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B36" s="97" t="s">
         <v>433</v>
       </c>
@@ -19801,7 +19812,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="13.9">
+    <row r="38" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B38" s="34" t="s">
         <v>409</v>
       </c>
@@ -19811,7 +19822,7 @@
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
     </row>
-    <row r="39" spans="2:7" ht="13.15">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
         <v>1-stage DCF</v>
@@ -19820,7 +19831,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="2:7">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B40" t="s">
         <v>548</v>
       </c>
@@ -19832,7 +19843,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="41" spans="2:7">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B41" s="97" t="s">
         <v>398</v>
       </c>
@@ -19842,7 +19853,7 @@
       </c>
       <c r="E41" s="97"/>
     </row>
-    <row r="43" spans="2:7" ht="13.9">
+    <row r="43" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B43" s="34" t="s">
         <v>276</v>
       </c>
@@ -19852,7 +19863,7 @@
       <c r="F43" s="35"/>
       <c r="G43" s="35"/>
     </row>
-    <row r="44" spans="2:7" ht="13.15">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B44" s="106" t="s">
         <v>249</v>
       </c>
@@ -19860,7 +19871,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="2:7">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B45" s="139" t="s">
         <v>111</v>
       </c>
@@ -19873,7 +19884,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="46" spans="2:7">
+    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B46" s="114" t="s">
         <v>112</v>
       </c>
@@ -19885,7 +19896,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="47" spans="2:7">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B47" s="97" t="s">
         <v>96</v>
       </c>
@@ -19901,7 +19912,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="49" spans="2:7" ht="13.15">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B49" s="106" t="s">
         <v>277</v>
       </c>
@@ -19913,7 +19924,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="2:7">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B50" s="97" t="s">
         <v>250</v>
       </c>
@@ -19923,7 +19934,7 @@
       </c>
       <c r="E50" s="126"/>
     </row>
-    <row r="51" spans="2:7">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B51" s="97" t="s">
         <v>246</v>
       </c>
@@ -19935,7 +19946,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="2:7">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B52" s="97" t="s">
         <v>245</v>
       </c>
@@ -19945,7 +19956,7 @@
       </c>
       <c r="E52" s="221"/>
     </row>
-    <row r="53" spans="2:7">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B53" s="97" t="s">
         <v>237</v>
       </c>
@@ -19961,7 +19972,7 @@
         <v>0.10477949826246805</v>
       </c>
     </row>
-    <row r="55" spans="2:7" ht="13.9">
+    <row r="55" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B55" s="34" t="s">
         <v>107</v>
       </c>
@@ -19971,12 +19982,12 @@
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="2:7" ht="13.15">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B56" s="106" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="2:7">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B57" s="220" t="s">
         <v>248</v>
       </c>
@@ -19986,7 +19997,7 @@
       </c>
       <c r="D57" s="126"/>
     </row>
-    <row r="58" spans="2:7">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B58" s="97" t="s">
         <v>331</v>
       </c>
@@ -19999,13 +20010,13 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="60" spans="2:7" ht="13.15">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B60" s="106" t="s">
         <v>471</v>
       </c>
       <c r="E60" s="413"/>
     </row>
-    <row r="61" spans="2:7" ht="13.15">
+    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B61" s="153" t="s">
         <v>460</v>
       </c>
@@ -20026,7 +20037,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="62" spans="2:7" ht="13.15">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B62" s="302" t="s">
         <v>311</v>
       </c>
@@ -20051,7 +20062,7 @@
         <v>0.52795340583818939</v>
       </c>
     </row>
-    <row r="63" spans="2:7" ht="13.15">
+    <row r="63" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B63" s="302" t="s">
         <v>312</v>
       </c>
@@ -20076,7 +20087,7 @@
         <v>0.40365495727218781</v>
       </c>
     </row>
-    <row r="65" spans="2:7" ht="13.15">
+    <row r="65" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B65" s="153" t="s">
         <v>461</v>
       </c>
@@ -20097,7 +20108,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="66" spans="2:7" ht="13.15">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B66" s="302" t="s">
         <v>314</v>
       </c>
@@ -20122,7 +20133,7 @@
         <v>0.15350815382753724</v>
       </c>
     </row>
-    <row r="67" spans="2:7" ht="13.15">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B67" s="302" t="s">
         <v>313</v>
       </c>
@@ -20163,7 +20174,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:J167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="343" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="343" customWidth="1"/>
@@ -20172,7 +20183,7 @@
     <col min="7" max="16384" width="9" style="343"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="345" t="s">
         <v>332</v>
       </c>
@@ -20186,7 +20197,7 @@
       <c r="I2" s="346"/>
       <c r="J2" s="346"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="E3" s="435" t="s">
         <v>539</v>
       </c>
@@ -20195,7 +20206,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B4" s="422" t="s">
         <v>531</v>
       </c>
@@ -20212,7 +20223,7 @@
         <v>CN</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B5" s="343" t="s">
         <v>362</v>
       </c>
@@ -20228,7 +20239,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B6" s="350" t="s">
         <v>334</v>
       </c>
@@ -20238,7 +20249,7 @@
       </c>
       <c r="E6" s="354"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B7" s="343" t="s">
         <v>364</v>
       </c>
@@ -20249,7 +20260,7 @@
       <c r="D7" s="354"/>
       <c r="E7" s="354"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B8" s="351" t="s">
         <v>363</v>
       </c>
@@ -20258,7 +20269,7 @@
         <v>116.25</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B9" s="351" t="s">
         <v>359</v>
       </c>
@@ -20267,7 +20278,7 @@
         <v>1471941963</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B10" s="351" t="s">
         <v>365</v>
       </c>
@@ -20283,27 +20294,27 @@
         <v>0.132879388946781</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="D11" s="349"/>
       <c r="E11" s="349"/>
     </row>
-    <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+    <row r="12" spans="1:10" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B14" s="347" t="s">
         <v>368</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B15" s="343" t="s">
         <v>335</v>
       </c>
@@ -20319,7 +20330,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B16" s="343" t="s">
         <v>336</v>
       </c>
@@ -20335,7 +20346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B17" s="343" t="s">
         <v>532</v>
       </c>
@@ -20351,7 +20362,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B18" s="343" t="str">
         <f>"预期股权价值 ("&amp;C7&amp;") :"</f>
         <v>预期股权价值 (CNY) :</v>
@@ -20368,7 +20379,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B19" s="350" t="s">
         <v>333</v>
       </c>
@@ -20384,11 +20395,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="D20" s="349"/>
       <c r="E20" s="349"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B21" s="347" t="s">
         <v>491</v>
       </c>
@@ -20404,7 +20415,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B22" s="343" t="s">
         <v>338</v>
       </c>
@@ -20420,7 +20431,7 @@
         <v>0.32950289523458665</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B23" s="343" t="s">
         <v>339</v>
       </c>
@@ -20436,7 +20447,7 @@
         <v>0.22621703288100403</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B24" s="343" t="s">
         <v>341</v>
       </c>
@@ -20452,7 +20463,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B25" s="343" t="s">
         <v>340</v>
       </c>
@@ -20468,7 +20479,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="13.9">
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A27" s="345" t="s">
         <v>343</v>
       </c>
@@ -20478,25 +20489,25 @@
       <c r="E27" s="345"/>
       <c r="F27" s="345"/>
     </row>
-    <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B29" s="471" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="472" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B32" s="369" t="s">
         <v>369</v>
       </c>
@@ -20505,7 +20516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="470" t="s">
         <v>498</v>
       </c>
@@ -20514,7 +20525,7 @@
       <c r="E33" s="470"/>
       <c r="F33" s="470"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" s="372" t="s">
         <v>197</v>
       </c>
@@ -20527,11 +20538,11 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" s="372"/>
       <c r="C35" s="374"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="470" t="s">
         <v>499</v>
       </c>
@@ -20540,7 +20551,7 @@
       <c r="E36" s="470"/>
       <c r="F36" s="470"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" s="372" t="s">
         <v>199</v>
       </c>
@@ -20553,7 +20564,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="375" t="s">
         <v>200</v>
       </c>
@@ -20566,7 +20577,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40" s="470" t="s">
         <v>500</v>
       </c>
@@ -20575,7 +20586,7 @@
       <c r="E40" s="470"/>
       <c r="F40" s="470"/>
     </row>
-    <row r="41" spans="2:6">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="372" t="s">
         <v>202</v>
       </c>
@@ -20588,7 +20599,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B43" s="470" t="s">
         <v>501</v>
       </c>
@@ -20597,7 +20608,7 @@
       <c r="E43" s="470"/>
       <c r="F43" s="470"/>
     </row>
-    <row r="44" spans="2:6">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B44" s="372" t="s">
         <v>267</v>
       </c>
@@ -20612,7 +20623,7 @@
       <c r="E44" s="371"/>
       <c r="F44" s="371"/>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45" s="372" t="s">
         <v>268</v>
       </c>
@@ -20627,7 +20638,7 @@
       <c r="E45" s="371"/>
       <c r="F45" s="371"/>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="372" t="s">
         <v>203</v>
       </c>
@@ -20640,12 +20651,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B48" s="343" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B49" s="372" t="s">
         <v>223</v>
       </c>
@@ -20658,7 +20669,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51" s="470" t="s">
         <v>503</v>
       </c>
@@ -20667,7 +20678,7 @@
       <c r="E51" s="470"/>
       <c r="F51" s="470"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="372" t="s">
         <v>494</v>
       </c>
@@ -20680,16 +20691,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
-    </row>
-    <row r="55" spans="2:6">
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B55" s="372" t="s">
         <v>207</v>
       </c>
@@ -20702,25 +20713,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
-    </row>
-    <row r="60" spans="2:6">
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B60" s="372" t="s">
         <v>370</v>
       </c>
@@ -20733,7 +20744,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B61" s="372" t="s">
         <v>213</v>
       </c>
@@ -20746,7 +20757,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B62" s="377" t="s">
         <v>302</v>
       </c>
@@ -20756,7 +20767,7 @@
       </c>
       <c r="F62" s="379"/>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B63" s="377" t="s">
         <v>330</v>
       </c>
@@ -20772,7 +20783,7 @@
         <v>0.51281220823452245</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B65" s="369" t="s">
         <v>374</v>
       </c>
@@ -20783,7 +20794,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B66" s="372" t="s">
         <v>324</v>
       </c>
@@ -20796,7 +20807,7 @@
         <v>0.37652309539416257</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B67" s="382" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -20810,7 +20821,7 @@
         <v>0.563411673135921</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B68" s="382" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -20824,7 +20835,7 @@
         <v>0.44445275381950455</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B69" s="382" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -20838,7 +20849,7 @@
         <v>1.5036272168761813</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="13.9">
+    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A71" s="345" t="s">
         <v>474</v>
       </c>
@@ -20848,43 +20859,43 @@
       <c r="E71" s="345"/>
       <c r="F71" s="345"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="385"/>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B74" s="472" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
-    </row>
-    <row r="76" spans="1:6">
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B76" s="369" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B77" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B78" s="343" t="s">
         <v>215</v>
       </c>
@@ -20897,7 +20908,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B79" s="372" t="s">
         <v>234</v>
       </c>
@@ -20910,7 +20921,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B80" s="382" t="s">
         <v>308</v>
       </c>
@@ -20919,7 +20930,7 @@
         <v>5.8904840599867017E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B81" s="382" t="s">
         <v>310</v>
       </c>
@@ -20928,12 +20939,12 @@
         <v>0.15503078912543219</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B83" s="343" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B84" s="343" t="s">
         <v>224</v>
       </c>
@@ -20946,7 +20957,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B85" s="382" t="s">
         <v>479</v>
       </c>
@@ -20959,7 +20970,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B86" s="372" t="s">
         <v>235</v>
       </c>
@@ -20972,12 +20983,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B88" s="343" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B89" s="343" t="s">
         <v>217</v>
       </c>
@@ -20990,7 +21001,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B90" s="372" t="s">
         <v>236</v>
       </c>
@@ -21003,7 +21014,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B92" s="372" t="s">
         <v>478</v>
       </c>
@@ -21016,7 +21027,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="13.9">
+    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A94" s="345" t="s">
         <v>480</v>
       </c>
@@ -21026,49 +21037,49 @@
       <c r="E94" s="345"/>
       <c r="F94" s="345"/>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="385"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
-    </row>
-    <row r="97" spans="1:6">
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
-    </row>
-    <row r="98" spans="1:6">
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
-    </row>
-    <row r="99" spans="1:6">
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="385"/>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="385"/>
       <c r="B100" s="369" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="385"/>
       <c r="B101" s="372" t="s">
         <v>212</v>
@@ -21078,7 +21089,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="385"/>
       <c r="B102" s="382" t="s">
         <v>317</v>
@@ -21088,7 +21099,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="385"/>
       <c r="B103" s="382" t="s">
         <v>316</v>
@@ -21098,7 +21109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
         <v>532</v>
@@ -21107,47 +21118,47 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="385"/>
       <c r="C105" s="392"/>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="385"/>
       <c r="B106" s="393" t="s">
         <v>373</v>
       </c>
       <c r="C106" s="392"/>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
-    </row>
-    <row r="108" spans="1:6">
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
-    </row>
-    <row r="109" spans="1:6">
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="385"/>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="385"/>
       <c r="B110" s="369" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="385"/>
       <c r="B111" s="375" t="s">
         <v>484</v>
@@ -21161,7 +21172,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="385"/>
       <c r="B112" s="372" t="s">
         <v>375</v>
@@ -21175,29 +21186,29 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="385"/>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="385"/>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="385"/>
       <c r="B116" s="369" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="385"/>
       <c r="B117" s="342" t="s">
         <v>376</v>
@@ -21215,7 +21226,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="385"/>
       <c r="B118" s="395" t="str">
         <f>DCF!B90</f>
@@ -21238,7 +21249,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="385"/>
       <c r="B119" s="400" t="str">
         <f>DCF!B91</f>
@@ -21261,7 +21272,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B120" s="400" t="str">
         <f>DCF!B92</f>
         <v>Base</v>
@@ -21283,7 +21294,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B121" s="400" t="str">
         <f>DCF!B93</f>
         <v>Pessimistic</v>
@@ -21305,7 +21316,7 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B122" s="400" t="str">
         <f>DCF!B94</f>
         <v>Devil's advocate</v>
@@ -21327,7 +21338,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B124" s="470" t="s">
         <v>516</v>
       </c>
@@ -21336,7 +21347,7 @@
       <c r="E124" s="470"/>
       <c r="F124" s="470"/>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B125" s="372" t="s">
         <v>218</v>
       </c>
@@ -21349,16 +21360,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B127" s="475" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
-    </row>
-    <row r="129" spans="1:6" ht="13.9">
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
+    </row>
+    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A129" s="345" t="s">
         <v>490</v>
       </c>
@@ -21368,30 +21379,30 @@
       <c r="E129" s="345"/>
       <c r="F129" s="345"/>
     </row>
-    <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B131" s="476" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B132" s="471" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B134" s="369" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B135" s="343" t="s">
         <v>380</v>
       </c>
@@ -21400,7 +21411,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B136" s="343" t="s">
         <v>381</v>
       </c>
@@ -21413,14 +21424,14 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B138" s="369" t="s">
         <v>491</v>
       </c>
       <c r="C138" s="407"/>
       <c r="D138" s="407"/>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B139" s="340" t="s">
         <v>460</v>
       </c>
@@ -21439,7 +21450,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B140" s="408" t="s">
         <v>311</v>
       </c>
@@ -21460,7 +21471,7 @@
         <v>0.32950289523458665</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B141" s="408" t="s">
         <v>312</v>
       </c>
@@ -21481,7 +21492,7 @@
         <v>0.22621703288100403</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B143" s="340" t="s">
         <v>461</v>
       </c>
@@ -21500,7 +21511,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B144" s="408" t="s">
         <v>314</v>
       </c>
@@ -21521,7 +21532,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B145" s="408" t="s">
         <v>313</v>
       </c>
@@ -21542,7 +21553,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="13.9">
+    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A147" s="345" t="s">
         <v>473</v>
       </c>
@@ -21552,50 +21563,50 @@
       <c r="E147" s="345"/>
       <c r="F147" s="345"/>
     </row>
-    <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B149" s="477" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B151" s="369" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B152" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
-    </row>
-    <row r="153" spans="1:6">
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B153" s="412" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B154" s="412" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B155" s="412" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B157" s="343" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="24.5" customHeight="1">
+    <row r="158" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B158" s="470" t="s">
         <v>437</v>
       </c>
@@ -21604,57 +21615,60 @@
       <c r="E158" s="470"/>
       <c r="F158" s="470"/>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B160" s="343" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+    <row r="161" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B161" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
-    </row>
-    <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
+    </row>
+    <row r="162" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B162" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
-    </row>
-    <row r="164" spans="2:6">
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B164" s="343" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="165" spans="2:6">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B165" s="412" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B166" s="412" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B167" s="412" t="s">
         <v>390</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21669,15 +21683,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C986D875-59CB-DD40-8B7B-7A7679246570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFF2F1D-A5F9-41C7-893A-35C7C7E48E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -39,17 +39,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -3280,27 +3269,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="19">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.00\x"/>
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="171" formatCode="#,##0_ "/>
-    <numFmt numFmtId="172" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="173" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="174" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="175" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="176" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="177" formatCode="0.000_ "/>
-    <numFmt numFmtId="178" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.0\x"/>
-    <numFmt numFmtId="180" formatCode="0\x"/>
-    <numFmt numFmtId="181" formatCode="0.000000000000000%"/>
-    <numFmt numFmtId="182" formatCode="#,##0_);\(#,##0\);0;@"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="170" formatCode="#,##0_ "/>
+    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="178" formatCode="0.0\x"/>
+    <numFmt numFmtId="179" formatCode="0\x"/>
+    <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="72" x14ac:knownFonts="1">
+  <fonts count="72">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4052,7 +4041,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4094,17 +4083,17 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4113,7 +4102,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4187,10 +4176,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4201,7 +4190,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4239,7 +4228,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4249,7 +4238,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4260,19 +4249,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4280,8 +4269,8 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4304,29 +4293,29 @@
     </xf>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4343,15 +4332,15 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4362,11 +4351,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4427,14 +4416,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4447,7 +4436,7 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4484,7 +4473,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4501,7 +4490,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4547,7 +4536,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4562,13 +4551,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4584,53 +4573,53 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="182" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4647,7 +4636,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -4660,21 +4649,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="182" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4684,14 +4673,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4700,8 +4689,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4713,7 +4702,7 @@
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4721,7 +4710,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4760,7 +4749,7 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4774,39 +4763,39 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="174" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4817,7 +4806,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4828,10 +4817,10 @@
     <xf numFmtId="9" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4840,7 +4829,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4853,7 +4842,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4862,8 +4851,8 @@
     <xf numFmtId="40" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4871,10 +4860,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4883,10 +4872,10 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4903,16 +4892,16 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4933,7 +4922,7 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4951,7 +4940,7 @@
     <xf numFmtId="40" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4961,10 +4950,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4979,7 +4968,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4993,34 +4982,34 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5030,30 +5019,30 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5335,7 +5324,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:I167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -5344,7 +5333,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="13.9">
       <c r="A2" s="200" t="s">
         <v>225</v>
       </c>
@@ -5357,7 +5346,7 @@
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9">
       <c r="E3" s="428" t="s">
         <v>535</v>
       </c>
@@ -5365,7 +5354,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="421" t="s">
         <v>530</v>
       </c>
@@ -5379,7 +5368,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
         <v>347</v>
       </c>
@@ -5393,7 +5382,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9">
       <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
@@ -5403,7 +5392,7 @@
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
         <v>349</v>
       </c>
@@ -5413,16 +5402,16 @@
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>116.25</v>
+        <v>110.5</v>
       </c>
       <c r="E8" s="32"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
         <v>344</v>
       </c>
@@ -5430,43 +5419,43 @@
         <v>1471941963</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
         <v>350</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>171113.25319875</v>
+        <v>162649.5869115</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.132879388946781</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+        <v>0.15281305363396264</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="460" t="s">
+    <row r="12" spans="1:9" ht="24.5" customHeight="1">
+      <c r="B12" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
         <v>1-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:9">
       <c r="B15" s="1" t="s">
         <v>318</v>
       </c>
@@ -5481,7 +5470,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:9">
       <c r="B16" s="1" t="s">
         <v>319</v>
       </c>
@@ -5495,7 +5484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
         <v>529</v>
       </c>
@@ -5509,7 +5498,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6">
       <c r="B18" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C7&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -5525,7 +5514,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
         <v>275</v>
       </c>
@@ -5541,11 +5530,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6">
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
         <v>402</v>
       </c>
@@ -5560,7 +5549,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:6">
       <c r="B22" s="1" t="s">
         <v>311</v>
       </c>
@@ -5575,7 +5564,7 @@
         <v>0.32950289523458665</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:6">
       <c r="B23" s="1" t="s">
         <v>312</v>
       </c>
@@ -5590,7 +5579,7 @@
         <v>0.22621703288100403</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:6">
       <c r="B24" s="1" t="s">
         <v>314</v>
       </c>
@@ -5605,7 +5594,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:6">
       <c r="B25" s="1" t="s">
         <v>313</v>
       </c>
@@ -5620,11 +5609,11 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:6">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="200" t="s">
         <v>280</v>
       </c>
@@ -5634,25 +5623,25 @@
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B29" s="460" t="s">
+    <row r="29" spans="1:6">
+      <c r="B29" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="462" t="s">
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
         <v>195</v>
       </c>
@@ -5661,16 +5650,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="461" t="s">
+    <row r="33" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
+    </row>
+    <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
         <v>197</v>
       </c>
@@ -5683,20 +5672,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:6">
       <c r="B35" s="44"/>
       <c r="C35" s="73"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="461" t="s">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
+    </row>
+    <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
         <v>199</v>
       </c>
@@ -5709,7 +5698,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="49" t="s">
         <v>200</v>
       </c>
@@ -5722,16 +5711,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B40" s="461" t="s">
+    <row r="40" spans="2:6">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
+    </row>
+    <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
         <v>202</v>
       </c>
@@ -5744,16 +5733,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B43" s="461" t="s">
+    <row r="43" spans="2:6">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
+    </row>
+    <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
         <v>267</v>
       </c>
@@ -5768,7 +5757,7 @@
       <c r="E44" s="244"/>
       <c r="F44" s="244"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6">
       <c r="B45" s="44" t="s">
         <v>268</v>
       </c>
@@ -5783,7 +5772,7 @@
       <c r="E45" s="244"/>
       <c r="F45" s="244"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="44" t="s">
         <v>203</v>
       </c>
@@ -5796,12 +5785,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6">
       <c r="B48" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6">
       <c r="B49" s="44" t="s">
         <v>223</v>
       </c>
@@ -5814,16 +5803,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B51" s="461" t="s">
+    <row r="51" spans="2:6">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
+    </row>
+    <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
         <v>204</v>
       </c>
@@ -5836,8 +5825,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B54" s="461" t="s">
+    <row r="54" spans="2:6">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5845,7 +5834,7 @@
       <c r="E54" s="464"/>
       <c r="F54" s="464"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
         <v>207</v>
       </c>
@@ -5858,25 +5847,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B57" s="460" t="s">
+    <row r="57" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
-    </row>
-    <row r="58" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B58" s="460" t="s">
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
+    </row>
+    <row r="58" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
         <v>227</v>
       </c>
@@ -5889,7 +5878,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:6">
       <c r="B61" s="44" t="s">
         <v>213</v>
       </c>
@@ -5902,23 +5891,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="204" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.7028344166783808E-2</v>
+        <v>8.1036606419806506E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6">
       <c r="B63" s="204" t="s">
         <v>330</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.5550967741935488E-2</v>
+        <v>3.7400904977375568E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5928,7 +5917,7 @@
         <v>0.51281220823452245</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6">
       <c r="B65" s="192" t="s">
         <v>323</v>
       </c>
@@ -5939,7 +5928,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:6">
       <c r="B66" s="44" t="s">
         <v>324</v>
       </c>
@@ -5952,7 +5941,7 @@
         <v>0.37652309539416257</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="B67" s="229" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -5966,7 +5955,7 @@
         <v>0.563411673135921</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="229" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -5980,7 +5969,7 @@
         <v>0.44445275381950455</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="229" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -5994,7 +5983,7 @@
         <v>1.5036272168761813</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="200" t="s">
         <v>475</v>
       </c>
@@ -6004,45 +5993,45 @@
       <c r="E71" s="34"/>
       <c r="F71" s="34"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="A72" s="191"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="A75" s="191"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
         <v>215</v>
@@ -6056,7 +6045,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
         <v>234</v>
@@ -6070,7 +6059,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
         <v>308</v>
@@ -6080,7 +6069,7 @@
         <v>5.8904840599867017E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:6">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
         <v>310</v>
@@ -6090,16 +6079,16 @@
         <v>0.15503078912543219</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="A82" s="191"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
         <v>224</v>
@@ -6113,7 +6102,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
         <v>222</v>
@@ -6127,7 +6116,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
         <v>235</v>
@@ -6141,16 +6130,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="A87" s="191"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:6">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
         <v>217</v>
@@ -6164,7 +6153,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
         <v>236</v>
@@ -6178,10 +6167,10 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="A91" s="191"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
         <v>467</v>
@@ -6195,7 +6184,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="200" t="s">
         <v>468</v>
       </c>
@@ -6205,42 +6194,42 @@
       <c r="E94" s="34"/>
       <c r="F94" s="34"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6">
       <c r="A95" s="191"/>
     </row>
-    <row r="96" spans="1:6" ht="11.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B96" s="460" t="s">
+    <row r="96" spans="1:6" ht="11.75" customHeight="1">
+      <c r="B96" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
-    </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="462" t="s">
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B98" s="462" t="s">
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
-    </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
+    </row>
+    <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
         <v>465</v>
       </c>
@@ -6249,7 +6238,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="229" t="s">
         <v>317</v>
       </c>
@@ -6258,7 +6247,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="229" t="s">
         <v>316</v>
       </c>
@@ -6267,7 +6256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="44" t="s">
         <v>214</v>
       </c>
@@ -6276,36 +6265,36 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:6">
       <c r="B106" s="250" t="s">
         <v>281</v>
       </c>
       <c r="C106" s="116"/>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B107" s="460" t="s">
+    <row r="107" spans="2:6">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
-    </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B108" s="460" t="s">
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
-    </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
+    </row>
+    <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
         <v>466</v>
       </c>
@@ -6318,7 +6307,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="44" t="s">
         <v>322</v>
       </c>
@@ -6331,21 +6320,21 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B114" s="460" t="s">
+    <row r="114" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B114" s="462" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
-    </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
+    </row>
+    <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:6" ht="12.4">
       <c r="B117" s="342" t="s">
         <v>101</v>
       </c>
@@ -6362,7 +6351,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="118" spans="2:6">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
         <v>Snowball Scenario (5yrs)</v>
@@ -6384,7 +6373,7 @@
         <v>-8.5764377786937424E-3</v>
       </c>
     </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="119" spans="2:6">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
         <v>Optimistic (5yrs)</v>
@@ -6406,7 +6395,7 @@
         <v>1.7826766936537737E-2</v>
       </c>
     </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="120" spans="2:6">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
         <v>Base (5yrs)</v>
@@ -6428,7 +6417,7 @@
         <v>3.134800981224807E-2</v>
       </c>
     </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="121" spans="2:6">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
         <v>Pessimistic (5yrs)</v>
@@ -6450,7 +6439,7 @@
         <v>4.5083874550095666E-2</v>
       </c>
     </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="122" spans="2:6">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
         <v>Devil's advocate (5yrs)</v>
@@ -6472,16 +6461,16 @@
         <v>5.9035182400374427E-2</v>
       </c>
     </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B124" s="461" t="s">
+    <row r="124" spans="2:6">
+      <c r="B124" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
-    </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
+    </row>
+    <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
         <v>218</v>
       </c>
@@ -6494,7 +6483,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="2:6" ht="24.5" customHeight="1">
       <c r="B127" s="465" t="s">
         <v>356</v>
       </c>
@@ -6503,7 +6492,7 @@
       <c r="E127" s="465"/>
       <c r="F127" s="465"/>
     </row>
-    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
         <v>472</v>
       </c>
@@ -6513,30 +6502,30 @@
       <c r="E129" s="34"/>
       <c r="F129" s="34"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B131" s="463" t="s">
+    <row r="131" spans="1:6">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B132" s="460" t="s">
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
+    </row>
+    <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="B135" s="1" t="s">
         <v>221</v>
       </c>
@@ -6545,7 +6534,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="194" t="s">
         <v>220</v>
       </c>
@@ -6558,14 +6547,14 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
         <v>492</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
-    <row r="139" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="340" t="s">
         <v>460</v>
       </c>
@@ -6584,7 +6573,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="336" t="s">
         <v>311</v>
       </c>
@@ -6605,7 +6594,7 @@
         <v>0.32950289523458665</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="336" t="s">
         <v>312</v>
       </c>
@@ -6626,14 +6615,14 @@
         <v>0.22621703288100403</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="194"/>
       <c r="C142" s="194"/>
       <c r="D142" s="194"/>
       <c r="E142" s="194"/>
       <c r="F142" s="194"/>
     </row>
-    <row r="143" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="340" t="s">
         <v>461</v>
       </c>
@@ -6652,7 +6641,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:6">
       <c r="B144" s="336" t="s">
         <v>314</v>
       </c>
@@ -6673,7 +6662,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:6">
       <c r="B145" s="336" t="s">
         <v>313</v>
       </c>
@@ -6694,7 +6683,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="200" t="s">
         <v>473</v>
       </c>
@@ -6704,21 +6693,21 @@
       <c r="E147" s="34"/>
       <c r="F147" s="34"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B149" s="467" t="s">
+    <row r="149" spans="1:6">
+      <c r="B149" s="461" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
+    </row>
+    <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:6">
       <c r="B152" s="464" t="s">
         <v>293</v>
       </c>
@@ -6727,92 +6716,80 @@
       <c r="E152" s="464"/>
       <c r="F152" s="464"/>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:6">
       <c r="B154" s="196" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:6">
       <c r="B155" s="196" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:6">
       <c r="B157" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B158" s="461" t="s">
+    <row r="158" spans="1:6" ht="34.25" customHeight="1">
+      <c r="B158" s="463" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
+    </row>
+    <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B161" s="466" t="s">
+    <row r="161" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B162" s="466" t="s">
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
+    </row>
+    <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:6">
       <c r="B165" s="196" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:6">
       <c r="B166" s="196" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:6">
       <c r="B167" s="196" t="s">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6829,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6856,15 +6845,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
         <v>CNY</v>
@@ -6913,7 +6902,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>93</v>
       </c>
@@ -6929,7 +6918,7 @@
       <c r="L2" s="35"/>
       <c r="M2" s="35"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>25</v>
       </c>
@@ -6937,7 +6926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="31" t="s">
         <v>0</v>
       </c>
@@ -6957,7 +6946,7 @@
       <c r="L4" s="287"/>
       <c r="M4" s="287"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="38" t="s">
         <v>40</v>
       </c>
@@ -6979,7 +6968,7 @@
       <c r="L5" s="287"/>
       <c r="M5" s="287"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="38" t="s">
         <v>51</v>
       </c>
@@ -7001,7 +6990,7 @@
       <c r="L6" s="287"/>
       <c r="M6" s="287"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="66" t="s">
         <v>58</v>
       </c>
@@ -7021,7 +7010,7 @@
       <c r="L7" s="288"/>
       <c r="M7" s="288"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="38" t="s">
         <v>46</v>
       </c>
@@ -7041,7 +7030,7 @@
       <c r="L8" s="287"/>
       <c r="M8" s="287"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="38" t="s">
         <v>134</v>
       </c>
@@ -7057,7 +7046,7 @@
       <c r="L9" s="287"/>
       <c r="M9" s="287"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="38" t="s">
         <v>138</v>
       </c>
@@ -7073,7 +7062,7 @@
       <c r="L10" s="287"/>
       <c r="M10" s="287"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="38" t="s">
         <v>133</v>
       </c>
@@ -7089,7 +7078,7 @@
       <c r="L11" s="287"/>
       <c r="M11" s="287"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="38" t="s">
         <v>37</v>
       </c>
@@ -7109,7 +7098,7 @@
       <c r="L12" s="287"/>
       <c r="M12" s="287"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="38" t="s">
         <v>64</v>
       </c>
@@ -7129,7 +7118,7 @@
       <c r="L13" s="287"/>
       <c r="M13" s="287"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="38" t="s">
         <v>47</v>
       </c>
@@ -7149,7 +7138,7 @@
       <c r="L14" s="287"/>
       <c r="M14" s="287"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="41" t="s">
         <v>39</v>
       </c>
@@ -7169,7 +7158,7 @@
       <c r="L15" s="289"/>
       <c r="M15" s="289"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="27" t="s">
         <v>41</v>
       </c>
@@ -7189,13 +7178,13 @@
       <c r="L16" s="287"/>
       <c r="M16" s="287"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
         <v>44</v>
       </c>
@@ -7211,7 +7200,7 @@
       <c r="L19" s="287"/>
       <c r="M19" s="287"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="26" t="s">
         <v>50</v>
       </c>
@@ -7227,7 +7216,7 @@
       <c r="L20" s="287"/>
       <c r="M20" s="287"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="26" t="s">
         <v>49</v>
       </c>
@@ -7243,7 +7232,7 @@
       <c r="L21" s="287"/>
       <c r="M21" s="287"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="26" t="s">
         <v>286</v>
       </c>
@@ -7263,7 +7252,7 @@
       <c r="L22" s="287"/>
       <c r="M22" s="287"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
         <v>288</v>
       </c>
@@ -7283,7 +7272,7 @@
       <c r="L23" s="287"/>
       <c r="M23" s="287"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="26" t="s">
         <v>287</v>
       </c>
@@ -7303,7 +7292,7 @@
       <c r="L24" s="287"/>
       <c r="M24" s="287"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="23" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -7326,7 +7315,7 @@
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>26</v>
       </c>
@@ -7334,7 +7323,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="25" t="s">
         <v>22</v>
       </c>
@@ -7356,7 +7345,7 @@
       <c r="L28" s="287"/>
       <c r="M28" s="287"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="25" t="s">
         <v>30</v>
       </c>
@@ -7377,7 +7366,7 @@
       <c r="L29" s="287"/>
       <c r="M29" s="287"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
         <v>38</v>
       </c>
@@ -7398,7 +7387,7 @@
       <c r="L30" s="289"/>
       <c r="M30" s="289"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="28" t="s">
         <v>28</v>
       </c>
@@ -7419,7 +7408,7 @@
       <c r="L31" s="289"/>
       <c r="M31" s="289"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="25" t="s">
         <v>143</v>
       </c>
@@ -7440,7 +7429,7 @@
       <c r="L32" s="287"/>
       <c r="M32" s="287"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="34" t="s">
         <v>78</v>
       </c>
@@ -7456,12 +7445,12 @@
       <c r="L34" s="35"/>
       <c r="M34" s="35"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="31" t="s">
         <v>0</v>
       </c>
@@ -7510,7 +7499,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="38" t="s">
         <v>40</v>
       </c>
@@ -7559,7 +7548,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="30" t="s">
         <v>55</v>
       </c>
@@ -7608,7 +7597,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="38" t="s">
         <v>51</v>
       </c>
@@ -7657,7 +7646,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="66" t="s">
         <v>58</v>
       </c>
@@ -7706,7 +7695,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="66" t="s">
         <v>61</v>
       </c>
@@ -7755,7 +7744,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="38" t="s">
         <v>46</v>
       </c>
@@ -7804,7 +7793,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="41" t="s">
         <v>127</v>
       </c>
@@ -7853,7 +7842,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="41" t="s">
         <v>139</v>
       </c>
@@ -7902,7 +7891,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="38" t="s">
         <v>65</v>
       </c>
@@ -7951,7 +7940,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="38" t="s">
         <v>47</v>
       </c>
@@ -8000,7 +7989,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="41" t="s">
         <v>39</v>
       </c>
@@ -8049,7 +8038,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="27" t="s">
         <v>41</v>
       </c>
@@ -8098,12 +8087,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="38" t="s">
         <v>37</v>
       </c>
@@ -8152,7 +8141,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="38" t="s">
         <v>64</v>
       </c>
@@ -8201,12 +8190,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="156" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="38" t="s">
         <v>134</v>
       </c>
@@ -8255,7 +8244,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="38" t="s">
         <v>138</v>
       </c>
@@ -8304,7 +8293,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="38" t="s">
         <v>133</v>
       </c>
@@ -8353,7 +8342,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="38" t="s">
         <v>135</v>
       </c>
@@ -8402,13 +8391,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="26" t="s">
         <v>44</v>
       </c>
@@ -8457,7 +8446,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="26" t="s">
         <v>50</v>
       </c>
@@ -8506,7 +8495,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="26" t="s">
         <v>49</v>
       </c>
@@ -8555,7 +8544,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="26" t="s">
         <v>305</v>
       </c>
@@ -8604,7 +8593,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="23" t="s">
         <v>34</v>
       </c>
@@ -8653,12 +8642,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8708,7 +8697,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="30" t="s">
         <v>55</v>
       </c>
@@ -8757,7 +8746,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="77" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8807,7 +8796,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="41" t="s">
         <v>139</v>
       </c>
@@ -8856,7 +8845,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="77" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8906,7 +8895,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="34" t="s">
         <v>79</v>
       </c>
@@ -8922,13 +8911,13 @@
       <c r="L74" s="35"/>
       <c r="M74" s="35"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="25" t="s">
         <v>1</v>
       </c>
@@ -8977,7 +8966,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="90" t="s">
         <v>82</v>
       </c>
@@ -9011,7 +9000,7 @@
       <c r="L77" s="291"/>
       <c r="M77" s="291"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="90" t="s">
         <v>83</v>
       </c>
@@ -9045,7 +9034,7 @@
       <c r="L78" s="291"/>
       <c r="M78" s="291"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="25" t="s">
         <v>38</v>
       </c>
@@ -9094,7 +9083,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="25" t="s">
         <v>28</v>
       </c>
@@ -9175,7 +9164,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -9186,7 +9175,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="17" t="s">
         <v>35</v>
       </c>
@@ -9202,7 +9191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="76" t="s">
         <v>131</v>
       </c>
@@ -9213,7 +9202,7 @@
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>154</v>
       </c>
@@ -9233,7 +9222,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
@@ -9255,7 +9244,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -9276,7 +9265,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
@@ -9297,7 +9286,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>66</v>
       </c>
@@ -9318,7 +9307,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>144</v>
       </c>
@@ -9339,7 +9328,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9360,7 +9349,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -9380,7 +9369,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
@@ -9392,7 +9381,7 @@
       </c>
       <c r="H11" s="232"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="77" t="s">
         <v>69</v>
       </c>
@@ -9416,12 +9405,12 @@
         <v>32872308844.689007</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="77"/>
       <c r="G13" s="78"/>
       <c r="H13" s="19"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>153</v>
       </c>
@@ -9441,7 +9430,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>327</v>
       </c>
@@ -9461,7 +9450,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
@@ -9481,7 +9470,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>66</v>
       </c>
@@ -9501,7 +9490,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>144</v>
       </c>
@@ -9521,7 +9510,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
@@ -9543,7 +9532,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>16</v>
       </c>
@@ -9563,7 +9552,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
@@ -9583,7 +9572,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
@@ -9595,7 +9584,7 @@
       </c>
       <c r="H22" s="232"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>19</v>
       </c>
@@ -9608,7 +9597,7 @@
       </c>
       <c r="H23" s="232"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="77" t="s">
         <v>70</v>
       </c>
@@ -9632,7 +9621,7 @@
         <v>332369284.89399999</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>169</v>
       </c>
@@ -9649,7 +9638,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
@@ -9668,7 +9657,7 @@
         <v>18874553188.800007</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>4</v>
       </c>
@@ -9683,7 +9672,7 @@
       </c>
       <c r="H28" s="170"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
@@ -9702,7 +9691,7 @@
         <v>18734486685.410007</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
@@ -9718,7 +9707,7 @@
       </c>
       <c r="H30" s="170"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="77" t="s">
         <v>172</v>
       </c>
@@ -9735,7 +9724,7 @@
       </c>
       <c r="H31" s="170"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
@@ -9755,7 +9744,7 @@
         <v>42384182398.360008</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="80" t="s">
         <v>2</v>
       </c>
@@ -9766,7 +9755,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="177"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
@@ -9779,7 +9768,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>170</v>
       </c>
@@ -9798,7 +9787,7 @@
         <v>9179504268.7770004</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
@@ -9814,7 +9803,7 @@
       </c>
       <c r="H36" s="177"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
@@ -9830,7 +9819,7 @@
       </c>
       <c r="H37" s="177"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>13</v>
       </c>
@@ -9846,7 +9835,7 @@
       </c>
       <c r="H38" s="177"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
@@ -9865,7 +9854,7 @@
         <v>1000531628.572</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="77" t="s">
         <v>173</v>
       </c>
@@ -9885,7 +9874,7 @@
         <v>33204678129.583008</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>15</v>
       </c>
@@ -9905,7 +9894,7 @@
         <v>31905972294.345009</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="80" t="s">
         <v>20</v>
       </c>
@@ -9924,7 +9913,7 @@
         <v>1298705835.2379999</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="76" t="s">
         <v>92</v>
       </c>
@@ -9935,7 +9924,7 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>228</v>
       </c>
@@ -9949,7 +9938,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>230</v>
       </c>
@@ -9963,7 +9952,7 @@
       </c>
       <c r="F46" s="223"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9978,10 +9967,10 @@
       </c>
       <c r="F47" s="223"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="223"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="143" t="s">
         <v>120</v>
       </c>
@@ -9994,7 +9983,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>90</v>
       </c>
@@ -10008,7 +9997,7 @@
       </c>
       <c r="F50" s="223"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>146</v>
       </c>
@@ -10019,10 +10008,10 @@
       </c>
       <c r="F51" s="223"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="223"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="143" t="s">
         <v>119</v>
       </c>
@@ -10034,7 +10023,7 @@
       </c>
       <c r="F53" s="223"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>116</v>
       </c>
@@ -10048,7 +10037,7 @@
       </c>
       <c r="F54" s="223"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>118</v>
       </c>
@@ -10062,10 +10051,10 @@
       </c>
       <c r="F55" s="223"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="223"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="143" t="s">
         <v>145</v>
       </c>
@@ -10077,7 +10066,7 @@
       </c>
       <c r="F57" s="223"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>86</v>
       </c>
@@ -10088,7 +10077,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>89</v>
       </c>
@@ -10099,10 +10088,10 @@
       </c>
       <c r="F59" s="223"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="223"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="143" t="s">
         <v>231</v>
       </c>
@@ -10114,7 +10103,7 @@
       </c>
       <c r="F61" s="223"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>210</v>
       </c>
@@ -10130,7 +10119,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="76" t="s">
         <v>162</v>
       </c>
@@ -10141,7 +10130,7 @@
       <c r="G64" s="35"/>
       <c r="H64" s="35"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>158</v>
       </c>
@@ -10155,7 +10144,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="102" t="s">
         <v>157</v>
       </c>
@@ -10171,7 +10160,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="102" t="s">
         <v>147</v>
       </c>
@@ -10181,7 +10170,7 @@
       </c>
       <c r="F67" s="223"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="102" t="s">
         <v>151</v>
       </c>
@@ -10191,7 +10180,7 @@
       </c>
       <c r="F68" s="223"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="102" t="s">
         <v>149</v>
       </c>
@@ -10201,7 +10190,7 @@
       </c>
       <c r="F69" s="223"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="77" t="s">
         <v>158</v>
       </c>
@@ -10211,10 +10200,10 @@
       </c>
       <c r="F70" s="223"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="223"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="225" t="s">
         <v>256</v>
       </c>
@@ -10226,7 +10215,7 @@
       </c>
       <c r="F72" s="223"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="102" t="s">
         <v>255</v>
       </c>
@@ -10242,7 +10231,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="227" t="s">
         <v>259</v>
       </c>
@@ -10258,7 +10247,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="77" t="s">
         <v>258</v>
       </c>
@@ -10271,7 +10260,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="229" t="s">
         <v>260</v>
       </c>
@@ -10284,10 +10273,10 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="223"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>159</v>
       </c>
@@ -10299,7 +10288,7 @@
       </c>
       <c r="F78" s="223"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="102" t="s">
         <v>148</v>
       </c>
@@ -10313,7 +10302,7 @@
       </c>
       <c r="F79" s="223"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="102" t="s">
         <v>152</v>
       </c>
@@ -10327,7 +10316,7 @@
       </c>
       <c r="F80" s="223"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="102" t="s">
         <v>150</v>
       </c>
@@ -10341,7 +10330,7 @@
       </c>
       <c r="F81" s="223"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="77" t="s">
         <v>159</v>
       </c>
@@ -10355,7 +10344,7 @@
       </c>
       <c r="F82" s="223"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="76" t="s">
         <v>241</v>
       </c>
@@ -10366,7 +10355,7 @@
       <c r="G84" s="35"/>
       <c r="H84" s="35"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>242</v>
       </c>
@@ -10374,7 +10363,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="212" t="s">
         <v>239</v>
       </c>
@@ -10391,7 +10380,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="212" t="s">
         <v>240</v>
       </c>
@@ -10408,7 +10397,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="213" t="s">
         <v>159</v>
       </c>
@@ -10425,7 +10414,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="77" t="s">
         <v>244</v>
       </c>
@@ -10461,19 +10450,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q807"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
@@ -10530,7 +10519,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
         <v>95</v>
@@ -10553,7 +10542,7 @@
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>391</v>
@@ -10573,7 +10562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -10630,7 +10619,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>43</v>
@@ -10685,7 +10674,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
         <v>45</v>
@@ -10740,7 +10729,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>42</v>
@@ -10795,7 +10784,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
         <v>127</v>
@@ -10852,7 +10841,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
         <v>413</v>
@@ -10909,7 +10898,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>65</v>
@@ -10964,7 +10953,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
         <v>137</v>
@@ -11019,7 +11008,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>60</v>
@@ -11074,7 +11063,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
         <v>208</v>
@@ -11131,7 +11120,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
         <v>129</v>
@@ -11188,7 +11177,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -11243,7 +11232,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
         <v>396</v>
@@ -11298,7 +11287,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
         <v>49</v>
@@ -11324,7 +11313,7 @@
       <c r="P17" s="272"/>
       <c r="Q17" s="272"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
         <v>94</v>
@@ -11349,7 +11338,7 @@
       <c r="P18" s="273"/>
       <c r="Q18" s="273"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
         <v>63</v>
@@ -11406,7 +11395,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="26"/>
       <c r="C20" s="59"/>
@@ -11425,7 +11414,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
         <v>174</v>
@@ -11448,7 +11437,7 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
         <v>43</v>
@@ -11469,7 +11458,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
         <v>40</v>
@@ -11526,7 +11515,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
         <v>59</v>
@@ -11583,7 +11572,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
         <v>46</v>
@@ -11640,7 +11629,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
         <v>43</v>
@@ -11697,18 +11686,18 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="E27" s="237"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
         <v>175</v>
       </c>
       <c r="E28" s="237"/>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
         <v>40</v>
@@ -11765,7 +11754,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="65" t="str">
         <f>B24</f>
@@ -11823,7 +11812,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="26" t="str">
         <f>B25</f>
@@ -11881,7 +11870,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
         <v>43</v>
@@ -11936,18 +11925,18 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="E33" s="237"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
         <v>42</v>
       </c>
       <c r="E34" s="237"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
         <v>394</v>
@@ -12004,18 +11993,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="237"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
         <v>176</v>
       </c>
       <c r="E37" s="237"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
         <v>394</v>
@@ -12070,18 +12059,18 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="E39" s="237"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
         <v>177</v>
       </c>
       <c r="E40" s="237"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
         <v>142</v>
@@ -12139,10 +12128,10 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
         <v>178</v>
@@ -12165,14 +12154,14 @@
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
         <v>57</v>
       </c>
       <c r="E44" s="237"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
         <v>37</v>
@@ -12227,7 +12216,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
         <v>272</v>
@@ -12282,7 +12271,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
         <v>269</v>
@@ -12339,7 +12328,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
         <v>65</v>
@@ -12394,11 +12383,11 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="E49" s="237"/>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
         <v>130</v>
@@ -12408,7 +12397,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
         <v>85</v>
@@ -12432,7 +12421,7 @@
       <c r="P51" s="151"/>
       <c r="Q51" s="151"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
         <v>84</v>
@@ -12456,7 +12445,7 @@
       <c r="P52" s="151"/>
       <c r="Q52" s="151"/>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
         <v>87</v>
@@ -12511,11 +12500,11 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="E54" s="237"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
         <v>139</v>
@@ -12525,7 +12514,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
         <v>138</v>
@@ -12580,7 +12569,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
         <v>134</v>
@@ -12635,7 +12624,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
         <v>133</v>
@@ -12690,7 +12679,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
         <v>163</v>
@@ -12745,7 +12734,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
         <v>135</v>
@@ -12801,7 +12790,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
         <v>164</v>
@@ -12856,11 +12845,11 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="E62" s="237"/>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
         <v>140</v>
@@ -12870,7 +12859,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
         <v>138</v>
@@ -12895,7 +12884,7 @@
       <c r="P64" s="157"/>
       <c r="Q64" s="157"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
         <v>132</v>
@@ -12920,7 +12909,7 @@
       <c r="P65" s="157"/>
       <c r="Q65" s="157"/>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
         <v>133</v>
@@ -12945,7 +12934,7 @@
       <c r="P66" s="157"/>
       <c r="Q66" s="157"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
         <v>163</v>
@@ -12972,10 +12961,10 @@
       <c r="P67" s="157"/>
       <c r="Q67" s="157"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
         <v>181</v>
@@ -12998,7 +12987,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
         <v>185</v>
@@ -13019,7 +13008,7 @@
       <c r="P70" s="12"/>
       <c r="Q70" s="12"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
         <v>43</v>
@@ -13076,7 +13065,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
         <v>45</v>
@@ -13133,7 +13122,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
         <v>42</v>
@@ -13190,7 +13179,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
         <v>127</v>
@@ -13247,7 +13236,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
         <v>128</v>
@@ -13304,7 +13293,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
         <v>65</v>
@@ -13361,7 +13350,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
         <v>137</v>
@@ -13418,7 +13407,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>60</v>
@@ -13475,7 +13464,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="38" t="str">
         <f>B13</f>
@@ -13533,7 +13522,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
         <v>129</v>
@@ -13590,7 +13579,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
         <v>62</v>
@@ -13647,7 +13636,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>77</v>
@@ -13706,7 +13695,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
         <v>49</v>
@@ -13732,7 +13721,7 @@
       <c r="P83" s="203"/>
       <c r="Q83" s="203"/>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
         <v>94</v>
@@ -13756,7 +13745,7 @@
       <c r="P84" s="151"/>
       <c r="Q84" s="151"/>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
         <v>117</v>
@@ -13813,18 +13802,18 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="E86" s="237"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
         <v>183</v>
       </c>
       <c r="E87" s="237"/>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="B88" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13880,7 +13869,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13936,7 +13925,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
         <v>182</v>
@@ -13991,7 +13980,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
         <v>329</v>
@@ -14012,23 +14001,23 @@
       <c r="P91" s="293"/>
       <c r="Q91" s="293"/>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>328</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5550967741935488E-2</v>
+        <v>3.7400904977375568E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5550967741935488E-2</v>
+        <v>3.7400904977375568E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.1807055483870967E-2</v>
+        <v>4.3982535746606335E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14067,11 +14056,11 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="E93" s="237"/>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
         <v>81</v>
@@ -14092,7 +14081,7 @@
       <c r="P94" s="12"/>
       <c r="Q94" s="12"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
         <v>121</v>
@@ -14149,7 +14138,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
         <v>137</v>
@@ -14206,10 +14195,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
         <v>184</v>
@@ -14232,7 +14221,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
         <v>26</v>
@@ -14242,7 +14231,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="25" t="s">
         <v>1</v>
@@ -14299,7 +14288,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
         <v>179</v>
@@ -14356,7 +14345,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
         <v>180</v>
@@ -14413,7 +14402,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
         <v>38</v>
@@ -14470,7 +14459,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
         <v>28</v>
@@ -14527,11 +14516,11 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="E105" s="237"/>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
         <v>189</v>
@@ -14554,7 +14543,7 @@
       <c r="P106" s="12"/>
       <c r="Q106" s="12"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
         <v>186</v>
@@ -14611,7 +14600,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
         <v>187</v>
@@ -14668,7 +14657,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
         <v>66</v>
@@ -14695,18 +14684,18 @@
       <c r="P109" s="186"/>
       <c r="Q109" s="186"/>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="E110" s="237"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
         <v>48</v>
       </c>
       <c r="E111" s="237"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
         <v>303</v>
@@ -14760,7 +14749,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>304</v>
@@ -14815,11 +14804,11 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="E114" s="237"/>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
         <v>36</v>
@@ -14878,7 +14867,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
         <v>190</v>
@@ -14936,7 +14925,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="B117" s="7" t="s">
         <v>80</v>
       </c>
@@ -14993,7 +14982,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>88</v>
       </c>
@@ -15052,7 +15041,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
         <v>191</v>
@@ -15112,7 +15101,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="26"/>
       <c r="C120" s="59"/>
@@ -15131,7 +15120,7 @@
       <c r="P120" s="12"/>
       <c r="Q120" s="12"/>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
         <v>192</v>
@@ -15154,7 +15143,7 @@
       <c r="P121" s="35"/>
       <c r="Q121" s="35"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
         <v>141</v>
@@ -15175,7 +15164,7 @@
       <c r="P122" s="12"/>
       <c r="Q122" s="12"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="26" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -15233,25 +15222,25 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
         <v>226</v>
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.7028344166783808E-2</v>
+        <v>8.1036606419806506E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.5061503510018654E-2</v>
+        <v>7.8967418851037724E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.2595080275249566E-2</v>
+        <v>7.6372652325771603E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15290,18 +15279,18 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="B125" s="2" t="s">
         <v>306</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8882134016890995E-2</v>
+        <v>8.2986860447634189E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7660027933517631E-2</v>
+        <v>8.1701160608791165E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15340,688 +15329,688 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q11 G13:Q16 G23:Q25">
@@ -16043,16 +16032,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:U118"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="11" width="11.1640625" customWidth="1"/>
+    <col min="10" max="11" width="11.1328125" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
     <col min="13" max="13" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>52</v>
       </c>
@@ -16067,7 +16056,7 @@
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:15" ht="13.15">
       <c r="B3" s="106" t="s">
         <v>136</v>
       </c>
@@ -16082,7 +16071,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
         <v>391</v>
       </c>
@@ -16114,7 +16103,7 @@
       </c>
       <c r="J4" s="305"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:15">
       <c r="B5" s="187" t="s">
         <v>105</v>
       </c>
@@ -16142,7 +16131,7 @@
       </c>
       <c r="J5" s="305"/>
     </row>
-    <row r="6" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:15" ht="13.25" customHeight="1">
       <c r="B6" s="136" t="s">
         <v>194</v>
       </c>
@@ -16175,7 +16164,7 @@
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
     </row>
-    <row r="7" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="318" t="s">
         <v>428</v>
       </c>
@@ -16205,7 +16194,7 @@
       <c r="N7" s="304"/>
       <c r="O7" s="304"/>
     </row>
-    <row r="8" spans="2:15" ht="14" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="136" t="s">
         <v>424</v>
       </c>
@@ -16240,7 +16229,7 @@
       <c r="N8" s="304"/>
       <c r="O8" s="304"/>
     </row>
-    <row r="9" spans="2:15" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:15" ht="13.15" thickBot="1">
       <c r="B9" s="189" t="str">
         <f>"*"&amp;Thesis!E15</f>
         <v>*CNY</v>
@@ -16266,7 +16255,7 @@
       <c r="N9" s="304"/>
       <c r="O9" s="304"/>
     </row>
-    <row r="10" spans="2:15" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
         <v>425</v>
       </c>
@@ -16288,7 +16277,7 @@
       <c r="N10" s="304"/>
       <c r="O10" s="304"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="136" t="s">
         <v>423</v>
       </c>
@@ -16304,7 +16293,7 @@
       <c r="I11" s="307"/>
       <c r="J11" s="307"/>
     </row>
-    <row r="13" spans="2:15" ht="16" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
         <v>426</v>
       </c>
@@ -16319,7 +16308,7 @@
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
         <v>397</v>
       </c>
@@ -16337,7 +16326,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:15">
       <c r="B15" s="139" t="s">
         <v>419</v>
       </c>
@@ -16362,7 +16351,7 @@
       </c>
       <c r="J15" s="126"/>
     </row>
-    <row r="16" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
         <v>420</v>
       </c>
@@ -16378,7 +16367,7 @@
         <v>2.38559171477595E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="308" t="s">
         <v>547</v>
       </c>
@@ -16397,7 +16386,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="308" t="s">
         <v>421</v>
       </c>
@@ -16424,10 +16413,10 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:21">
       <c r="L19" s="275"/>
     </row>
-    <row r="20" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="121" t="s">
         <v>397</v>
       </c>
@@ -16466,7 +16455,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:21">
       <c r="A21" s="302" t="str">
         <f t="shared" ref="A21:A50" si="0">IF($C$15&lt;B21,"",IF(B21&gt;=$F$15,"II","I"))</f>
         <v>I</v>
@@ -16515,7 +16504,7 @@
         <v>12582755392.17198</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:21">
       <c r="A22" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16564,7 +16553,7 @@
         <v>12012054603.541407</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:21">
       <c r="A23" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16621,7 +16610,7 @@
       <c r="T23" s="275"/>
       <c r="U23" s="275"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:21">
       <c r="A24" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16678,7 +16667,7 @@
       <c r="T24" s="275"/>
       <c r="U24" s="275"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:21">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16735,7 +16724,7 @@
       <c r="T25" s="275"/>
       <c r="U25" s="275"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:21">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16784,7 +16773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:21">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16833,7 +16822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:21">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16882,7 +16871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:21">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16931,7 +16920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:21">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16980,7 +16969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:21">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17029,7 +17018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:21">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17078,7 +17067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:21">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17135,7 +17124,7 @@
       <c r="T33" s="275"/>
       <c r="U33" s="275"/>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:21">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17192,7 +17181,7 @@
       <c r="T34" s="275"/>
       <c r="U34" s="275"/>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:21">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17249,7 +17238,7 @@
       <c r="T35" s="275"/>
       <c r="U35" s="275"/>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:21">
       <c r="A36" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17298,7 +17287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:21">
       <c r="A37" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17347,7 +17336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:21">
       <c r="A38" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17396,7 +17385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:21">
       <c r="A39" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17445,7 +17434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:21">
       <c r="A40" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17494,7 +17483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:21">
       <c r="A41" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17543,7 +17532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:21">
       <c r="A42" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17592,7 +17581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:21">
       <c r="A43" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17641,7 +17630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:21">
       <c r="A44" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17690,7 +17679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:21">
       <c r="A45" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17739,7 +17728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:21">
       <c r="A46" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17788,7 +17777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:21">
       <c r="A47" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17845,7 +17834,7 @@
       <c r="T47" s="275"/>
       <c r="U47" s="275"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:21">
       <c r="A48" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17902,7 +17891,7 @@
       <c r="T48" s="275"/>
       <c r="U48" s="275"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:21">
       <c r="A49" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17959,7 +17948,7 @@
       <c r="T49" s="275"/>
       <c r="U49" s="275"/>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:21">
       <c r="A50" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18016,7 +18005,7 @@
       <c r="T50" s="275"/>
       <c r="U50" s="275"/>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:21">
       <c r="A51" s="315" t="s">
         <v>416</v>
       </c>
@@ -18062,7 +18051,7 @@
         <v>147029369191.0303</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:21" ht="13.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
@@ -18075,10 +18064,10 @@
         <v>204489167276.40967</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:21">
       <c r="C53" s="111"/>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:21" ht="13.15">
       <c r="B54" s="115" t="s">
         <v>108</v>
       </c>
@@ -18093,7 +18082,7 @@
       <c r="K54" s="113"/>
       <c r="L54" s="113"/>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
         <v>204489167276.40967</v>
@@ -18125,7 +18114,7 @@
       <c r="K55" s="123"/>
       <c r="L55" s="123"/>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:21" ht="13.15">
       <c r="A56" s="131">
         <v>1</v>
       </c>
@@ -18152,7 +18141,7 @@
       <c r="K56" s="295"/>
       <c r="L56" s="295"/>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:21" ht="13.15">
       <c r="A57" s="131">
         <v>2</v>
       </c>
@@ -18178,7 +18167,7 @@
       <c r="K57" s="295"/>
       <c r="L57" s="295"/>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:21" ht="13.15">
       <c r="A58" s="131">
         <v>3</v>
       </c>
@@ -18204,7 +18193,7 @@
       <c r="K58" s="295"/>
       <c r="L58" s="295"/>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:21" ht="13.15">
       <c r="A59" s="131">
         <v>4</v>
       </c>
@@ -18230,7 +18219,7 @@
       <c r="K59" s="295"/>
       <c r="L59" s="295"/>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:21" ht="13.15">
       <c r="A60" s="131">
         <v>5</v>
       </c>
@@ -18256,7 +18245,7 @@
       <c r="K60" s="295"/>
       <c r="L60" s="295"/>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:21" ht="13.15">
       <c r="A61" s="131">
         <v>6</v>
       </c>
@@ -18282,7 +18271,7 @@
       <c r="K61" s="295"/>
       <c r="L61" s="295"/>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:21" ht="13.15">
       <c r="A62" s="131">
         <v>7</v>
       </c>
@@ -18308,7 +18297,7 @@
       <c r="K62" s="295"/>
       <c r="L62" s="295"/>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:21" ht="13.15">
       <c r="A63" s="131">
         <v>8</v>
       </c>
@@ -18334,7 +18323,7 @@
       <c r="K63" s="295"/>
       <c r="L63" s="295"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:21" ht="13.15">
       <c r="A64" s="131">
         <v>9</v>
       </c>
@@ -18360,7 +18349,7 @@
       <c r="K64" s="295"/>
       <c r="L64" s="295"/>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:21" ht="13.15">
       <c r="A65" s="131">
         <v>10</v>
       </c>
@@ -18386,7 +18375,7 @@
       <c r="K65" s="295"/>
       <c r="L65" s="295"/>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:21" ht="13.15">
       <c r="A66" s="131">
         <v>15</v>
       </c>
@@ -18421,7 +18410,7 @@
       <c r="T66" s="275"/>
       <c r="U66" s="275"/>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:21" ht="13.15">
       <c r="A67" s="132">
         <v>20</v>
       </c>
@@ -18456,7 +18445,7 @@
       <c r="T67" s="275"/>
       <c r="U67" s="275"/>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:21" ht="13.15">
       <c r="A68" s="132">
         <v>25</v>
       </c>
@@ -18491,7 +18480,7 @@
       <c r="T68" s="275"/>
       <c r="U68" s="275"/>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:21" ht="13.15">
       <c r="A69" s="132">
         <v>30</v>
       </c>
@@ -18526,7 +18515,7 @@
       <c r="T69" s="275"/>
       <c r="U69" s="275"/>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:21">
       <c r="C70" s="275"/>
       <c r="D70" s="111"/>
       <c r="E70" s="111"/>
@@ -18547,7 +18536,7 @@
       <c r="T70" s="275"/>
       <c r="U70" s="275"/>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:21" ht="13.15">
       <c r="B71" s="115" t="s">
         <v>109</v>
       </c>
@@ -18571,7 +18560,7 @@
       <c r="T71" s="275"/>
       <c r="U71" s="275"/>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:21" ht="13.15">
       <c r="B72" s="124">
         <f>B55</f>
         <v>0</v>
@@ -18599,7 +18588,7 @@
       <c r="K72" s="124"/>
       <c r="L72" s="124"/>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:21" ht="13.15">
       <c r="A73" s="131">
         <v>0</v>
       </c>
@@ -18630,7 +18619,7 @@
       <c r="K73" s="296"/>
       <c r="L73" s="296"/>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:21" ht="13.15">
       <c r="A74" s="131">
         <v>1</v>
       </c>
@@ -18661,7 +18650,7 @@
       <c r="K74" s="296"/>
       <c r="L74" s="296"/>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:21" ht="13.15">
       <c r="A75" s="131">
         <v>2</v>
       </c>
@@ -18692,7 +18681,7 @@
       <c r="K75" s="296"/>
       <c r="L75" s="296"/>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:21" ht="13.15">
       <c r="A76" s="131">
         <v>3</v>
       </c>
@@ -18723,7 +18712,7 @@
       <c r="K76" s="296"/>
       <c r="L76" s="296"/>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:21" ht="13.15">
       <c r="A77" s="131">
         <v>4</v>
       </c>
@@ -18754,7 +18743,7 @@
       <c r="K77" s="296"/>
       <c r="L77" s="296"/>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:21" ht="13.15">
       <c r="A78" s="131">
         <v>5</v>
       </c>
@@ -18785,7 +18774,7 @@
       <c r="K78" s="296"/>
       <c r="L78" s="296"/>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:21" ht="13.15">
       <c r="A79" s="131">
         <v>6</v>
       </c>
@@ -18816,7 +18805,7 @@
       <c r="K79" s="296"/>
       <c r="L79" s="296"/>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:21" ht="13.15">
       <c r="A80" s="131">
         <f t="shared" ref="A80" si="12">A62</f>
         <v>7</v>
@@ -18848,7 +18837,7 @@
       <c r="K80" s="296"/>
       <c r="L80" s="296"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:12" ht="13.15">
       <c r="A81" s="131">
         <v>8</v>
       </c>
@@ -18879,7 +18868,7 @@
       <c r="K81" s="296"/>
       <c r="L81" s="296"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:12" ht="13.15">
       <c r="A82" s="131">
         <f t="shared" ref="A82" si="13">A64</f>
         <v>9</v>
@@ -18911,7 +18900,7 @@
       <c r="K82" s="296"/>
       <c r="L82" s="296"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:12" ht="13.15">
       <c r="A83" s="131">
         <f t="shared" ref="A83:A87" si="14">A65</f>
         <v>10</v>
@@ -18943,7 +18932,7 @@
       <c r="K83" s="296"/>
       <c r="L83" s="296"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:12" ht="13.15">
       <c r="A84" s="131">
         <f t="shared" si="14"/>
         <v>15</v>
@@ -18975,7 +18964,7 @@
       <c r="K84" s="296"/>
       <c r="L84" s="296"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:12" ht="13.15">
       <c r="A85" s="132">
         <f t="shared" si="14"/>
         <v>20</v>
@@ -19007,7 +18996,7 @@
       <c r="K85" s="296"/>
       <c r="L85" s="296"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:12" ht="13.15">
       <c r="A86" s="132">
         <f t="shared" si="14"/>
         <v>25</v>
@@ -19039,7 +19028,7 @@
       <c r="K86" s="296"/>
       <c r="L86" s="296"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:12" ht="13.15">
       <c r="A87" s="132">
         <f t="shared" si="14"/>
         <v>30</v>
@@ -19071,7 +19060,7 @@
       <c r="K87" s="296"/>
       <c r="L87" s="296"/>
     </row>
-    <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="13.15">
       <c r="B89" s="153" t="s">
         <v>101</v>
       </c>
@@ -19094,7 +19083,7 @@
       <c r="K89" s="323"/>
       <c r="L89" s="323"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:12">
       <c r="B90" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
@@ -19122,7 +19111,7 @@
       <c r="K90" s="297"/>
       <c r="L90" s="297"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:12">
       <c r="B91" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
@@ -19150,7 +19139,7 @@
       <c r="K91" s="297"/>
       <c r="L91" s="297"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:12">
       <c r="B92" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
@@ -19178,7 +19167,7 @@
       <c r="K92" s="297"/>
       <c r="L92" s="297"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:12">
       <c r="B93" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
@@ -19206,7 +19195,7 @@
       <c r="K93" s="297"/>
       <c r="L93" s="297"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:12">
       <c r="B94" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
@@ -19234,7 +19223,7 @@
       <c r="K94" s="297"/>
       <c r="L94" s="297"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:12">
       <c r="B95" s="141"/>
       <c r="C95" s="141"/>
       <c r="D95" s="141"/>
@@ -19247,16 +19236,16 @@
       <c r="K95" s="142"/>
       <c r="L95" s="142"/>
     </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:3">
       <c r="C105" s="112"/>
     </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="106" spans="3:3">
       <c r="C106" s="112"/>
     </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="107" spans="3:3">
       <c r="C107" s="112"/>
     </row>
-    <row r="114" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="114" spans="3:21">
       <c r="C114" s="275"/>
       <c r="M114" s="275"/>
       <c r="N114" s="275"/>
@@ -19268,7 +19257,7 @@
       <c r="T114" s="275"/>
       <c r="U114" s="275"/>
     </row>
-    <row r="115" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="115" spans="3:21">
       <c r="C115" s="275"/>
       <c r="M115" s="275"/>
       <c r="N115" s="275"/>
@@ -19280,7 +19269,7 @@
       <c r="T115" s="275"/>
       <c r="U115" s="275"/>
     </row>
-    <row r="116" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="116" spans="3:21">
       <c r="C116" s="275"/>
       <c r="M116" s="275"/>
       <c r="N116" s="275"/>
@@ -19292,7 +19281,7 @@
       <c r="T116" s="275"/>
       <c r="U116" s="275"/>
     </row>
-    <row r="117" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="117" spans="3:21">
       <c r="C117" s="275"/>
       <c r="M117" s="275"/>
       <c r="N117" s="275"/>
@@ -19304,7 +19293,7 @@
       <c r="T117" s="275"/>
       <c r="U117" s="275"/>
     </row>
-    <row r="118" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="118" spans="3:21">
       <c r="C118" s="275"/>
       <c r="M118" s="275"/>
       <c r="N118" s="275"/>
@@ -19344,14 +19333,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:G67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>122</v>
       </c>
@@ -19361,7 +19350,7 @@
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:7" ht="13.15">
       <c r="B3" s="145" t="s">
         <v>125</v>
       </c>
@@ -19370,7 +19359,7 @@
       </c>
       <c r="E3" s="97"/>
     </row>
-    <row r="4" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:7" ht="12.75" customHeight="1">
       <c r="B4" s="139" t="s">
         <v>123</v>
       </c>
@@ -19391,14 +19380,14 @@
       <c r="F4" s="469"/>
       <c r="G4" s="469"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:7">
       <c r="C5" s="445"/>
       <c r="D5" s="469"/>
       <c r="E5" s="469"/>
       <c r="F5" s="469"/>
       <c r="G5" s="469"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
         <v>91</v>
       </c>
@@ -19411,7 +19400,7 @@
       <c r="F6" s="469"/>
       <c r="G6" s="469"/>
     </row>
-    <row r="7" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
         <v>232</v>
       </c>
@@ -19424,7 +19413,7 @@
       <c r="F7" s="469"/>
       <c r="G7" s="469"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
         <v>63</v>
       </c>
@@ -19437,7 +19426,7 @@
       <c r="F8" s="469"/>
       <c r="G8" s="469"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
         <v>54</v>
       </c>
@@ -19450,14 +19439,14 @@
       <c r="F9" s="469"/>
       <c r="G9" s="469"/>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:7">
       <c r="C10" s="448"/>
       <c r="D10" s="469"/>
       <c r="E10" s="469"/>
       <c r="F10" s="469"/>
       <c r="G10" s="469"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
         <v>320</v>
       </c>
@@ -19467,7 +19456,7 @@
       <c r="F11" s="469"/>
       <c r="G11" s="469"/>
     </row>
-    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
         <v>121</v>
       </c>
@@ -19480,7 +19469,7 @@
       <c r="F12" s="469"/>
       <c r="G12" s="469"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
         <v>127</v>
       </c>
@@ -19493,7 +19482,7 @@
       <c r="F13" s="469"/>
       <c r="G13" s="469"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
         <v>63</v>
       </c>
@@ -19506,7 +19495,7 @@
       <c r="F14" s="469"/>
       <c r="G14" s="469"/>
     </row>
-    <row r="16" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
         <v>451</v>
       </c>
@@ -19516,7 +19505,7 @@
       <c r="F16" s="35"/>
       <c r="G16" s="35"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:7" ht="13.15">
       <c r="B17" s="106" t="s">
         <v>126</v>
       </c>
@@ -19524,7 +19513,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:7" ht="12.75" customHeight="1">
       <c r="B18" s="139" t="s">
         <v>111</v>
       </c>
@@ -19536,18 +19525,18 @@
       </c>
       <c r="F18" s="319"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:7">
       <c r="E19" s="319"/>
       <c r="F19" s="319"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
         <v>448</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
-    <row r="21" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="153" t="s">
         <v>434</v>
       </c>
@@ -19568,7 +19557,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:7">
       <c r="B22" s="302" t="s">
         <v>443</v>
       </c>
@@ -19592,7 +19581,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:7">
       <c r="B23" s="302" t="s">
         <v>435</v>
       </c>
@@ -19615,7 +19604,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:7">
       <c r="B24" s="302" t="s">
         <v>444</v>
       </c>
@@ -19638,7 +19627,7 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:7">
       <c r="B25" s="141" t="s">
         <v>449</v>
       </c>
@@ -19652,12 +19641,12 @@
       </c>
       <c r="G25" s="149"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="153" t="s">
         <v>434</v>
       </c>
@@ -19678,7 +19667,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:7">
       <c r="B29" s="302" t="s">
         <v>442</v>
       </c>
@@ -19701,7 +19690,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:7">
       <c r="B30" s="315" t="s">
         <v>445</v>
       </c>
@@ -19724,16 +19713,16 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:7">
       <c r="E31" s="329"/>
       <c r="F31" s="329"/>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="145" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
         <v>456</v>
       </c>
@@ -19753,13 +19742,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:7">
       <c r="B34" s="97" t="s">
         <v>233</v>
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>116.25</v>
+        <v>110.5</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19770,10 +19759,10 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.132879388946781</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.15">
+        <v>0.15281305363396264</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
         <v>432</v>
       </c>
@@ -19793,7 +19782,7 @@
         <v>-4.2866666015237087E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
         <v>433</v>
       </c>
@@ -19812,7 +19801,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
         <v>409</v>
       </c>
@@ -19822,7 +19811,7 @@
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:7" ht="13.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
         <v>1-stage DCF</v>
@@ -19831,7 +19820,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:7">
       <c r="B40" t="s">
         <v>548</v>
       </c>
@@ -19843,7 +19832,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
         <v>398</v>
       </c>
@@ -19853,7 +19842,7 @@
       </c>
       <c r="E41" s="97"/>
     </row>
-    <row r="43" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" ht="13.9">
       <c r="B43" s="34" t="s">
         <v>276</v>
       </c>
@@ -19863,7 +19852,7 @@
       <c r="F43" s="35"/>
       <c r="G43" s="35"/>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:7" ht="13.15">
       <c r="B44" s="106" t="s">
         <v>249</v>
       </c>
@@ -19871,7 +19860,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:7">
       <c r="B45" s="139" t="s">
         <v>111</v>
       </c>
@@ -19884,7 +19873,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:7">
       <c r="B46" s="114" t="s">
         <v>112</v>
       </c>
@@ -19896,7 +19885,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:7">
       <c r="B47" s="97" t="s">
         <v>96</v>
       </c>
@@ -19912,7 +19901,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:7" ht="13.15">
       <c r="B49" s="106" t="s">
         <v>277</v>
       </c>
@@ -19924,7 +19913,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:7">
       <c r="B50" s="97" t="s">
         <v>250</v>
       </c>
@@ -19934,7 +19923,7 @@
       </c>
       <c r="E50" s="126"/>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:7">
       <c r="B51" s="97" t="s">
         <v>246</v>
       </c>
@@ -19946,7 +19935,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:7">
       <c r="B52" s="97" t="s">
         <v>245</v>
       </c>
@@ -19956,7 +19945,7 @@
       </c>
       <c r="E52" s="221"/>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:7">
       <c r="B53" s="97" t="s">
         <v>237</v>
       </c>
@@ -19972,7 +19961,7 @@
         <v>0.10477949826246805</v>
       </c>
     </row>
-    <row r="55" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:7" ht="13.9">
       <c r="B55" s="34" t="s">
         <v>107</v>
       </c>
@@ -19982,12 +19971,12 @@
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:7" ht="13.15">
       <c r="B56" s="106" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:7">
       <c r="B57" s="220" t="s">
         <v>248</v>
       </c>
@@ -19997,7 +19986,7 @@
       </c>
       <c r="D57" s="126"/>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:7">
       <c r="B58" s="97" t="s">
         <v>331</v>
       </c>
@@ -20010,13 +19999,13 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
         <v>471</v>
       </c>
       <c r="E60" s="413"/>
     </row>
-    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="153" t="s">
         <v>460</v>
       </c>
@@ -20037,7 +20026,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:7" ht="13.15">
       <c r="B62" s="302" t="s">
         <v>311</v>
       </c>
@@ -20062,7 +20051,7 @@
         <v>0.52795340583818939</v>
       </c>
     </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:7" ht="13.15">
       <c r="B63" s="302" t="s">
         <v>312</v>
       </c>
@@ -20087,7 +20076,7 @@
         <v>0.40365495727218781</v>
       </c>
     </row>
-    <row r="65" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="153" t="s">
         <v>461</v>
       </c>
@@ -20108,7 +20097,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:7" ht="13.15">
       <c r="B66" s="302" t="s">
         <v>314</v>
       </c>
@@ -20133,7 +20122,7 @@
         <v>0.15350815382753724</v>
       </c>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:7" ht="13.15">
       <c r="B67" s="302" t="s">
         <v>313</v>
       </c>
@@ -20174,7 +20163,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:J167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="343" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="343" customWidth="1"/>
@@ -20183,7 +20172,7 @@
     <col min="7" max="16384" width="9" style="343"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="345" t="s">
         <v>332</v>
       </c>
@@ -20197,7 +20186,7 @@
       <c r="I2" s="346"/>
       <c r="J2" s="346"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="E3" s="435" t="s">
         <v>539</v>
       </c>
@@ -20206,7 +20195,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="B4" s="422" t="s">
         <v>531</v>
       </c>
@@ -20223,7 +20212,7 @@
         <v>CN</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="B5" s="343" t="s">
         <v>362</v>
       </c>
@@ -20239,7 +20228,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="B6" s="350" t="s">
         <v>334</v>
       </c>
@@ -20249,7 +20238,7 @@
       </c>
       <c r="E6" s="354"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="B7" s="343" t="s">
         <v>364</v>
       </c>
@@ -20260,16 +20249,16 @@
       <c r="D7" s="354"/>
       <c r="E7" s="354"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="B8" s="351" t="s">
         <v>363</v>
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>116.25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>110.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" s="351" t="s">
         <v>359</v>
       </c>
@@ -20278,43 +20267,43 @@
         <v>1471941963</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="B10" s="351" t="s">
         <v>365</v>
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>171113.25319875</v>
+        <v>162649.5869115</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.132879388946781</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.15281305363396264</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="D11" s="349"/>
       <c r="E11" s="349"/>
     </row>
-    <row r="12" spans="1:10" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="471" t="s">
+    <row r="12" spans="1:10" ht="24.5" customHeight="1">
+      <c r="B12" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
         <v>368</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="B15" s="343" t="s">
         <v>335</v>
       </c>
@@ -20330,7 +20319,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="B16" s="343" t="s">
         <v>336</v>
       </c>
@@ -20346,7 +20335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="B17" s="343" t="s">
         <v>532</v>
       </c>
@@ -20362,7 +20351,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="B18" s="343" t="str">
         <f>"预期股权价值 ("&amp;C7&amp;") :"</f>
         <v>预期股权价值 (CNY) :</v>
@@ -20379,7 +20368,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="B19" s="350" t="s">
         <v>333</v>
       </c>
@@ -20395,11 +20384,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="D20" s="349"/>
       <c r="E20" s="349"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="B21" s="347" t="s">
         <v>491</v>
       </c>
@@ -20415,7 +20404,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="B22" s="343" t="s">
         <v>338</v>
       </c>
@@ -20431,7 +20420,7 @@
         <v>0.32950289523458665</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="B23" s="343" t="s">
         <v>339</v>
       </c>
@@ -20447,7 +20436,7 @@
         <v>0.22621703288100403</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="B24" s="343" t="s">
         <v>341</v>
       </c>
@@ -20463,7 +20452,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="B25" s="343" t="s">
         <v>340</v>
       </c>
@@ -20479,7 +20468,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="345" t="s">
         <v>343</v>
       </c>
@@ -20489,25 +20478,25 @@
       <c r="E27" s="345"/>
       <c r="F27" s="345"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="471" t="s">
+    <row r="29" spans="1:6">
+      <c r="B29" s="474" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="472" t="s">
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="477" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
         <v>369</v>
       </c>
@@ -20516,7 +20505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:6">
       <c r="B33" s="470" t="s">
         <v>498</v>
       </c>
@@ -20525,7 +20514,7 @@
       <c r="E33" s="470"/>
       <c r="F33" s="470"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:6">
       <c r="B34" s="372" t="s">
         <v>197</v>
       </c>
@@ -20538,11 +20527,11 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:6">
       <c r="B35" s="372"/>
       <c r="C35" s="374"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="470" t="s">
         <v>499</v>
       </c>
@@ -20551,7 +20540,7 @@
       <c r="E36" s="470"/>
       <c r="F36" s="470"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:6">
       <c r="B37" s="372" t="s">
         <v>199</v>
       </c>
@@ -20564,7 +20553,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:6">
       <c r="B38" s="375" t="s">
         <v>200</v>
       </c>
@@ -20577,7 +20566,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:6">
       <c r="B40" s="470" t="s">
         <v>500</v>
       </c>
@@ -20586,7 +20575,7 @@
       <c r="E40" s="470"/>
       <c r="F40" s="470"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:6">
       <c r="B41" s="372" t="s">
         <v>202</v>
       </c>
@@ -20599,7 +20588,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:6">
       <c r="B43" s="470" t="s">
         <v>501</v>
       </c>
@@ -20608,7 +20597,7 @@
       <c r="E43" s="470"/>
       <c r="F43" s="470"/>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:6">
       <c r="B44" s="372" t="s">
         <v>267</v>
       </c>
@@ -20623,7 +20612,7 @@
       <c r="E44" s="371"/>
       <c r="F44" s="371"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:6">
       <c r="B45" s="372" t="s">
         <v>268</v>
       </c>
@@ -20638,7 +20627,7 @@
       <c r="E45" s="371"/>
       <c r="F45" s="371"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:6">
       <c r="B46" s="372" t="s">
         <v>203</v>
       </c>
@@ -20651,12 +20640,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:6">
       <c r="B48" s="343" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:6">
       <c r="B49" s="372" t="s">
         <v>223</v>
       </c>
@@ -20669,7 +20658,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:6">
       <c r="B51" s="470" t="s">
         <v>503</v>
       </c>
@@ -20678,7 +20667,7 @@
       <c r="E51" s="470"/>
       <c r="F51" s="470"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:6">
       <c r="B52" s="372" t="s">
         <v>494</v>
       </c>
@@ -20691,16 +20680,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:6">
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
+    </row>
+    <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
         <v>207</v>
       </c>
@@ -20713,25 +20702,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B57" s="471" t="s">
+    <row r="57" spans="2:6">
+      <c r="B57" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B58" s="471" t="s">
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
         <v>370</v>
       </c>
@@ -20744,7 +20733,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:6">
       <c r="B61" s="372" t="s">
         <v>213</v>
       </c>
@@ -20757,23 +20746,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:6">
       <c r="B62" s="377" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.7028344166783808E-2</v>
+        <v>8.1036606419806506E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:6">
       <c r="B63" s="377" t="s">
         <v>330</v>
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.5550967741935488E-2</v>
+        <v>3.7400904977375568E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20783,7 +20772,7 @@
         <v>0.51281220823452245</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6">
       <c r="B65" s="369" t="s">
         <v>374</v>
       </c>
@@ -20794,7 +20783,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6">
       <c r="B66" s="372" t="s">
         <v>324</v>
       </c>
@@ -20807,7 +20796,7 @@
         <v>0.37652309539416257</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6">
       <c r="B67" s="382" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -20821,7 +20810,7 @@
         <v>0.563411673135921</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6">
       <c r="B68" s="382" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -20835,7 +20824,7 @@
         <v>0.44445275381950455</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6">
       <c r="B69" s="382" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -20849,7 +20838,7 @@
         <v>1.5036272168761813</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="345" t="s">
         <v>474</v>
       </c>
@@ -20859,43 +20848,43 @@
       <c r="E71" s="345"/>
       <c r="F71" s="345"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6">
       <c r="A72" s="385"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B74" s="472" t="s">
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="477" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
+    </row>
+    <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B77" s="471" t="s">
+    <row r="77" spans="1:6">
+      <c r="B77" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
         <v>215</v>
       </c>
@@ -20908,7 +20897,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6">
       <c r="B79" s="372" t="s">
         <v>234</v>
       </c>
@@ -20921,7 +20910,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6">
       <c r="B80" s="382" t="s">
         <v>308</v>
       </c>
@@ -20930,7 +20919,7 @@
         <v>5.8904840599867017E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6">
       <c r="B81" s="382" t="s">
         <v>310</v>
       </c>
@@ -20939,12 +20928,12 @@
         <v>0.15503078912543219</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6">
       <c r="B83" s="343" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6">
       <c r="B84" s="343" t="s">
         <v>224</v>
       </c>
@@ -20957,7 +20946,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6">
       <c r="B85" s="382" t="s">
         <v>479</v>
       </c>
@@ -20970,7 +20959,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6">
       <c r="B86" s="372" t="s">
         <v>235</v>
       </c>
@@ -20983,12 +20972,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6">
       <c r="B88" s="343" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6">
       <c r="B89" s="343" t="s">
         <v>217</v>
       </c>
@@ -21001,7 +20990,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6">
       <c r="B90" s="372" t="s">
         <v>236</v>
       </c>
@@ -21014,7 +21003,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6">
       <c r="B92" s="372" t="s">
         <v>478</v>
       </c>
@@ -21027,7 +21016,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="345" t="s">
         <v>480</v>
       </c>
@@ -21037,49 +21026,49 @@
       <c r="E94" s="345"/>
       <c r="F94" s="345"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6">
       <c r="A95" s="385"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" s="385"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6">
       <c r="A100" s="385"/>
       <c r="B100" s="369" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6">
       <c r="A101" s="385"/>
       <c r="B101" s="372" t="s">
         <v>212</v>
@@ -21089,7 +21078,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6">
       <c r="A102" s="385"/>
       <c r="B102" s="382" t="s">
         <v>317</v>
@@ -21099,7 +21088,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6">
       <c r="A103" s="385"/>
       <c r="B103" s="382" t="s">
         <v>316</v>
@@ -21109,7 +21098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
         <v>532</v>
@@ -21118,47 +21107,47 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6">
       <c r="A105" s="385"/>
       <c r="C105" s="392"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6">
       <c r="A106" s="385"/>
       <c r="B106" s="393" t="s">
         <v>373</v>
       </c>
       <c r="C106" s="392"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" s="385"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6">
       <c r="A110" s="385"/>
       <c r="B110" s="369" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6">
       <c r="A111" s="385"/>
       <c r="B111" s="375" t="s">
         <v>484</v>
@@ -21172,7 +21161,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6">
       <c r="A112" s="385"/>
       <c r="B112" s="372" t="s">
         <v>375</v>
@@ -21186,29 +21175,29 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6">
       <c r="A113" s="385"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" s="385"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6">
       <c r="A116" s="385"/>
       <c r="B116" s="369" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6">
       <c r="A117" s="385"/>
       <c r="B117" s="342" t="s">
         <v>376</v>
@@ -21226,7 +21215,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6">
       <c r="A118" s="385"/>
       <c r="B118" s="395" t="str">
         <f>DCF!B90</f>
@@ -21249,7 +21238,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6">
       <c r="A119" s="385"/>
       <c r="B119" s="400" t="str">
         <f>DCF!B91</f>
@@ -21272,7 +21261,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6">
       <c r="B120" s="400" t="str">
         <f>DCF!B92</f>
         <v>Base</v>
@@ -21294,7 +21283,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6">
       <c r="B121" s="400" t="str">
         <f>DCF!B93</f>
         <v>Pessimistic</v>
@@ -21316,7 +21305,7 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6">
       <c r="B122" s="400" t="str">
         <f>DCF!B94</f>
         <v>Devil's advocate</v>
@@ -21338,7 +21327,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6">
       <c r="B124" s="470" t="s">
         <v>516</v>
       </c>
@@ -21347,7 +21336,7 @@
       <c r="E124" s="470"/>
       <c r="F124" s="470"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6">
       <c r="B125" s="372" t="s">
         <v>218</v>
       </c>
@@ -21360,16 +21349,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B127" s="475" t="s">
+    <row r="127" spans="1:6">
+      <c r="B127" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
-    </row>
-    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
+    </row>
+    <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
         <v>490</v>
       </c>
@@ -21379,30 +21368,30 @@
       <c r="E129" s="345"/>
       <c r="F129" s="345"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B131" s="476" t="s">
+    <row r="131" spans="1:6">
+      <c r="B131" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="471" t="s">
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B132" s="474" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
+    </row>
+    <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6">
       <c r="B135" s="343" t="s">
         <v>380</v>
       </c>
@@ -21411,7 +21400,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6">
       <c r="B136" s="343" t="s">
         <v>381</v>
       </c>
@@ -21424,14 +21413,14 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6">
       <c r="B138" s="369" t="s">
         <v>491</v>
       </c>
       <c r="C138" s="407"/>
       <c r="D138" s="407"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6">
       <c r="B139" s="340" t="s">
         <v>460</v>
       </c>
@@ -21450,7 +21439,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6">
       <c r="B140" s="408" t="s">
         <v>311</v>
       </c>
@@ -21471,7 +21460,7 @@
         <v>0.32950289523458665</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6">
       <c r="B141" s="408" t="s">
         <v>312</v>
       </c>
@@ -21492,7 +21481,7 @@
         <v>0.22621703288100403</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6">
       <c r="B143" s="340" t="s">
         <v>461</v>
       </c>
@@ -21511,7 +21500,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6">
       <c r="B144" s="408" t="s">
         <v>314</v>
       </c>
@@ -21532,7 +21521,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6">
       <c r="B145" s="408" t="s">
         <v>313</v>
       </c>
@@ -21553,7 +21542,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="345" t="s">
         <v>473</v>
       </c>
@@ -21563,50 +21552,50 @@
       <c r="E147" s="345"/>
       <c r="F147" s="345"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B149" s="477" t="s">
+    <row r="149" spans="1:6">
+      <c r="B149" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
+    </row>
+    <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B152" s="473" t="s">
+    <row r="152" spans="1:6">
+      <c r="B152" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
+    </row>
+    <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6">
       <c r="B154" s="412" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6">
       <c r="B155" s="412" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6">
       <c r="B157" s="343" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" ht="24.5" customHeight="1">
       <c r="B158" s="470" t="s">
         <v>437</v>
       </c>
@@ -21615,60 +21604,57 @@
       <c r="E158" s="470"/>
       <c r="F158" s="470"/>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6">
       <c r="B160" s="343" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B161" s="474" t="s">
+    <row r="161" spans="2:6">
+      <c r="B161" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
-    </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B162" s="474" t="s">
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
+    </row>
+    <row r="162" spans="2:6">
+      <c r="B162" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
+    </row>
+    <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:6">
       <c r="B165" s="412" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:6">
       <c r="B166" s="412" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:6">
       <c r="B167" s="412" t="s">
         <v>390</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21683,12 +21669,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFF2F1D-A5F9-41C7-893A-35C7C7E48E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9646B4-C006-465D-B919-128AC2098916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>110.5</v>
+        <v>105.98</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>162649.5869115</v>
+        <v>155996.40923874002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.15281305363396264</v>
+        <v>0.16950158815718475</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.1036606419806506E-2</v>
+        <v>8.449278174550498E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.7400904977375568E-2</v>
+        <v>3.8996036988110966E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.7400904977375568E-2</v>
+        <v>3.8996036988110966E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.7400904977375568E-2</v>
+        <v>3.8996036988110966E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.3982535746606335E-2</v>
+        <v>4.5858371390828455E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.1036606419806506E-2</v>
+        <v>8.449278174550498E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.8967418851037724E-2</v>
+        <v>8.2335344244571312E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.6372652325771603E-2</v>
+        <v>7.962991207772939E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2986860447634189E-2</v>
+        <v>8.6526213242721056E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1701160608791165E-2</v>
+        <v>8.518567887593341E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>110.5</v>
+        <v>105.98</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15281305363396264</v>
+        <v>0.16950158815718475</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>110.5</v>
+        <v>105.98</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>162649.5869115</v>
+        <v>155996.40923874002</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.15281305363396264</v>
+        <v>0.16950158815718475</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.1036606419806506E-2</v>
+        <v>8.449278174550498E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.7400904977375568E-2</v>
+        <v>3.8996036988110966E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,12 +21649,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21669,15 +21672,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9646B4-C006-465D-B919-128AC2098916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA812263-6AEB-4C7E-9358-D7457F7E68DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>105.98</v>
+        <v>105.21</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>155996.40923874002</v>
+        <v>154863.01392722997</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.16950158815718475</v>
+        <v>0.17244132069135837</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.449278174550498E-2</v>
+        <v>8.5111158724347685E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.8996036988110966E-2</v>
+        <v>3.9281437125748511E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.8996036988110966E-2</v>
+        <v>3.9281437125748511E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.8996036988110966E-2</v>
+        <v>3.9281437125748511E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.5858371390828455E-2</v>
+        <v>4.6193994867408043E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.449278174550498E-2</v>
+        <v>8.5111158724347685E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.2335344244571312E-2</v>
+        <v>8.2937931594331993E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.962991207772939E-2</v>
+        <v>8.0212699192070733E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6526213242721056E-2</v>
+        <v>8.7159472288409645E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.518567887593341E-2</v>
+        <v>8.5809126958192428E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>105.98</v>
+        <v>105.21</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16950158815718475</v>
+        <v>0.17244132069135837</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>105.98</v>
+        <v>105.21</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>155996.40923874002</v>
+        <v>154863.01392722997</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.16950158815718475</v>
+        <v>0.17244132069135837</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.449278174550498E-2</v>
+        <v>8.5111158724347685E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.8996036988110966E-2</v>
+        <v>3.9281437125748511E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,15 +21649,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21672,12 +21669,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA812263-6AEB-4C7E-9358-D7457F7E68DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3474F9BA-91C2-4005-94A8-8975436D4E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>105.21</v>
+        <v>104.8</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>154863.01392722997</v>
+        <v>154259.51772239999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.17244132069135837</v>
+        <v>0.17401862015234429</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.5111158724347685E-2</v>
+        <v>8.5444131768975376E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.9281437125748511E-2</v>
+        <v>3.9435114503816801E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.9281437125748511E-2</v>
+        <v>3.9435114503816801E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.9281437125748511E-2</v>
+        <v>3.9435114503816801E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.6193994867408043E-2</v>
+        <v>4.637471564885496E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.5111158724347685E-2</v>
+        <v>8.5444131768975376E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.2937931594331993E-2</v>
+        <v>8.3262402509920508E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.0212699192070733E-2</v>
+        <v>8.0526508416009182E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7159472288409645E-2</v>
+        <v>8.7500458773507428E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5809126958192428E-2</v>
+        <v>8.614483060373497E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>105.21</v>
+        <v>104.8</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.17244132069135837</v>
+        <v>0.17401862015234429</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>105.21</v>
+        <v>104.8</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>154863.01392722997</v>
+        <v>154259.51772239999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.17244132069135837</v>
+        <v>0.17401862015234429</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.5111158724347685E-2</v>
+        <v>8.5444131768975376E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.9281437125748511E-2</v>
+        <v>3.9435114503816801E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,12 +21649,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21669,15 +21672,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3474F9BA-91C2-4005-94A8-8975436D4E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AFD8EF9-FB7C-423A-8B07-C44C9AB7738D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>104.8</v>
+        <v>107.86</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>154259.51772239999</v>
+        <v>158763.66012918</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.17401862015234429</v>
+        <v>0.16244471801925806</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.5444131768975376E-2</v>
+        <v>8.3020072403009626E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.9435114503816801E-2</v>
+        <v>3.8316335991099577E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.9435114503816801E-2</v>
+        <v>3.8316335991099577E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.9435114503816801E-2</v>
+        <v>3.8316335991099577E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.637471564885496E-2</v>
+        <v>4.5059059892453179E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.5444131768975376E-2</v>
+        <v>8.3020072403009626E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.3262402509920508E-2</v>
+        <v>8.0900239041717684E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.0526508416009182E-2</v>
+        <v>7.8241962562560372E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7500458773507428E-2</v>
+        <v>8.5018061185458738E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.614483060373497E-2</v>
+        <v>8.3700892335169891E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>104.8</v>
+        <v>107.86</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.17401862015234429</v>
+        <v>0.16244471801925806</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>104.8</v>
+        <v>107.86</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>154259.51772239999</v>
+        <v>158763.66012918</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.17401862015234429</v>
+        <v>0.16244471801925806</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.5444131768975376E-2</v>
+        <v>8.3020072403009626E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.9435114503816801E-2</v>
+        <v>3.8316335991099577E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,15 +21649,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21672,12 +21669,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AFD8EF9-FB7C-423A-8B07-C44C9AB7738D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBFFD21D-C8E5-4B3B-B7FC-2E6C29CA3931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>107.86</v>
+        <v>109.99</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>158763.66012918</v>
+        <v>161898.89651036999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.16244471801925806</v>
+        <v>0.15464914212088174</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.3020072403009626E-2</v>
+        <v>8.141235575405599E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.8316335991099577E-2</v>
+        <v>3.757432493863079E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.8316335991099577E-2</v>
+        <v>3.757432493863079E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.8316335991099577E-2</v>
+        <v>3.757432493863079E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.5059059892453179E-2</v>
+        <v>4.4186473315755981E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.3020072403009626E-2</v>
+        <v>8.141235575405599E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.0900239041717684E-2</v>
+        <v>7.9333573807070359E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.8241962562560372E-2</v>
+        <v>7.6726775906880276E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5018061185458738E-2</v>
+        <v>8.3371652690822612E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3700892335169891E-2</v>
+        <v>8.2079991338043681E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>107.86</v>
+        <v>109.99</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16244471801925806</v>
+        <v>0.15464914212088174</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>107.86</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>158763.66012918</v>
+        <v>161898.89651036999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.16244471801925806</v>
+        <v>0.15464914212088174</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.3020072403009626E-2</v>
+        <v>8.141235575405599E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.8316335991099577E-2</v>
+        <v>3.757432493863079E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,12 +21649,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21669,15 +21672,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBFFD21D-C8E5-4B3B-B7FC-2E6C29CA3931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725F6A6E-D825-46D4-8D00-1C36608105AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>109.99</v>
+        <v>108.13</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>161898.89651036999</v>
+        <v>159161.08445918999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.15464914212088174</v>
+        <v>0.16144498911950469</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5555,13 +5555,13 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>73.121635714867196</v>
+        <v>78.012426135280521</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>404</v>
       </c>
       <c r="E22" s="79">
-        <v>0.32950289523458665</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5570,13 +5570,13 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>92.375891520070169</v>
+        <v>98.348854293525079</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>405</v>
       </c>
       <c r="E23" s="443">
-        <v>0.22621703288100403</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.141235575405599E-2</v>
+        <v>8.2812771750565228E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.757432493863079E-2</v>
+        <v>3.8220660316285959E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6579,19 +6579,19 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>7.2052832811602343</v>
+        <v>7.5056313154301346</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>65.916352433706962</v>
+        <v>70.506794819850384</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>73.121635714867196</v>
+        <v>78.012426135280521</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.32950289523458665</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6600,19 +6600,19 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>8.3604728249046811</v>
+        <v>8.7056666666666676</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>84.015418695165494</v>
+        <v>89.643187626858406</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>92.375891520070169</v>
+        <v>98.348854293525079</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.22621703288100403</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.757432493863079E-2</v>
+        <v>3.8220660316285959E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.757432493863079E-2</v>
+        <v>3.8220660316285959E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.4186473315755981E-2</v>
+        <v>4.4946547674095998E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.141235575405599E-2</v>
+        <v>8.2812771750565228E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.9333573807070359E-2</v>
+        <v>8.0698231601217696E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.6726775906880276E-2</v>
+        <v>7.8046592823432556E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3371652690822612E-2</v>
+        <v>8.4805771566295929E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2079991338043681E-2</v>
+        <v>8.3491891679195629E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>109.99</v>
+        <v>108.13</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15464914212088174</v>
+        <v>0.16144498911950469</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20032,23 +20032,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>7.2052832811602343</v>
+        <v>7.5056313154301346</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>65.916352433706962</v>
+        <v>70.506794819850384</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>73.121635714867196</v>
+        <v>78.012426135280521</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.32950289523458665</v>
+        <v>0.3</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.52795340583818939</v>
+        <v>0.49638024779618584</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20057,23 +20057,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>8.3604728249046811</v>
+        <v>8.7056666666666676</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>84.015418695165494</v>
+        <v>89.643187626858406</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>92.375891520070169</v>
+        <v>98.348854293525079</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.22621703288100403</v>
+        <v>0.2</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.40365495727218781</v>
+        <v>0.36509568946177962</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>109.99</v>
+        <v>108.13</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>161898.89651036999</v>
+        <v>159161.08445918999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.15464914212088174</v>
+        <v>0.16144498911950469</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20410,14 +20410,14 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>73.121635714867196</v>
+        <v>78.012426135280521</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>438</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.32950289523458665</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20426,14 +20426,14 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>92.375891520070169</v>
+        <v>98.348854293525079</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>439</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.22621703288100403</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.141235575405599E-2</v>
+        <v>8.2812771750565228E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.757432493863079E-2</v>
+        <v>3.8220660316285959E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21445,19 +21445,19 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>7.2052832811602343</v>
+        <v>7.5056313154301346</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>65.916352433706962</v>
+        <v>70.506794819850384</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>73.121635714867196</v>
+        <v>78.012426135280521</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.32950289523458665</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21466,19 +21466,19 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>8.3604728249046811</v>
+        <v>8.7056666666666676</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>84.015418695165494</v>
+        <v>89.643187626858406</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>92.375891520070169</v>
+        <v>98.348854293525079</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.22621703288100403</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,15 +21649,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21672,12 +21669,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725F6A6E-D825-46D4-8D00-1C36608105AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918DA406-0606-4C85-AB2E-5FA385F335A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,12 +21649,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21669,15 +21672,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918DA406-0606-4C85-AB2E-5FA385F335A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{567DF11E-1846-43E9-BDE5-562F01F4503A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>108.13</v>
+        <v>105.2</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>159161.08445918999</v>
+        <v>154848.29450760002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.16144498911950469</v>
+        <v>0.17247969171843658</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.2812771750565228E-2</v>
+        <v>8.5119249138675079E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.8220660316285959E-2</v>
+        <v>3.9285171102661602E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.8220660316285959E-2</v>
+        <v>3.9285171102661602E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.8220660316285959E-2</v>
+        <v>3.9285171102661602E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.4946547674095998E-2</v>
+        <v>4.6198385931558936E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.2812771750565228E-2</v>
+        <v>8.5119249138675079E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.0698231601217696E-2</v>
+        <v>8.2945815428133729E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.8046592823432556E-2</v>
+        <v>8.0220323973362748E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4805771566295929E-2</v>
+        <v>8.7167757409349594E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3491891679195629E-2</v>
+        <v>8.5817283719310106E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>108.13</v>
+        <v>105.2</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16144498911950469</v>
+        <v>0.17247969171843658</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>108.13</v>
+        <v>105.2</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>159161.08445918999</v>
+        <v>154848.29450760002</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.16144498911950469</v>
+        <v>0.17247969171843658</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.2812771750565228E-2</v>
+        <v>8.5119249138675079E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.8220660316285959E-2</v>
+        <v>3.9285171102661602E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,15 +21649,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21672,12 +21669,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{567DF11E-1846-43E9-BDE5-562F01F4503A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696668C8-F0F9-4632-B18B-9F402E99E5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,6 +4986,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5012,9 +5015,6 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -5351,7 +5351,7 @@
         <v>535</v>
       </c>
       <c r="F3" s="429">
-        <v>46066</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="12.4">
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>105.2</v>
+        <v>103.39</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>154848.29450760002</v>
+        <v>152184.07955456999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.17247969171843658</v>
+        <v>0.22370349845707738</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="463" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="463"/>
+      <c r="D12" s="463"/>
+      <c r="E12" s="463"/>
+      <c r="F12" s="463"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>154.90342821921132</v>
+        <v>174.07668204091138</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>345</v>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>78.012426135280521</v>
+        <v>86.739441984939162</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>404</v>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>98.348854293525079</v>
+        <v>109.4444872921941</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>405</v>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>131.12448893172376</v>
+        <v>146.05268014903339</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>406</v>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>136.36157636797898</v>
+        <v>151.90346952484109</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>407</v>
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="463" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="463"/>
+      <c r="D29" s="463"/>
+      <c r="E29" s="463"/>
+      <c r="F29" s="463"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="467" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="467"/>
+      <c r="D30" s="467"/>
+      <c r="E30" s="467"/>
+      <c r="F30" s="467"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="464" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="464"/>
+      <c r="D33" s="464"/>
+      <c r="E33" s="464"/>
+      <c r="F33" s="464"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="464" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="464"/>
+      <c r="D36" s="464"/>
+      <c r="E36" s="464"/>
+      <c r="F36" s="464"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="464" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="464"/>
+      <c r="D40" s="464"/>
+      <c r="E40" s="464"/>
+      <c r="F40" s="464"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="464" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="464"/>
+      <c r="D43" s="464"/>
+      <c r="E43" s="464"/>
+      <c r="F43" s="464"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="464" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="464"/>
+      <c r="D51" s="464"/>
+      <c r="E51" s="464"/>
+      <c r="F51" s="464"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,13 +5826,13 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="464" t="s">
         <v>265</v>
       </c>
-      <c r="C54" s="464"/>
-      <c r="D54" s="464"/>
-      <c r="E54" s="464"/>
-      <c r="F54" s="464"/>
+      <c r="C54" s="465"/>
+      <c r="D54" s="465"/>
+      <c r="E54" s="465"/>
+      <c r="F54" s="465"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="463" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="463"/>
+      <c r="D57" s="463"/>
+      <c r="E57" s="463"/>
+      <c r="F57" s="463"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="463" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="463"/>
+      <c r="D58" s="463"/>
+      <c r="E58" s="463"/>
+      <c r="F58" s="463"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.5119249138675079E-2</v>
+        <v>8.6609391714755957E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.9285171102661602E-2</v>
+        <v>3.9972918077183485E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="463" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="463"/>
+      <c r="D73" s="463"/>
+      <c r="E73" s="463"/>
+      <c r="F73" s="463"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="463" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="463"/>
+      <c r="D77" s="463"/>
+      <c r="E77" s="463"/>
+      <c r="F77" s="463"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="463" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="463"/>
+      <c r="D96" s="463"/>
+      <c r="E96" s="463"/>
+      <c r="F96" s="463"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="467" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="467"/>
+      <c r="D97" s="467"/>
+      <c r="E97" s="467"/>
+      <c r="F97" s="467"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="467" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="467"/>
+      <c r="D98" s="467"/>
+      <c r="E98" s="467"/>
+      <c r="F98" s="467"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="463" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="463"/>
+      <c r="D107" s="463"/>
+      <c r="E107" s="463"/>
+      <c r="F107" s="463"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="463"/>
+      <c r="D108" s="463"/>
+      <c r="E108" s="463"/>
+      <c r="F108" s="463"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="463" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="463"/>
+      <c r="D114" s="463"/>
+      <c r="E114" s="463"/>
+      <c r="F114" s="463"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6354,7 +6354,7 @@
     <row r="118" spans="2:6">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
-        <v>Snowball Scenario (5yrs)</v>
+        <v>Snowball Scenario (15yrs)</v>
       </c>
       <c r="C118" s="206">
         <f>DCF!C90</f>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>171.57 CNY</v>
+        <v>221.73 CNY</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6370,13 +6370,13 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-8.5764377786937424E-3</v>
+        <v>-5.7264664828039394E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
-        <v>Optimistic (5yrs)</v>
+        <v>Optimistic (15yrs)</v>
       </c>
       <c r="C119" s="198">
         <f>DCF!C91</f>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>158.88 CNY</v>
+        <v>183.61 CNY</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6392,13 +6392,13 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>1.7826766936537737E-2</v>
+        <v>5.2933765449977585E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
-        <v>Base (5yrs)</v>
+        <v>Base (15yrs)</v>
       </c>
       <c r="C120" s="198">
         <f>DCF!C92</f>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>152.86 CNY</v>
+        <v>167.6 CNY</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6414,13 +6414,13 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.134800981224807E-2</v>
+        <v>3.707620088055634E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
-        <v>Pessimistic (5yrs)</v>
+        <v>Pessimistic (15yrs)</v>
       </c>
       <c r="C121" s="198">
         <f>DCF!C93</f>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>147.07 CNY</v>
+        <v>153.33 CNY</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6436,13 +6436,13 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>4.5083874550095666E-2</v>
+        <v>6.9083307477753805E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
-        <v>Devil's advocate (5yrs)</v>
+        <v>Devil's advocate (15yrs)</v>
       </c>
       <c r="C122" s="198">
         <f>DCF!C94</f>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>141.48 CNY</v>
+        <v>140.61 CNY</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6458,17 +6458,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>5.9035182400374427E-2</v>
+        <v>0.10122435665685528</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="464" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="464"/>
+      <c r="D124" s="464"/>
+      <c r="E124" s="464"/>
+      <c r="F124" s="464"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>154.90342821921132</v>
+        <v>174.07668204091138</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6484,13 +6484,13 @@
       </c>
     </row>
     <row r="127" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B127" s="465" t="s">
+      <c r="B127" s="466" t="s">
         <v>356</v>
       </c>
-      <c r="C127" s="465"/>
-      <c r="D127" s="465"/>
-      <c r="E127" s="465"/>
-      <c r="F127" s="465"/>
+      <c r="C127" s="466"/>
+      <c r="D127" s="466"/>
+      <c r="E127" s="466"/>
+      <c r="F127" s="466"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="468" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="468"/>
+      <c r="D131" s="468"/>
+      <c r="E131" s="468"/>
+      <c r="F131" s="468"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="463"/>
+      <c r="D132" s="463"/>
+      <c r="E132" s="463"/>
+      <c r="F132" s="463"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6583,11 +6583,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>70.506794819850384</v>
+        <v>79.233810669509026</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>78.012426135280521</v>
+        <v>86.739441984939162</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6604,11 +6604,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>89.643187626858406</v>
+        <v>100.73882062552742</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>98.348854293525079</v>
+        <v>109.4444872921941</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6651,11 +6651,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>120.60696729816429</v>
+        <v>135.53515851547391</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>131.12448893172376</v>
+        <v>146.05268014903339</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6672,11 +6672,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>125.56515202911834</v>
+        <v>141.10704518598044</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>136.36157636797898</v>
+        <v>151.90346952484109</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="462" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="463"/>
+      <c r="D149" s="463"/>
+      <c r="E149" s="463"/>
+      <c r="F149" s="463"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6708,13 +6708,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="464" t="s">
+      <c r="B152" s="465" t="s">
         <v>293</v>
       </c>
-      <c r="C152" s="464"/>
-      <c r="D152" s="464"/>
-      <c r="E152" s="464"/>
-      <c r="F152" s="464"/>
+      <c r="C152" s="465"/>
+      <c r="D152" s="465"/>
+      <c r="E152" s="465"/>
+      <c r="F152" s="465"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="464" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="464"/>
+      <c r="D158" s="464"/>
+      <c r="E158" s="464"/>
+      <c r="F158" s="464"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="461" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="461"/>
+      <c r="D161" s="461"/>
+      <c r="E161" s="461"/>
+      <c r="F161" s="461"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="461" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="461"/>
+      <c r="D162" s="461"/>
+      <c r="E162" s="461"/>
+      <c r="F162" s="461"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.9285171102661602E-2</v>
+        <v>3.9972918077183485E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.9285171102661602E-2</v>
+        <v>3.9972918077183485E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.6198385931558936E-2</v>
+        <v>4.7007159299738852E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14819,7 +14819,7 @@
       <c r="D115" s="52"/>
       <c r="E115" s="451" t="str">
         <f>DCF!F15&amp;"yrs Projection"</f>
-        <v>6yrs Projection</v>
+        <v>16yrs Projection</v>
       </c>
       <c r="F115" s="52"/>
       <c r="G115" s="22" t="str">
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.5119249138675079E-2</v>
+        <v>8.6609391714755957E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.2945815428133729E-2</v>
+        <v>8.4397908724631668E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.0220323973362748E-2</v>
+        <v>8.1624703375546587E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7167757409349594E-2</v>
+        <v>8.8693762254217795E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5817283719310106E-2</v>
+        <v>8.7319646457794983E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="C15" s="148">
         <f>Scenarios!C45</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E15" s="308" t="str">
         <f>IF(F14="II","Change year","Terminal Year")</f>
@@ -16340,7 +16340,7 @@
       </c>
       <c r="F15" s="310">
         <f>IF(F14="II",_xlfn.CEILING.MATH(C15/2),C15+1)</f>
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H15" s="97" t="s">
         <v>427</v>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>155.15545216460865</v>
+        <v>173.55524443059508</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16727,26 +16727,26 @@
     <row r="26" spans="1:21">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B26" s="117">
         <v>6</v>
       </c>
       <c r="C26" s="277">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>35936471632.093979</v>
       </c>
       <c r="D26" s="299">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.38559171477595E-2</v>
       </c>
       <c r="E26" s="299">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.56520395086535147</v>
       </c>
       <c r="F26" s="277">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20311435746.620144</v>
       </c>
       <c r="G26" s="299">
         <f t="shared" si="2"/>
@@ -16754,48 +16754,48 @@
       </c>
       <c r="H26" s="277">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>15183338612.427582</v>
       </c>
       <c r="I26" s="299">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J26" s="299">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.4225049906921779</v>
       </c>
       <c r="K26" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.65707689293158289</v>
       </c>
       <c r="L26" s="277">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9976620959.7820473</v>
       </c>
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B27" s="117">
         <v>7</v>
       </c>
       <c r="C27" s="277">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>36793769121.932022</v>
       </c>
       <c r="D27" s="299">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.38559171477595E-2</v>
       </c>
       <c r="E27" s="299">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.56520395086535147</v>
       </c>
       <c r="F27" s="277">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20795983674.943554</v>
       </c>
       <c r="G27" s="299">
         <f t="shared" si="2"/>
@@ -16803,48 +16803,48 @@
       </c>
       <c r="H27" s="277">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>15545551080.392033</v>
       </c>
       <c r="I27" s="299">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J27" s="299">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.42250499069217795</v>
       </c>
       <c r="K27" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.61265910762851561</v>
       </c>
       <c r="L27" s="277">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9524123452.5064888</v>
       </c>
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B28" s="117">
         <v>8</v>
       </c>
       <c r="C28" s="277">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37671518229.658623</v>
       </c>
       <c r="D28" s="299">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.38559171477595E-2</v>
       </c>
       <c r="E28" s="299">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.56520395086535147</v>
       </c>
       <c r="F28" s="277">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>21292090938.499165</v>
       </c>
       <c r="G28" s="299">
         <f t="shared" si="2"/>
@@ -16852,48 +16852,48 @@
       </c>
       <c r="H28" s="277">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>15916404458.982128</v>
       </c>
       <c r="I28" s="299">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J28" s="299">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.42250499069217795</v>
       </c>
       <c r="K28" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.5712439231967511</v>
       </c>
       <c r="L28" s="277">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9092149326.3352127</v>
       </c>
     </row>
     <row r="29" spans="1:21">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B29" s="117">
         <v>9</v>
       </c>
       <c r="C29" s="277">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>38570206847.375671</v>
       </c>
       <c r="D29" s="299">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.38559171477595E-2</v>
       </c>
       <c r="E29" s="299">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.56520395086535147</v>
       </c>
       <c r="F29" s="277">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>21800033295.830563</v>
       </c>
       <c r="G29" s="299">
         <f t="shared" si="2"/>
@@ -16901,48 +16901,48 @@
       </c>
       <c r="H29" s="277">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>16296104885.045834</v>
       </c>
       <c r="I29" s="299">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J29" s="299">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.4225049906921779</v>
       </c>
       <c r="K29" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.53262836661701729</v>
       </c>
       <c r="L29" s="277">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8679767727.1415596</v>
       </c>
     </row>
     <row r="30" spans="1:21">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B30" s="117">
         <v>10</v>
       </c>
       <c r="C30" s="277">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>39490334506.298607</v>
       </c>
       <c r="D30" s="299">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.38559171477595E-2</v>
       </c>
       <c r="E30" s="299">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.56520395086535147</v>
       </c>
       <c r="F30" s="277">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>22320093083.954292</v>
       </c>
       <c r="G30" s="299">
         <f t="shared" si="2"/>
@@ -16950,48 +16950,48 @@
       </c>
       <c r="H30" s="277">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>16684863413.014685</v>
       </c>
       <c r="I30" s="299">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J30" s="299">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.4225049906921779</v>
       </c>
       <c r="K30" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.49662318565689262</v>
       </c>
       <c r="L30" s="277">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8286090020.4214869</v>
       </c>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B31" s="117">
         <v>11</v>
       </c>
       <c r="C31" s="277">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>40432412654.418175</v>
       </c>
       <c r="D31" s="299">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.38559171477595E-2</v>
       </c>
       <c r="E31" s="299">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.56520395086535147</v>
       </c>
       <c r="F31" s="277">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>22852559375.295383</v>
       </c>
       <c r="G31" s="299">
         <f t="shared" si="2"/>
@@ -16999,48 +16999,48 @@
       </c>
       <c r="H31" s="277">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>17082896132.217247</v>
       </c>
       <c r="I31" s="299">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J31" s="299">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.4225049906921779</v>
       </c>
       <c r="K31" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.46305192135840806</v>
       </c>
       <c r="L31" s="277">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7910267876.3893137</v>
       </c>
     </row>
     <row r="32" spans="1:21">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B32" s="117">
         <v>12</v>
       </c>
       <c r="C32" s="277">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>41396964940.785995</v>
       </c>
       <c r="D32" s="299">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.38559171477595E-2</v>
       </c>
       <c r="E32" s="299">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.56520395086535147</v>
       </c>
       <c r="F32" s="277">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>23397728138.366684</v>
       </c>
       <c r="G32" s="299">
         <f t="shared" si="2"/>
@@ -17048,48 +17048,48 @@
       </c>
       <c r="H32" s="277">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>17490424286.991199</v>
       </c>
       <c r="I32" s="299">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.3855917147759254E-2</v>
       </c>
       <c r="J32" s="299">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.42250499069217784</v>
       </c>
       <c r="K32" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.43175004322462285</v>
       </c>
       <c r="L32" s="277">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7551491441.9254436</v>
       </c>
     </row>
     <row r="33" spans="1:21">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B33" s="117">
         <v>13</v>
       </c>
       <c r="C33" s="277">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>42384527506.582092</v>
       </c>
       <c r="D33" s="299">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.38559171477595E-2</v>
       </c>
       <c r="E33" s="299">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.56520395086535147</v>
       </c>
       <c r="F33" s="277">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>23955902402.281364</v>
       </c>
       <c r="G33" s="299">
         <f t="shared" si="2"/>
@@ -17097,23 +17097,23 @@
       </c>
       <c r="H33" s="277">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>17907674399.660824</v>
       </c>
       <c r="I33" s="299">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.3855917147759698E-2</v>
       </c>
       <c r="J33" s="299">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.4225049906921779</v>
       </c>
       <c r="K33" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.40256414286678116</v>
       </c>
       <c r="L33" s="277">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7208987595.4368591</v>
       </c>
       <c r="N33" s="275"/>
       <c r="O33" s="275"/>
@@ -17127,26 +17127,26 @@
     <row r="34" spans="1:21">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B34" s="117">
         <v>14</v>
       </c>
       <c r="C34" s="277">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>43395649283.126045</v>
       </c>
       <c r="D34" s="299">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.38559171477595E-2</v>
       </c>
       <c r="E34" s="299">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.56520395086535147</v>
       </c>
       <c r="F34" s="277">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24527392425.189999</v>
       </c>
       <c r="G34" s="299">
         <f t="shared" si="2"/>
@@ -17154,23 +17154,23 @@
       </c>
       <c r="H34" s="277">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>18334878396.448185</v>
       </c>
       <c r="I34" s="299">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J34" s="299">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.4225049906921779</v>
       </c>
       <c r="K34" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.37535118216016894</v>
       </c>
       <c r="L34" s="277">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6882018280.8697691</v>
       </c>
       <c r="N34" s="275"/>
       <c r="O34" s="275"/>
@@ -17184,26 +17184,26 @@
     <row r="35" spans="1:21">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B35" s="117">
         <v>15</v>
       </c>
       <c r="C35" s="277">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>44430892296.997528</v>
       </c>
       <c r="D35" s="299">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.38559171477595E-2</v>
       </c>
       <c r="E35" s="299">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.56520395086535147</v>
       </c>
       <c r="F35" s="277">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>25112515866.735912</v>
       </c>
       <c r="G35" s="299">
         <f t="shared" si="2"/>
@@ -17211,23 +17211,23 @@
       </c>
       <c r="H35" s="277">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>18772273736.388096</v>
       </c>
       <c r="I35" s="299">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.3855917147759254E-2</v>
       </c>
       <c r="J35" s="299">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.42250499069217784</v>
       </c>
       <c r="K35" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.34997779222393377</v>
       </c>
       <c r="L35" s="277">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6569878917.2844419</v>
       </c>
       <c r="N35" s="275"/>
       <c r="O35" s="275"/>
@@ -18011,11 +18011,11 @@
       </c>
       <c r="B51" s="316">
         <f>C15+1</f>
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C51" s="277">
         <f>VLOOKUP(C15,B21:C50,2,FALSE)*(1+Terminal_Growth)</f>
-        <v>35801132220.68325</v>
+        <v>45319510142.937477</v>
       </c>
       <c r="D51" s="301">
         <f>Terminal_Growth</f>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="F51" s="277">
         <f>C51*E51</f>
-        <v>20234941376.583008</v>
+        <v>25614766184.070633</v>
       </c>
       <c r="G51" s="299">
         <f>F18</f>
@@ -18035,33 +18035,33 @@
       </c>
       <c r="H51" s="277">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/Equity_Cost</f>
-        <v>208636648767.85114</v>
+        <v>264106471877.46021</v>
       </c>
       <c r="I51" s="415">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/VLOOKUP(C15,B21:H50,COLUMN(H20)-1,FALSE)-1</f>
-        <v>1.9999999999999796E-2</v>
+        <v>2.000000000000024E-2</v>
       </c>
       <c r="J51" s="454"/>
       <c r="K51" s="119">
         <f>1/(1+Equity_Cost)^C15</f>
-        <v>0.70471496766912267</v>
+        <v>0.34997779222393377</v>
       </c>
       <c r="L51" s="277">
         <f t="shared" si="4"/>
-        <v>147029369191.0303</v>
+        <v>92431399939.725983</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
-      <c r="J52" s="468" t="s">
+      <c r="J52" s="469" t="s">
         <v>418</v>
       </c>
-      <c r="K52" s="468"/>
+      <c r="K52" s="469"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>204489167276.40967</v>
+        <v>231572593623.19797</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18085,7 +18085,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>204489167276.40967</v>
+        <v>231572593623.19797</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -19094,11 +19094,11 @@
       </c>
       <c r="D90" s="133">
         <f>Scenarios!D29</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>171.57248846328142</v>
+        <v>221.73100887050737</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19122,11 +19122,11 @@
       </c>
       <c r="D91" s="133">
         <f>Scenarios!D22</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>158.87510787252245</v>
+        <v>183.60962128589512</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19150,11 +19150,11 @@
       </c>
       <c r="D92" s="133">
         <f>Scenarios!D23</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>152.86330883759453</v>
+        <v>167.5989435170556</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19178,11 +19178,11 @@
       </c>
       <c r="D93" s="133">
         <f>Scenarios!D24</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>147.06779159338589</v>
+        <v>153.32823302640435</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19206,11 +19206,11 @@
       </c>
       <c r="D94" s="133">
         <f>Scenarios!D30</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>141.48246965793527</v>
+        <v>140.60619103613459</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19366,7 +19366,7 @@
       <c r="C4" s="449">
         <v>2</v>
       </c>
-      <c r="D4" s="469" t="str">
+      <c r="D4" s="460" t="str">
         <f>"DCF Model Inputs for " &amp; Thesis!C5 &amp; " – " &amp; Thesis!C4 &amp; ": Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. " &amp;
 "Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. " &amp;
 "Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. " &amp;
@@ -19376,16 +19376,16 @@
 "For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario."</f>
         <v>DCF Model Inputs for 000568.SZ – 泸州老窖: Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. Margins should remain constant within each stage and be identical across all scenarios; any variation in outlook should be reflected through adjustments to the growth rate, not the margin. Terminal growth is fixed at 0%, so modify the high-growth duration or rate accordingly to reflect long-term expectations. Specify the FCFE margin (stage-specific if applicable) for all scenarios. For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario.</v>
       </c>
-      <c r="E4" s="469"/>
-      <c r="F4" s="469"/>
-      <c r="G4" s="469"/>
+      <c r="E4" s="460"/>
+      <c r="F4" s="460"/>
+      <c r="G4" s="460"/>
     </row>
     <row r="5" spans="2:7">
       <c r="C5" s="445"/>
-      <c r="D5" s="469"/>
-      <c r="E5" s="469"/>
-      <c r="F5" s="469"/>
-      <c r="G5" s="469"/>
+      <c r="D5" s="460"/>
+      <c r="E5" s="460"/>
+      <c r="F5" s="460"/>
+      <c r="G5" s="460"/>
     </row>
     <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
@@ -19395,10 +19395,10 @@
         <f>DCF!C3&amp;" "&amp;Reporting_currency</f>
         <v>1 CNY</v>
       </c>
-      <c r="D6" s="469"/>
-      <c r="E6" s="469"/>
-      <c r="F6" s="469"/>
-      <c r="G6" s="469"/>
+      <c r="D6" s="460"/>
+      <c r="E6" s="460"/>
+      <c r="F6" s="460"/>
+      <c r="G6" s="460"/>
     </row>
     <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
@@ -19408,10 +19408,10 @@
         <f>Normalized_FCF!G8</f>
         <v>17654238551.57</v>
       </c>
-      <c r="D7" s="469"/>
-      <c r="E7" s="469"/>
-      <c r="F7" s="469"/>
-      <c r="G7" s="469"/>
+      <c r="D7" s="460"/>
+      <c r="E7" s="460"/>
+      <c r="F7" s="460"/>
+      <c r="G7" s="460"/>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
@@ -19421,10 +19421,10 @@
         <f>Normalized_FCF!G19</f>
         <v>12844018055.588684</v>
       </c>
-      <c r="D8" s="469"/>
-      <c r="E8" s="469"/>
-      <c r="F8" s="469"/>
-      <c r="G8" s="469"/>
+      <c r="D8" s="460"/>
+      <c r="E8" s="460"/>
+      <c r="F8" s="460"/>
+      <c r="G8" s="460"/>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
@@ -19434,27 +19434,27 @@
         <f>Normalized_FCF!C19</f>
         <v>13180570558.891336</v>
       </c>
-      <c r="D9" s="469"/>
-      <c r="E9" s="469"/>
-      <c r="F9" s="469"/>
-      <c r="G9" s="469"/>
+      <c r="D9" s="460"/>
+      <c r="E9" s="460"/>
+      <c r="F9" s="460"/>
+      <c r="G9" s="460"/>
     </row>
     <row r="10" spans="2:7">
       <c r="C10" s="448"/>
-      <c r="D10" s="469"/>
-      <c r="E10" s="469"/>
-      <c r="F10" s="469"/>
-      <c r="G10" s="469"/>
+      <c r="D10" s="460"/>
+      <c r="E10" s="460"/>
+      <c r="F10" s="460"/>
+      <c r="G10" s="460"/>
     </row>
     <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
         <v>320</v>
       </c>
       <c r="C11" s="448"/>
-      <c r="D11" s="469"/>
-      <c r="E11" s="469"/>
-      <c r="F11" s="469"/>
-      <c r="G11" s="469"/>
+      <c r="D11" s="460"/>
+      <c r="E11" s="460"/>
+      <c r="F11" s="460"/>
+      <c r="G11" s="460"/>
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
@@ -19464,10 +19464,10 @@
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D12" s="469"/>
-      <c r="E12" s="469"/>
-      <c r="F12" s="469"/>
-      <c r="G12" s="469"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
+      <c r="G12" s="460"/>
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
@@ -19477,10 +19477,10 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D13" s="469"/>
-      <c r="E13" s="469"/>
-      <c r="F13" s="469"/>
-      <c r="G13" s="469"/>
+      <c r="D13" s="460"/>
+      <c r="E13" s="460"/>
+      <c r="F13" s="460"/>
+      <c r="G13" s="460"/>
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
@@ -19490,10 +19490,10 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D14" s="469"/>
-      <c r="E14" s="469"/>
-      <c r="F14" s="469"/>
-      <c r="G14" s="469"/>
+      <c r="D14" s="460"/>
+      <c r="E14" s="460"/>
+      <c r="F14" s="460"/>
+      <c r="G14" s="460"/>
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
@@ -19518,7 +19518,7 @@
         <v>111</v>
       </c>
       <c r="C18" s="137">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E18" s="450" t="s">
         <v>541</v>
@@ -19566,11 +19566,11 @@
       </c>
       <c r="D22" s="325">
         <f>C18</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>158.87510787252245</v>
+        <v>183.60962128589512</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19590,11 +19590,11 @@
       </c>
       <c r="D23" s="325">
         <f>C18</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>152.86330883759453</v>
+        <v>167.5989435170556</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19613,11 +19613,11 @@
       </c>
       <c r="D24" s="325">
         <f>C18</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>147.06779159338589</v>
+        <v>153.32823302640435</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>152.61678933352795</v>
+        <v>167.23340144816069</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19676,11 +19676,11 @@
       </c>
       <c r="D29" s="325">
         <f>C18</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>171.57248846328142</v>
+        <v>221.73100887050737</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19699,11 +19699,11 @@
       </c>
       <c r="D30" s="325">
         <f>C18</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>141.48246965793527</v>
+        <v>140.60619103613459</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>105.2</v>
+        <v>103.39</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.17247969171843658</v>
+        <v>0.22370349845707738</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19779,7 +19779,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-4.2866666015237087E-2</v>
+        <v>-6.7271782565768174E-3</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>154.90342821921132</v>
+        <v>174.07668204091138</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19866,7 +19866,7 @@
       </c>
       <c r="C45" s="150">
         <f>C18</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D45" s="137"/>
       <c r="E45" s="221" t="s">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>155.15545216460865</v>
+        <v>173.55524443059508</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19958,7 +19958,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.10477949826246805</v>
+        <v>9.3238814628432934E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20036,11 +20036,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>70.506794819850384</v>
+        <v>79.233810669509026</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>78.012426135280521</v>
+        <v>86.739441984939162</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20048,7 +20048,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.49638024779618584</v>
+        <v>0.50171705384094056</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20061,11 +20061,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>89.643187626858406</v>
+        <v>100.73882062552742</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>98.348854293525079</v>
+        <v>109.4444872921941</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20073,7 +20073,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.36509568946177962</v>
+        <v>0.37128576895512899</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20107,11 +20107,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>120.60696729816429</v>
+        <v>135.53515851547391</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>131.12448893172376</v>
+        <v>146.05268014903339</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.15350815382753724</v>
+        <v>0.16098653514829631</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20132,11 +20132,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>125.56515202911834</v>
+        <v>141.10704518598044</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>136.36157636797898</v>
+        <v>151.90346952484109</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20144,7 +20144,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.11969942863364436</v>
+        <v>0.12737612100659845</v>
       </c>
     </row>
   </sheetData>
@@ -20192,7 +20192,7 @@
       </c>
       <c r="F3" s="436">
         <f>Thesis!F3</f>
-        <v>46066</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>105.2</v>
+        <v>103.39</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>154848.29450760002</v>
+        <v>152184.07955456999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.17247969171843658</v>
+        <v>0.22370349845707738</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20358,7 +20358,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>154.90342821921132</v>
+        <v>174.07668204091138</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>360</v>
@@ -20410,7 +20410,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>78.012426135280521</v>
+        <v>86.739441984939162</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>438</v>
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>98.348854293525079</v>
+        <v>109.4444872921941</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>439</v>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>131.12448893172376</v>
+        <v>146.05268014903339</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>441</v>
@@ -20458,7 +20458,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>136.36157636797898</v>
+        <v>151.90346952484109</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>440</v>
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.5119249138675079E-2</v>
+        <v>8.6609391714755957E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.9285171102661602E-2</v>
+        <v>3.9972918077183485E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -21227,11 +21227,11 @@
       </c>
       <c r="D118" s="397">
         <f>DCF!D90</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>171.57 CNY</v>
+        <v>221.73 CNY</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21250,11 +21250,11 @@
       </c>
       <c r="D119" s="402">
         <f>DCF!D91</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>158.88 CNY</v>
+        <v>183.61 CNY</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21272,11 +21272,11 @@
       </c>
       <c r="D120" s="402">
         <f>DCF!D92</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>152.86 CNY</v>
+        <v>167.6 CNY</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21294,11 +21294,11 @@
       </c>
       <c r="D121" s="402">
         <f>DCF!D93</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>147.07 CNY</v>
+        <v>153.33 CNY</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21316,11 +21316,11 @@
       </c>
       <c r="D122" s="402">
         <f>DCF!D94</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>141.48 CNY</v>
+        <v>140.61 CNY</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21342,7 +21342,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>154.90342821921132</v>
+        <v>174.07668204091138</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21449,11 +21449,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>70.506794819850384</v>
+        <v>79.233810669509026</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>78.012426135280521</v>
+        <v>86.739441984939162</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21470,11 +21470,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>89.643187626858406</v>
+        <v>100.73882062552742</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>98.348854293525079</v>
+        <v>109.4444872921941</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21510,11 +21510,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>120.60696729816429</v>
+        <v>135.53515851547391</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>131.12448893172376</v>
+        <v>146.05268014903339</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21531,11 +21531,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>125.56515202911834</v>
+        <v>141.10704518598044</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>136.36157636797898</v>
+        <v>151.90346952484109</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696668C8-F0F9-4632-B18B-9F402E99E5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF07B4E1-91DC-424B-8568-4D7662A7C51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF07B4E1-91DC-424B-8568-4D7662A7C51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47F146B-CB5B-471B-938D-4085549D7644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,36 +4989,45 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>103.39</v>
+        <v>103.84</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>152184.07955456999</v>
+        <v>152846.45343792002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.22370349845707738</v>
+        <v>0.22187735344450002</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="463" t="s">
+      <c r="B12" s="461" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="463"/>
-      <c r="D12" s="463"/>
-      <c r="E12" s="463"/>
-      <c r="F12" s="463"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="463" t="s">
+      <c r="B29" s="461" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="463"/>
-      <c r="D29" s="463"/>
-      <c r="E29" s="463"/>
-      <c r="F29" s="463"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="467" t="s">
+      <c r="B30" s="463" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="467"/>
-      <c r="D30" s="467"/>
-      <c r="E30" s="467"/>
-      <c r="F30" s="467"/>
+      <c r="C30" s="463"/>
+      <c r="D30" s="463"/>
+      <c r="E30" s="463"/>
+      <c r="F30" s="463"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="464" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="464"/>
-      <c r="D33" s="464"/>
-      <c r="E33" s="464"/>
-      <c r="F33" s="464"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="464" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="464"/>
-      <c r="D36" s="464"/>
-      <c r="E36" s="464"/>
-      <c r="F36" s="464"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="464" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="464"/>
-      <c r="D40" s="464"/>
-      <c r="E40" s="464"/>
-      <c r="F40" s="464"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="464" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="464"/>
-      <c r="D43" s="464"/>
-      <c r="E43" s="464"/>
-      <c r="F43" s="464"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="464" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="464"/>
-      <c r="D51" s="464"/>
-      <c r="E51" s="464"/>
-      <c r="F51" s="464"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="464" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="463" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="463"/>
-      <c r="D57" s="463"/>
-      <c r="E57" s="463"/>
-      <c r="F57" s="463"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="463" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="463"/>
-      <c r="D58" s="463"/>
-      <c r="E58" s="463"/>
-      <c r="F58" s="463"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.6609391714755957E-2</v>
+        <v>8.6234062108904247E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.9972918077183485E-2</v>
+        <v>3.979969183359014E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="463" t="s">
+      <c r="B73" s="461" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="463"/>
-      <c r="D73" s="463"/>
-      <c r="E73" s="463"/>
-      <c r="F73" s="463"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="463" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="463"/>
-      <c r="D77" s="463"/>
-      <c r="E77" s="463"/>
-      <c r="F77" s="463"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="463" t="s">
+      <c r="B96" s="461" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="463"/>
-      <c r="D96" s="463"/>
-      <c r="E96" s="463"/>
-      <c r="F96" s="463"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="467" t="s">
+      <c r="B97" s="463" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="467"/>
-      <c r="D97" s="467"/>
-      <c r="E97" s="467"/>
-      <c r="F97" s="467"/>
+      <c r="C97" s="463"/>
+      <c r="D97" s="463"/>
+      <c r="E97" s="463"/>
+      <c r="F97" s="463"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="467" t="s">
+      <c r="B98" s="463" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="467"/>
-      <c r="D98" s="467"/>
-      <c r="E98" s="467"/>
-      <c r="F98" s="467"/>
+      <c r="C98" s="463"/>
+      <c r="D98" s="463"/>
+      <c r="E98" s="463"/>
+      <c r="F98" s="463"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="463" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="463"/>
-      <c r="D107" s="463"/>
-      <c r="E107" s="463"/>
-      <c r="F107" s="463"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="463" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="463"/>
-      <c r="D108" s="463"/>
-      <c r="E108" s="463"/>
-      <c r="F108" s="463"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="463" t="s">
+      <c r="B114" s="461" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="463"/>
-      <c r="D114" s="463"/>
-      <c r="E114" s="463"/>
-      <c r="F114" s="463"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="464" t="s">
+      <c r="B124" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="464"/>
-      <c r="D124" s="464"/>
-      <c r="E124" s="464"/>
-      <c r="F124" s="464"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="468" t="s">
+      <c r="B131" s="464" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="468"/>
-      <c r="D131" s="468"/>
-      <c r="E131" s="468"/>
-      <c r="F131" s="468"/>
+      <c r="C131" s="464"/>
+      <c r="D131" s="464"/>
+      <c r="E131" s="464"/>
+      <c r="F131" s="464"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="463" t="s">
+      <c r="B132" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="463"/>
-      <c r="D132" s="463"/>
-      <c r="E132" s="463"/>
-      <c r="F132" s="463"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="462" t="s">
+      <c r="B149" s="468" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="463"/>
-      <c r="D149" s="463"/>
-      <c r="E149" s="463"/>
-      <c r="F149" s="463"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="464" t="s">
+      <c r="B158" s="462" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="464"/>
-      <c r="D158" s="464"/>
-      <c r="E158" s="464"/>
-      <c r="F158" s="464"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="461" t="s">
+      <c r="B161" s="467" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="461"/>
-      <c r="D161" s="461"/>
-      <c r="E161" s="461"/>
-      <c r="F161" s="461"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="461" t="s">
+      <c r="B162" s="467" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="461"/>
-      <c r="D162" s="461"/>
-      <c r="E162" s="461"/>
-      <c r="F162" s="461"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.9972918077183485E-2</v>
+        <v>3.979969183359014E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.9972918077183485E-2</v>
+        <v>3.979969183359014E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.7007159299738852E-2</v>
+        <v>4.6803449537750383E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.6609391714755957E-2</v>
+        <v>8.6234062108904247E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.4397908724631668E-2</v>
+        <v>8.4032162779657818E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.1624703375546587E-2</v>
+        <v>8.1270975365926049E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8693762254217795E-2</v>
+        <v>8.8309399840750938E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7319646457794983E-2</v>
+        <v>8.6941238898992898E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>103.39</v>
+        <v>103.84</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.22370349845707738</v>
+        <v>0.22187735344450002</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>103.39</v>
+        <v>103.84</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>152184.07955456999</v>
+        <v>152846.45343792002</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.22370349845707738</v>
+        <v>0.22187735344450002</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.6609391714755957E-2</v>
+        <v>8.6234062108904247E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.9972918077183485E-2</v>
+        <v>3.979969183359014E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,12 +21649,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21669,15 +21672,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47F146B-CB5B-471B-938D-4085549D7644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC791196-A29C-425B-A0AE-07410D6DF753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,55 +4989,55 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>103.84</v>
+        <v>105.3</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>152846.45343792002</v>
+        <v>154995.48870389999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.22187735344450002</v>
+        <v>0.2160259300061575</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="463" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="463"/>
+      <c r="D12" s="463"/>
+      <c r="E12" s="463"/>
+      <c r="F12" s="463"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="463" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="463"/>
+      <c r="D29" s="463"/>
+      <c r="E29" s="463"/>
+      <c r="F29" s="463"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="463" t="s">
+      <c r="B30" s="467" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="463"/>
-      <c r="D30" s="463"/>
-      <c r="E30" s="463"/>
-      <c r="F30" s="463"/>
+      <c r="C30" s="467"/>
+      <c r="D30" s="467"/>
+      <c r="E30" s="467"/>
+      <c r="F30" s="467"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="464" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="464"/>
+      <c r="D33" s="464"/>
+      <c r="E33" s="464"/>
+      <c r="F33" s="464"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="464" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="464"/>
+      <c r="D36" s="464"/>
+      <c r="E36" s="464"/>
+      <c r="F36" s="464"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="464" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="464"/>
+      <c r="D40" s="464"/>
+      <c r="E40" s="464"/>
+      <c r="F40" s="464"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="464" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="464"/>
+      <c r="D43" s="464"/>
+      <c r="E43" s="464"/>
+      <c r="F43" s="464"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="464" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="464"/>
+      <c r="D51" s="464"/>
+      <c r="E51" s="464"/>
+      <c r="F51" s="464"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="464" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="463" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="463"/>
+      <c r="D57" s="463"/>
+      <c r="E57" s="463"/>
+      <c r="F57" s="463"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="463" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="463"/>
+      <c r="D58" s="463"/>
+      <c r="E58" s="463"/>
+      <c r="F58" s="463"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.6234062108904247E-2</v>
+        <v>8.5038414144241389E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.979969183359014E-2</v>
+        <v>3.9247863247863252E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="463" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="463"/>
+      <c r="D73" s="463"/>
+      <c r="E73" s="463"/>
+      <c r="F73" s="463"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="463" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="463"/>
+      <c r="D77" s="463"/>
+      <c r="E77" s="463"/>
+      <c r="F77" s="463"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="463" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="463"/>
+      <c r="D96" s="463"/>
+      <c r="E96" s="463"/>
+      <c r="F96" s="463"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="463" t="s">
+      <c r="B97" s="467" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="463"/>
-      <c r="D97" s="463"/>
-      <c r="E97" s="463"/>
-      <c r="F97" s="463"/>
+      <c r="C97" s="467"/>
+      <c r="D97" s="467"/>
+      <c r="E97" s="467"/>
+      <c r="F97" s="467"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="463" t="s">
+      <c r="B98" s="467" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="463"/>
-      <c r="D98" s="463"/>
-      <c r="E98" s="463"/>
-      <c r="F98" s="463"/>
+      <c r="C98" s="467"/>
+      <c r="D98" s="467"/>
+      <c r="E98" s="467"/>
+      <c r="F98" s="467"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="463" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="463"/>
+      <c r="D107" s="463"/>
+      <c r="E107" s="463"/>
+      <c r="F107" s="463"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="463"/>
+      <c r="D108" s="463"/>
+      <c r="E108" s="463"/>
+      <c r="F108" s="463"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="463" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="463"/>
+      <c r="D114" s="463"/>
+      <c r="E114" s="463"/>
+      <c r="F114" s="463"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="464" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="464"/>
+      <c r="D124" s="464"/>
+      <c r="E124" s="464"/>
+      <c r="F124" s="464"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="464" t="s">
+      <c r="B131" s="468" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="464"/>
-      <c r="D131" s="464"/>
-      <c r="E131" s="464"/>
-      <c r="F131" s="464"/>
+      <c r="C131" s="468"/>
+      <c r="D131" s="468"/>
+      <c r="E131" s="468"/>
+      <c r="F131" s="468"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="463"/>
+      <c r="D132" s="463"/>
+      <c r="E132" s="463"/>
+      <c r="F132" s="463"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="468" t="s">
+      <c r="B149" s="462" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="463"/>
+      <c r="D149" s="463"/>
+      <c r="E149" s="463"/>
+      <c r="F149" s="463"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="464" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="464"/>
+      <c r="D158" s="464"/>
+      <c r="E158" s="464"/>
+      <c r="F158" s="464"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="461" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="461"/>
+      <c r="D161" s="461"/>
+      <c r="E161" s="461"/>
+      <c r="F161" s="461"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="461" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="461"/>
+      <c r="D162" s="461"/>
+      <c r="E162" s="461"/>
+      <c r="F162" s="461"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.979969183359014E-2</v>
+        <v>3.9247863247863252E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.979969183359014E-2</v>
+        <v>3.9247863247863252E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.6803449537750383E-2</v>
+        <v>4.6154512820512819E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.6234062108904247E-2</v>
+        <v>8.5038414144241389E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.4032162779657818E-2</v>
+        <v>8.2867044473311197E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.1270975365926049E-2</v>
+        <v>8.0144141329513405E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8309399840750938E-2</v>
+        <v>8.7084977012949469E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6941238898992898E-2</v>
+        <v>8.5735785824040123E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>103.84</v>
+        <v>105.3</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.22187735344450002</v>
+        <v>0.2160259300061575</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>103.84</v>
+        <v>105.3</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>152846.45343792002</v>
+        <v>154995.48870389999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.22187735344450002</v>
+        <v>0.2160259300061575</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.6234062108904247E-2</v>
+        <v>8.5038414144241389E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.979969183359014E-2</v>
+        <v>3.9247863247863252E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,15 +21649,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21672,12 +21669,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC791196-A29C-425B-A0AE-07410D6DF753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73CEA6B3-BE3A-4756-86E4-322A0D8F0F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -96,9 +96,6 @@
   </si>
   <si>
     <t>Other LT liabilities</t>
-  </si>
-  <si>
-    <t>Biological assets</t>
   </si>
   <si>
     <t>Intangible assets</t>
@@ -3252,16 +3249,19 @@
     <t>Sales/Total Assets g Projection</t>
   </si>
   <si>
+    <t>Biological/Mineral assets</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>泸州老窖</t>
+  </si>
+  <si>
     <t>000568.SZ</t>
   </si>
   <si>
     <t>CNY</t>
-  </si>
-  <si>
-    <t>泸州老窖</t>
-  </si>
-  <si>
-    <t>CN</t>
   </si>
 </sst>
 </file>
@@ -4986,35 +4986,35 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -5335,7 +5335,7 @@
   <sheetData>
     <row r="2" spans="1:9" ht="13.9">
       <c r="A2" s="200" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
@@ -5348,7 +5348,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="E3" s="428" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F3" s="429">
         <v>46105</v>
@@ -5356,64 +5356,64 @@
     </row>
     <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="421" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C4" s="420" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E4" s="430" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F4" s="431" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E5" s="433" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F5" s="432" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="B6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
     <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
     <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C8" s="47">
-        <v>105.3</v>
+        <v>106.26</v>
       </c>
       <c r="E8" s="32"/>
     </row>
     <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C9" s="48">
         <v>1471941963</v>
@@ -5421,18 +5421,18 @@
     </row>
     <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>154995.48870389999</v>
+        <v>156408.55298838002</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.2160259300061575</v>
+        <v>0.21223826010541716</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="463" t="s">
-        <v>353</v>
-      </c>
-      <c r="C12" s="463"/>
-      <c r="D12" s="463"/>
-      <c r="E12" s="463"/>
-      <c r="F12" s="463"/>
+      <c r="B12" s="462" t="s">
+        <v>352</v>
+      </c>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5457,13 +5457,13 @@
     </row>
     <row r="15" spans="1:9">
       <c r="B15" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C15" s="417" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E15" s="253" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -5472,13 +5472,13 @@
     </row>
     <row r="16" spans="1:9">
       <c r="B16" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C16" s="417" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E16" s="416">
         <v>1</v>
@@ -5486,16 +5486,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C17" s="456">
         <v>0.02</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E17" s="224" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5508,7 +5508,7 @@
         <v>174.07668204091138</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E18" s="418">
         <v>6</v>
@@ -5516,14 +5516,14 @@
     </row>
     <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C19" s="31" t="str">
         <f>IF(Terminal_Growth&lt;2%, "Lower than Inflation rate", IF(Terminal_Growth&lt;5%, "Low growth", IF(Terminal_Growth&lt;8%, "Medium growth", "High growth")))</f>
         <v>Low growth</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E19" s="419">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -5536,14 +5536,14 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C21" s="254" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
         <v xml:space="preserve"> (CNY)</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E21" s="442">
         <v>3</v>
@@ -5551,14 +5551,14 @@
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C22" s="255">
         <f>E140</f>
         <v>86.739441984939162</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E22" s="79">
         <v>0.3</v>
@@ -5566,14 +5566,14 @@
     </row>
     <row r="23" spans="1:6">
       <c r="B23" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C23" s="256">
         <f>E141</f>
         <v>109.4444872921941</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E23" s="443">
         <v>0.2</v>
@@ -5581,14 +5581,14 @@
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C24" s="256">
         <f>E144</f>
         <v>146.05268014903339</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E24" s="443">
         <v>8.6999999999999994E-2</v>
@@ -5596,14 +5596,14 @@
     </row>
     <row r="25" spans="1:6">
       <c r="B25" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C25" s="256">
         <f>E145</f>
         <v>151.90346952484109</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E25" s="444">
         <v>7.2499999999999995E-2</v>
@@ -5615,7 +5615,7 @@
     </row>
     <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="200" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B27" s="34"/>
       <c r="C27" s="34"/>
@@ -5624,26 +5624,26 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="463" t="s">
-        <v>354</v>
-      </c>
-      <c r="C29" s="463"/>
-      <c r="D29" s="463"/>
-      <c r="E29" s="463"/>
-      <c r="F29" s="463"/>
+      <c r="B29" s="462" t="s">
+        <v>353</v>
+      </c>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="467" t="s">
-        <v>266</v>
-      </c>
-      <c r="C30" s="467"/>
-      <c r="D30" s="467"/>
-      <c r="E30" s="467"/>
-      <c r="F30" s="467"/>
+      <c r="B30" s="466" t="s">
+        <v>265</v>
+      </c>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C32" s="105">
         <f>scaling_factor</f>
@@ -5651,17 +5651,17 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="464" t="s">
-        <v>196</v>
-      </c>
-      <c r="C33" s="464"/>
-      <c r="D33" s="464"/>
-      <c r="E33" s="464"/>
-      <c r="F33" s="464"/>
+      <c r="B33" s="463" t="s">
+        <v>195</v>
+      </c>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C34" s="285">
         <f>Normalized_FCF!C8</f>
@@ -5677,17 +5677,17 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="464" t="s">
-        <v>198</v>
-      </c>
-      <c r="C36" s="464"/>
-      <c r="D36" s="464"/>
-      <c r="E36" s="464"/>
-      <c r="F36" s="464"/>
+      <c r="B36" s="463" t="s">
+        <v>197</v>
+      </c>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C37" s="285">
         <f>Normalized_FCF!C15</f>
@@ -5700,7 +5700,7 @@
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="49" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C38" s="285">
         <f>Normalized_FCF!C16</f>
@@ -5712,17 +5712,17 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="464" t="s">
-        <v>201</v>
-      </c>
-      <c r="C40" s="464"/>
-      <c r="D40" s="464"/>
-      <c r="E40" s="464"/>
-      <c r="F40" s="464"/>
+      <c r="B40" s="463" t="s">
+        <v>200</v>
+      </c>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C41" s="285">
         <f>Normalized_FCF!C9</f>
@@ -5734,17 +5734,17 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="464" t="s">
-        <v>205</v>
-      </c>
-      <c r="C43" s="464"/>
-      <c r="D43" s="464"/>
-      <c r="E43" s="464"/>
-      <c r="F43" s="464"/>
+      <c r="B43" s="463" t="s">
+        <v>204</v>
+      </c>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C44" s="286">
         <f>Normalized_FCF!C46</f>
@@ -5759,7 +5759,7 @@
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="44" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C45" s="286">
         <f>Normalized_FCF!C45</f>
@@ -5774,7 +5774,7 @@
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="44" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C46" s="285">
         <f>Normalized_FCF!C10</f>
@@ -5787,12 +5787,12 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="44" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C49" s="285">
         <f>Normalized_FCF!C13</f>
@@ -5804,17 +5804,17 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="464" t="s">
-        <v>206</v>
-      </c>
-      <c r="C51" s="464"/>
-      <c r="D51" s="464"/>
-      <c r="E51" s="464"/>
-      <c r="F51" s="464"/>
+      <c r="B51" s="463" t="s">
+        <v>205</v>
+      </c>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C52" s="285">
         <f>Normalized_FCF!C12</f>
@@ -5826,17 +5826,17 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="464" t="s">
-        <v>265</v>
-      </c>
-      <c r="C54" s="465"/>
-      <c r="D54" s="465"/>
-      <c r="E54" s="465"/>
-      <c r="F54" s="465"/>
+      <c r="B54" s="463" t="s">
+        <v>264</v>
+      </c>
+      <c r="C54" s="464"/>
+      <c r="D54" s="464"/>
+      <c r="E54" s="464"/>
+      <c r="F54" s="464"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C55" s="285">
         <f>Normalized_FCF!C17</f>
@@ -5848,26 +5848,26 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="463" t="s">
-        <v>270</v>
-      </c>
-      <c r="C57" s="463"/>
-      <c r="D57" s="463"/>
-      <c r="E57" s="463"/>
-      <c r="F57" s="463"/>
+      <c r="B57" s="462" t="s">
+        <v>269</v>
+      </c>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="463" t="s">
-        <v>282</v>
-      </c>
-      <c r="C58" s="463"/>
-      <c r="D58" s="463"/>
-      <c r="E58" s="463"/>
-      <c r="F58" s="463"/>
+      <c r="B58" s="462" t="s">
+        <v>281</v>
+      </c>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C60" s="285">
         <f>Normalized_FCF!G19</f>
@@ -5880,7 +5880,7 @@
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="44" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C61" s="285">
         <f>Normalized_FCF!C19</f>
@@ -5893,24 +5893,24 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="204" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.5038414144241389E-2</v>
+        <v>8.4270139369363992E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="204" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.9247863247863252E-2</v>
+        <v>3.889328063241107E-2</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F63" s="258">
         <f>Normalized_FCF!C90</f>
@@ -5919,18 +5919,18 @@
     </row>
     <row r="65" spans="1:6">
       <c r="B65" s="192" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C65" s="264" t="s">
+        <v>324</v>
+      </c>
+      <c r="D65" s="264" t="s">
         <v>325</v>
-      </c>
-      <c r="D65" s="264" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="44" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!E119</f>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="200" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -5998,18 +5998,18 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="463" t="s">
-        <v>476</v>
-      </c>
-      <c r="C73" s="463"/>
-      <c r="D73" s="463"/>
-      <c r="E73" s="463"/>
-      <c r="F73" s="463"/>
+      <c r="B73" s="462" t="s">
+        <v>475</v>
+      </c>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -6018,23 +6018,23 @@
     <row r="76" spans="1:6">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="463" t="s">
-        <v>271</v>
-      </c>
-      <c r="C77" s="463"/>
-      <c r="D77" s="463"/>
-      <c r="E77" s="463"/>
-      <c r="F77" s="463"/>
+      <c r="B77" s="462" t="s">
+        <v>270</v>
+      </c>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C78" s="285">
         <f>DCF!F4</f>
@@ -6048,7 +6048,7 @@
     <row r="79" spans="1:6">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -6062,7 +6062,7 @@
     <row r="80" spans="1:6">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C80" s="337">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -6072,7 +6072,7 @@
     <row r="81" spans="1:6">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C81" s="338">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -6085,13 +6085,13 @@
     <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C84" s="285">
         <f>DCF!F5</f>
@@ -6105,7 +6105,7 @@
     <row r="85" spans="1:6">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C85" s="291">
         <f>BS!C66</f>
@@ -6119,7 +6119,7 @@
     <row r="86" spans="1:6">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -6136,13 +6136,13 @@
     <row r="88" spans="1:6">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C89" s="285">
         <f>DCF!F6</f>
@@ -6156,7 +6156,7 @@
     <row r="90" spans="1:6">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -6173,7 +6173,7 @@
     <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
@@ -6186,7 +6186,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="200" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -6198,40 +6198,40 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="463" t="s">
-        <v>483</v>
-      </c>
-      <c r="C96" s="463"/>
-      <c r="D96" s="463"/>
-      <c r="E96" s="463"/>
-      <c r="F96" s="463"/>
+      <c r="B96" s="462" t="s">
+        <v>482</v>
+      </c>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="467" t="s">
-        <v>482</v>
-      </c>
-      <c r="C97" s="467"/>
-      <c r="D97" s="467"/>
-      <c r="E97" s="467"/>
-      <c r="F97" s="467"/>
+      <c r="B97" s="466" t="s">
+        <v>481</v>
+      </c>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="467" t="s">
-        <v>481</v>
-      </c>
-      <c r="C98" s="467"/>
-      <c r="D98" s="467"/>
-      <c r="E98" s="467"/>
-      <c r="F98" s="467"/>
+      <c r="B98" s="466" t="s">
+        <v>480</v>
+      </c>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C101" s="211">
         <f>E25+C103</f>
@@ -6240,7 +6240,7 @@
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="229" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C102" s="263">
         <f>E25</f>
@@ -6249,7 +6249,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="229" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C103" s="263">
         <f>IF(C15="Y",1%,0)+IF(C16="Y",1%,0)</f>
@@ -6258,7 +6258,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="44" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C104" s="211">
         <f>Terminal_Growth</f>
@@ -6267,36 +6267,36 @@
     </row>
     <row r="106" spans="2:6">
       <c r="B106" s="250" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="463" t="s">
+      <c r="B107" s="462" t="s">
+        <v>282</v>
+      </c>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="463"/>
-      <c r="D107" s="463"/>
-      <c r="E107" s="463"/>
-      <c r="F107" s="463"/>
-    </row>
-    <row r="108" spans="2:6">
-      <c r="B108" s="463" t="s">
-        <v>284</v>
-      </c>
-      <c r="C108" s="463"/>
-      <c r="D108" s="463"/>
-      <c r="E108" s="463"/>
-      <c r="F108" s="463"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
@@ -6309,7 +6309,7 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="44" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
@@ -6321,34 +6321,34 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="463" t="s">
-        <v>489</v>
-      </c>
-      <c r="C114" s="463"/>
-      <c r="D114" s="463"/>
-      <c r="E114" s="463"/>
-      <c r="F114" s="463"/>
+      <c r="B114" s="462" t="s">
+        <v>488</v>
+      </c>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="12.4">
       <c r="B117" s="342" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C117" s="342" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D117" s="342" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E117" s="342" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F117" s="342" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="118" spans="2:6">
@@ -6462,17 +6462,17 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="464" t="s">
-        <v>355</v>
-      </c>
-      <c r="C124" s="464"/>
-      <c r="D124" s="464"/>
-      <c r="E124" s="464"/>
-      <c r="F124" s="464"/>
+      <c r="B124" s="463" t="s">
+        <v>354</v>
+      </c>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
@@ -6484,17 +6484,17 @@
       </c>
     </row>
     <row r="127" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B127" s="466" t="s">
-        <v>356</v>
-      </c>
-      <c r="C127" s="466"/>
-      <c r="D127" s="466"/>
-      <c r="E127" s="466"/>
-      <c r="F127" s="466"/>
+      <c r="B127" s="465" t="s">
+        <v>355</v>
+      </c>
+      <c r="C127" s="465"/>
+      <c r="D127" s="465"/>
+      <c r="E127" s="465"/>
+      <c r="F127" s="465"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B129" s="34"/>
       <c r="C129" s="34"/>
@@ -6503,31 +6503,31 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="468" t="s">
-        <v>285</v>
-      </c>
-      <c r="C131" s="468"/>
-      <c r="D131" s="468"/>
-      <c r="E131" s="468"/>
-      <c r="F131" s="468"/>
+      <c r="B131" s="467" t="s">
+        <v>284</v>
+      </c>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="463" t="s">
-        <v>357</v>
-      </c>
-      <c r="C132" s="463"/>
-      <c r="D132" s="463"/>
-      <c r="E132" s="463"/>
-      <c r="F132" s="463"/>
+      <c r="B132" s="462" t="s">
+        <v>356</v>
+      </c>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C135" s="202">
         <f>E21</f>
@@ -6536,7 +6536,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="194" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
@@ -6549,33 +6549,33 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
     <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="340" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C139" s="340" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="340" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E139" s="341" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (CNY)</v>
       </c>
       <c r="F139" s="341" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="336" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
@@ -6596,7 +6596,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="336" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
@@ -6624,26 +6624,26 @@
     </row>
     <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="340" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C143" s="340" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="340" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E143" s="341" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (CNY)</v>
       </c>
       <c r="F143" s="341" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="B144" s="336" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C144" s="333">
         <f>Scenarios!C66</f>
@@ -6664,7 +6664,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="B145" s="336" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C145" s="333">
         <f>Scenarios!C67</f>
@@ -6685,7 +6685,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="200" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B147" s="34"/>
       <c r="C147" s="34"/>
@@ -6694,98 +6694,98 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="462" t="s">
-        <v>358</v>
-      </c>
-      <c r="C149" s="463"/>
-      <c r="D149" s="463"/>
-      <c r="E149" s="463"/>
-      <c r="F149" s="463"/>
+      <c r="B149" s="461" t="s">
+        <v>357</v>
+      </c>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="465" t="s">
-        <v>293</v>
-      </c>
-      <c r="C152" s="465"/>
-      <c r="D152" s="465"/>
-      <c r="E152" s="465"/>
-      <c r="F152" s="465"/>
+      <c r="B152" s="464" t="s">
+        <v>292</v>
+      </c>
+      <c r="C152" s="464"/>
+      <c r="D152" s="464"/>
+      <c r="E152" s="464"/>
+      <c r="F152" s="464"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="196" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="196" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="464" t="s">
-        <v>436</v>
-      </c>
-      <c r="C158" s="464"/>
-      <c r="D158" s="464"/>
-      <c r="E158" s="464"/>
-      <c r="F158" s="464"/>
+      <c r="B158" s="463" t="s">
+        <v>435</v>
+      </c>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="461" t="s">
+      <c r="B161" s="460" t="s">
+        <v>293</v>
+      </c>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="461"/>
-      <c r="D161" s="461"/>
-      <c r="E161" s="461"/>
-      <c r="F161" s="461"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="461" t="s">
-        <v>295</v>
-      </c>
-      <c r="C162" s="461"/>
-      <c r="D162" s="461"/>
-      <c r="E162" s="461"/>
-      <c r="F162" s="461"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="196" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="196" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="196" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -6904,7 +6904,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -6920,7 +6920,7 @@
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="103">
         <v>1</v>
@@ -6948,7 +6948,7 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="287">
         <f>3888116183.93+4753755581.18</f>
@@ -6970,7 +6970,7 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="287">
         <f>1100779964.56+C7</f>
@@ -6992,7 +6992,7 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="66" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7" s="288">
         <v>3538382615.9899998</v>
@@ -7012,7 +7012,7 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" s="287">
         <v>260975311.09999999</v>
@@ -7032,7 +7032,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C9" s="287"/>
       <c r="D9" s="287"/>
@@ -7048,7 +7048,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C10" s="287"/>
       <c r="D10" s="287"/>
@@ -7064,7 +7064,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="287"/>
       <c r="D11" s="287"/>
@@ -7080,7 +7080,7 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" s="287">
         <v>305448236.36000001</v>
@@ -7100,7 +7100,7 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C13" s="287">
         <v>797923434.29999995</v>
@@ -7120,7 +7120,7 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="287">
         <v>4707520248.1499996</v>
@@ -7140,7 +7140,7 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="289">
         <v>13497778570.889999</v>
@@ -7160,7 +7160,7 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" s="287">
         <v>24792094.879999999</v>
@@ -7180,13 +7180,13 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C19" s="287"/>
       <c r="D19" s="287"/>
@@ -7202,7 +7202,7 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C20" s="287"/>
       <c r="D20" s="287"/>
@@ -7218,7 +7218,7 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C21" s="287"/>
       <c r="D21" s="287"/>
@@ -7234,7 +7234,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="26" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C22" s="287">
         <v>19181768363.650002</v>
@@ -7254,7 +7254,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C23" s="287">
         <v>-1382505932.55</v>
@@ -7274,7 +7274,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="26" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C24" s="287">
         <v>-10328853037.68</v>
@@ -7317,15 +7317,15 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C28" s="270">
         <f>BS!C4</f>
@@ -7347,7 +7347,7 @@
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" s="270">
         <f>BS!C6</f>
@@ -7368,7 +7368,7 @@
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30" s="271">
         <f>BS!C33+BS!C42</f>
@@ -7389,7 +7389,7 @@
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="271">
         <f>BS!G27</f>
@@ -7410,7 +7410,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C32" s="270">
         <f>BS!G28</f>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="34" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C34" s="35"/>
       <c r="D34" s="35"/>
@@ -7447,7 +7447,7 @@
     </row>
     <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="2:13">
@@ -7501,7 +7501,7 @@
     </row>
     <row r="37" spans="2:13">
       <c r="B37" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37" s="270">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -7550,7 +7550,7 @@
     </row>
     <row r="38" spans="2:13">
       <c r="B38" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C38" s="267">
         <f>IF(C36="","",C36+C37)</f>
@@ -7599,7 +7599,7 @@
     </row>
     <row r="39" spans="2:13">
       <c r="B39" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C39" s="270">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -7648,7 +7648,7 @@
     </row>
     <row r="40" spans="2:13">
       <c r="B40" s="66" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C40" s="282">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -7697,7 +7697,7 @@
     </row>
     <row r="41" spans="2:13">
       <c r="B41" s="66" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C41" s="282">
         <f>IF(C$4="","",C39-C40)</f>
@@ -7746,7 +7746,7 @@
     </row>
     <row r="42" spans="2:13">
       <c r="B42" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42" s="270">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -7795,7 +7795,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C43" s="271">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7844,7 +7844,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C44" s="290">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7893,7 +7893,7 @@
     </row>
     <row r="45" spans="2:13">
       <c r="B45" s="38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C45" s="285">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -7942,7 +7942,7 @@
     </row>
     <row r="46" spans="2:13">
       <c r="B46" s="38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C46" s="270">
         <f>IF(C$4="","",-C14)</f>
@@ -7991,7 +7991,7 @@
     </row>
     <row r="47" spans="2:13">
       <c r="B47" s="41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C47" s="271">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -8040,7 +8040,7 @@
     </row>
     <row r="48" spans="2:13">
       <c r="B48" s="27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C48" s="270">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -8089,12 +8089,12 @@
     </row>
     <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="2:13">
       <c r="B51" s="38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C51" s="270">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -8143,7 +8143,7 @@
     </row>
     <row r="52" spans="2:13">
       <c r="B52" s="38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C52" s="270">
         <f>IF(C$4="","",C13)</f>
@@ -8192,12 +8192,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C55" s="285">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -8246,7 +8246,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C56" s="285">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -8295,7 +8295,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C57" s="285">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -8344,7 +8344,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C58" s="285">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -8393,13 +8393,13 @@
     </row>
     <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13">
       <c r="B61" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C61" s="270">
         <f>IF(C$4="","",-C19)</f>
@@ -8448,7 +8448,7 @@
     </row>
     <row r="62" spans="2:13">
       <c r="B62" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C62" s="270">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
@@ -8497,7 +8497,7 @@
     </row>
     <row r="63" spans="2:13">
       <c r="B63" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C63" s="270">
         <f>IF(C$4="","",-C21)</f>
@@ -8546,7 +8546,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="26" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C64" s="270">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8595,7 +8595,7 @@
     </row>
     <row r="65" spans="2:13">
       <c r="B65" s="23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
@@ -8644,7 +8644,7 @@
     </row>
     <row r="67" spans="2:13">
       <c r="B67" s="88" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -8699,7 +8699,7 @@
     </row>
     <row r="69" spans="2:13">
       <c r="B69" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C69" s="89">
         <f>IF(D$36="","",C38/D38-1)</f>
@@ -8798,7 +8798,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C71" s="98">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8897,7 +8897,7 @@
     </row>
     <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C74" s="35"/>
       <c r="D74" s="35"/>
@@ -8913,7 +8913,7 @@
     </row>
     <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C75" s="9"/>
     </row>
@@ -8968,7 +8968,7 @@
     </row>
     <row r="77" spans="2:13">
       <c r="B77" s="90" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C77" s="260">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
@@ -9002,7 +9002,7 @@
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="90" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C78" s="260">
         <f t="shared" si="40"/>
@@ -9036,7 +9036,7 @@
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C79" s="259">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
@@ -9085,7 +9085,7 @@
     </row>
     <row r="80" spans="2:13">
       <c r="B80" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C80" s="259">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
@@ -9149,7 +9149,7 @@
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{87139493-416E-4F03-A3A9-B1C3E5C019E4}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9177,7 +9177,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1" s="96">
         <v>45838</v>
@@ -9193,7 +9193,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="76" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -9204,27 +9204,27 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="164" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="165" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="164" t="s">
-        <v>113</v>
-      </c>
-      <c r="D3" s="165" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>155</v>
-      </c>
       <c r="G3" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H3" s="165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="18">
         <f>16077566.15+1411989312.86+42044835.12</f>
@@ -9235,7 +9235,7 @@
       </c>
       <c r="E4" s="24"/>
       <c r="F4" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G4" s="18">
         <v>35451080327.050003</v>
@@ -9246,7 +9246,7 @@
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="18">
         <v>0</v>
@@ -9256,7 +9256,7 @@
       </c>
       <c r="E5" s="24"/>
       <c r="F5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" s="18">
         <v>0</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="E6" s="24"/>
       <c r="F6" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G6" s="18">
         <v>0</v>
@@ -9288,7 +9288,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" s="18">
         <v>0</v>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="E7" s="24"/>
       <c r="F7" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G7" s="18">
         <v>1610560917.24</v>
@@ -9309,7 +9309,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C8" s="18">
         <v>0</v>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G8" s="18">
         <v>0</v>
@@ -9330,7 +9330,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="18">
         <v>228470687.43000001</v>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="E9" s="24"/>
       <c r="F9" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G9" s="18">
         <v>0</v>
@@ -9360,7 +9360,7 @@
         <v>0.9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G10" s="18">
         <v>0</v>
@@ -9383,7 +9383,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12" s="78">
         <f>SUM(C4:C11)</f>
@@ -9394,7 +9394,7 @@
         <v>7799389157.8345003</v>
       </c>
       <c r="F12" s="77" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G12" s="78">
         <f>SUM(G4:G10)</f>
@@ -9412,27 +9412,27 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C14" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D14" s="165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G14" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H14" s="165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C15" s="18">
         <v>0</v>
@@ -9441,7 +9441,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G15" s="18">
         <v>0</v>
@@ -9452,7 +9452,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="18">
         <v>0</v>
@@ -9461,7 +9461,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G16" s="18">
         <v>0</v>
@@ -9472,7 +9472,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C17" s="18">
         <v>0</v>
@@ -9481,7 +9481,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G17" s="18">
         <v>0</v>
@@ -9492,7 +9492,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="18">
         <v>0</v>
@@ -9501,7 +9501,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G18" s="18">
         <v>0</v>
@@ -9512,7 +9512,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" s="18">
         <f>8815147343.06+1165735552.56+24433390.1</f>
@@ -9522,7 +9522,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G19" s="18">
         <f>2836552287.45+438338355.95</f>
@@ -9534,7 +9534,7 @@
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
-        <v>16</v>
+        <v>552</v>
       </c>
       <c r="C20" s="18">
         <v>0</v>
@@ -9543,7 +9543,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G20" s="18">
         <v>0</v>
@@ -9554,7 +9554,7 @@
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" s="18">
         <v>3452040130.0700002</v>
@@ -9563,7 +9563,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G21" s="18">
         <v>48802205.539999999</v>
@@ -9574,7 +9574,7 @@
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="18">
         <v>229979417.63</v>
@@ -9586,7 +9586,7 @@
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C23" s="18">
         <f>1322375.9+588898590.92</f>
@@ -9599,7 +9599,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="77" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C24" s="78">
         <f>SUM(C15:C23)</f>
@@ -9610,7 +9610,7 @@
         <v>1380115110.9425001</v>
       </c>
       <c r="F24" s="77" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G24" s="78">
         <f>SUM(G15:G21)</f>
@@ -9623,19 +9623,19 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C26" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F26" s="166" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G26" s="167" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H26" s="168" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1">
@@ -9646,7 +9646,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="169" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G27" s="82">
         <f>G32-G30</f>
@@ -9665,7 +9665,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="171" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G28" s="287">
         <v>140066503.38999999</v>
@@ -9680,7 +9680,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="172" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -9699,7 +9699,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="169" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G30" s="82">
         <f>C33+C42</f>
@@ -9709,14 +9709,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C31" s="78">
         <f>SUM(C27:C30)</f>
         <v>0</v>
       </c>
       <c r="F31" s="172" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G31" s="173">
         <f>C31+C40</f>
@@ -9733,7 +9733,7 @@
         <v>20518442745.68</v>
       </c>
       <c r="F32" s="174" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G32" s="175">
         <f>G35+G40</f>
@@ -9759,24 +9759,24 @@
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G34" s="179" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H34" s="180" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C35" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F35" s="181" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G35" s="175">
         <f>C12+C24</f>
@@ -9795,7 +9795,7 @@
         <v>2728700000</v>
       </c>
       <c r="F36" s="172" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G36" s="173">
         <f>C4+C15</f>
@@ -9811,7 +9811,7 @@
         <v>21014302.059999999</v>
       </c>
       <c r="F37" s="172" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G37" s="173">
         <f>C6</f>
@@ -9827,7 +9827,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="172" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G38" s="173">
         <f>C7+C17</f>
@@ -9843,7 +9843,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="172" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G39" s="173">
         <f>C7+C17+C19+C20</f>
@@ -9856,14 +9856,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="77" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C40" s="78">
         <f>SUM(C36:C39)</f>
         <v>2749714302.0599999</v>
       </c>
       <c r="F40" s="181" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G40" s="175">
         <f>G12+G24</f>
@@ -9883,7 +9883,7 @@
         <v>241472161.82000017</v>
       </c>
       <c r="F41" s="172" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G41" s="173">
         <f>C70</f>
@@ -9896,13 +9896,13 @@
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="80" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C42" s="81">
         <v>2991186463.8800001</v>
       </c>
       <c r="F42" s="183" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G42" s="184">
         <f>C82</f>
@@ -9915,7 +9915,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="76" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C44" s="35"/>
       <c r="D44" s="35"/>
@@ -9926,21 +9926,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C45" s="209" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D45" s="164" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F45" s="226" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C46" s="73">
         <f>G29</f>
@@ -9972,20 +9972,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="143" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C49" s="210" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D49" s="179" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C50" s="92">
         <f>G31/Normalized_FCF!C8</f>
@@ -9999,7 +9999,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C51" s="163"/>
       <c r="D51" s="89">
@@ -10013,19 +10013,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="143" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C53" s="210" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D53" s="179" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F53" s="223"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C54" s="89">
         <f>Normalized_FCF!C8/G35</f>
@@ -10039,7 +10039,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C55" s="89">
         <f>Normalized_FCF!C9/G40</f>
@@ -10056,19 +10056,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="143" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C57" s="210" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D57" s="179" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F57" s="223"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C58" s="95"/>
       <c r="D58" s="22">
@@ -10079,7 +10079,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C59" s="95"/>
       <c r="D59" s="89">
@@ -10093,19 +10093,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="143" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C61" s="210" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D61" s="179" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F61" s="223"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C62" s="89">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -10116,12 +10116,12 @@
         <v>3.0095583736849908E-3</v>
       </c>
       <c r="F62" s="223" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="76" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C64" s="35"/>
       <c r="D64" s="35"/>
@@ -10132,21 +10132,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C65" s="209" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D65" s="165" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F65" s="226" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="102" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C66" s="19">
         <f>G4+G5+G15</f>
@@ -10157,12 +10157,12 @@
         <v>25341662019.738998</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="102" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C67" s="19">
         <f>G6+G16</f>
@@ -10172,7 +10172,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="102" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C68" s="19">
         <f>G18</f>
@@ -10182,7 +10182,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="102" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C69" s="19">
         <f>G8+G20</f>
@@ -10192,7 +10192,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="77" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C70" s="78">
         <f>SUM(C66:C69)</f>
@@ -10205,19 +10205,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="225" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C72" s="209" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D72" s="164" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F72" s="223"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="102" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C73" s="285">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
@@ -10228,12 +10228,12 @@
         <v>-1684903051.2185009</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="227" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
@@ -10244,12 +10244,12 @@
         <v>21.040427401097187</v>
       </c>
       <c r="F74" s="223" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="77" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C75" s="261"/>
       <c r="D75" s="262">
@@ -10257,12 +10257,12 @@
         <v>10109418307.311005</v>
       </c>
       <c r="F75" s="223" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="229" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C76" s="230"/>
       <c r="D76" s="248">
@@ -10270,7 +10270,7 @@
         <v>6</v>
       </c>
       <c r="F76" s="223" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -10278,19 +10278,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C78" s="209" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D78" s="165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F78" s="223"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="102" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C79" s="19">
         <f>G7+G17</f>
@@ -10304,7 +10304,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="102" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C80" s="19">
         <f>G19</f>
@@ -10318,7 +10318,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="102" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C81" s="19">
         <f>G9+G21</f>
@@ -10332,7 +10332,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="77" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C82" s="78">
         <f>SUM(C79:C81)</f>
@@ -10346,7 +10346,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="76" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C84" s="35"/>
       <c r="D84" s="35"/>
@@ -10357,15 +10357,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="D85" s="215" t="s">
         <v>242</v>
-      </c>
-      <c r="D85" s="215" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="212" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
@@ -10382,7 +10382,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="212" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
@@ -10399,7 +10399,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="213" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
@@ -10416,7 +10416,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="77" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
@@ -10469,7 +10469,7 @@
         <v>CNY</v>
       </c>
       <c r="C1" s="50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D1" s="50"/>
       <c r="E1" s="50"/>
@@ -10522,12 +10522,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="53"/>
       <c r="E2" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F2" s="53"/>
       <c r="G2" s="35"/>
@@ -10545,7 +10545,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C3" s="104">
         <f>scaling_factor</f>
@@ -10555,7 +10555,7 @@
       <c r="E3" s="237"/>
       <c r="F3" s="9"/>
       <c r="G3" s="16" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H3" s="104">
         <f>scaling_factor</f>
@@ -10622,7 +10622,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="266">
         <f>C26</f>
@@ -10677,7 +10677,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="267">
         <f>C4+C5</f>
@@ -10732,7 +10732,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="266">
         <f>C35</f>
@@ -10787,7 +10787,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C8" s="268">
         <f>C6+C7</f>
@@ -10844,7 +10844,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C9" s="300">
         <f>C61</f>
@@ -10901,7 +10901,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" s="266">
         <f>C48</f>
@@ -10956,7 +10956,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C11" s="267">
         <f>SUM(C8:C10)</f>
@@ -11011,7 +11011,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" s="266">
         <f>-C11*C41</f>
@@ -11066,7 +11066,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C13" s="266">
         <f>-C4*C79</f>
@@ -11123,7 +11123,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="269">
         <f>SUM(C11:C13)</f>
@@ -11180,7 +11180,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C15" s="266">
         <f>BS!$G$39*BS!D58</f>
@@ -11235,7 +11235,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C16" s="266">
         <f>-C4*C82</f>
@@ -11290,7 +11290,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" s="266">
         <f>-C4*C83</f>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="D17" s="55"/>
       <c r="E17" s="236" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F17" s="55"/>
       <c r="G17" s="272"/>
@@ -11316,14 +11316,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C18" s="266">
         <v>0</v>
       </c>
       <c r="D18" s="55"/>
       <c r="E18" s="236" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F18" s="55"/>
       <c r="G18" s="273"/>
@@ -11341,7 +11341,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="267">
         <f>C14+C17</f>
@@ -11417,12 +11417,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C21" s="51"/>
       <c r="D21" s="53"/>
       <c r="E21" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F21" s="53"/>
       <c r="G21" s="35"/>
@@ -11440,7 +11440,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" s="59"/>
       <c r="D22" s="26"/>
@@ -11461,7 +11461,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" s="274">
         <f>-C4*C29</f>
@@ -11518,7 +11518,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C24" s="266">
         <f>-C4*C30</f>
@@ -11575,7 +11575,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" s="266">
         <f>-C4*C31</f>
@@ -11632,7 +11632,7 @@
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" s="267">
         <f>SUM(C23:C25)</f>
@@ -11693,14 +11693,14 @@
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E28" s="237"/>
     </row>
     <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C29" s="60">
         <f>AVERAGE(G29:H29)</f>
@@ -11873,7 +11873,7 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" s="68">
         <f>ABS(C26/$C$4)</f>
@@ -11932,14 +11932,14 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E34" s="237"/>
     </row>
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C35" s="276">
         <f>G35</f>
@@ -12000,14 +12000,14 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E37" s="237"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C38" s="68">
         <f>ABS(C35/$C$4)</f>
@@ -12066,21 +12066,21 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E40" s="237"/>
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C41" s="457">
         <v>0.25</v>
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="234" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="6">
@@ -12134,12 +12134,12 @@
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C43" s="51"/>
       <c r="D43" s="53"/>
       <c r="E43" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F43" s="53"/>
       <c r="G43" s="35"/>
@@ -12157,14 +12157,14 @@
     <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E44" s="237"/>
     </row>
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C45" s="266">
         <f>-BS!G31*Normalized_FCF!C52</f>
@@ -12219,7 +12219,7 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C46" s="266">
         <f>BS!D75*C51</f>
@@ -12274,7 +12274,7 @@
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C47" s="278">
         <f>BS!$C$66*C51</f>
@@ -12331,7 +12331,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C48" s="267">
         <f>C45+C46</f>
@@ -12390,17 +12390,17 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E50" s="237"/>
       <c r="G50" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C51" s="84">
         <v>6.0000000000000001E-3</v>
@@ -12424,7 +12424,7 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C52" s="79">
         <v>0.06</v>
@@ -12448,7 +12448,7 @@
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C53" s="40">
         <f>-C8/C45</f>
@@ -12507,17 +12507,17 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E55" s="237"/>
       <c r="G55" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C56" s="266">
         <f>BS!$C67*C64</f>
@@ -12572,7 +12572,7 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C57" s="266">
         <f>BS!$C68*C65</f>
@@ -12627,7 +12627,7 @@
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C58" s="266">
         <f>BS!$C69*C66</f>
@@ -12682,7 +12682,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C59" s="267">
         <f>SUM(C56:C58)</f>
@@ -12737,13 +12737,13 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C60" s="279">
         <v>0</v>
       </c>
       <c r="E60" s="235" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G60" s="266">
         <f>Data!C58</f>
@@ -12793,7 +12793,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C61" s="267">
         <f>C59+C60</f>
@@ -12852,17 +12852,17 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E63" s="237"/>
       <c r="G63" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C64" s="158">
         <f>G64</f>
@@ -12887,7 +12887,7 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C65" s="158">
         <f>G65</f>
@@ -12912,7 +12912,7 @@
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C66" s="158">
         <f>G66</f>
@@ -12937,7 +12937,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C67" s="68">
         <f>C59/BS!C70</f>
@@ -12967,12 +12967,12 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C69" s="51"/>
       <c r="D69" s="53"/>
       <c r="E69" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F69" s="53"/>
       <c r="G69" s="35"/>
@@ -12990,7 +12990,7 @@
     <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C70" s="59"/>
       <c r="D70" s="26"/>
@@ -13011,7 +13011,7 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C71" s="74">
         <f t="shared" ref="C71:C76" si="22">ABS(C5/C$4)</f>
@@ -13068,7 +13068,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C72" s="75">
         <f t="shared" si="22"/>
@@ -13125,7 +13125,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C73" s="74">
         <f t="shared" si="22"/>
@@ -13182,7 +13182,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C74" s="75">
         <f t="shared" si="22"/>
@@ -13239,7 +13239,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C75" s="74">
         <f t="shared" si="22"/>
@@ -13296,7 +13296,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
@@ -13353,7 +13353,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
@@ -13410,7 +13410,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
@@ -13525,7 +13525,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
@@ -13582,7 +13582,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C81" s="74">
         <f>ABS(C15/C$4)</f>
@@ -13639,7 +13639,7 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C82" s="85">
         <f>MAX(AVERAGE(G82:J82),C81)</f>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="235" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F82" s="26"/>
       <c r="G82" s="6">
@@ -13698,7 +13698,7 @@
     <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C83" s="233">
         <v>0</v>
@@ -13724,7 +13724,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C84" s="74">
         <v>0</v>
@@ -13748,7 +13748,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
@@ -13809,7 +13809,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E87" s="237"/>
     </row>
@@ -13928,7 +13928,7 @@
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
@@ -13983,7 +13983,7 @@
     <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C91" s="292">
         <v>0.1</v>
@@ -14004,20 +14004,20 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.9247863247863252E-2</v>
+        <v>3.889328063241107E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.9247863247863252E-2</v>
+        <v>3.889328063241107E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.6154512820512819E-2</v>
+        <v>4.5737532467532468E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14063,7 +14063,7 @@
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C94" s="59"/>
       <c r="D94" s="26"/>
@@ -14084,7 +14084,7 @@
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C95" s="74">
         <f>C4/G4-1</f>
@@ -14141,7 +14141,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
@@ -14201,12 +14201,12 @@
     <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C98" s="51"/>
       <c r="D98" s="53"/>
       <c r="E98" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F98" s="53"/>
       <c r="G98" s="35"/>
@@ -14224,11 +14224,11 @@
     <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E99" s="237"/>
       <c r="G99" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="100" spans="1:17" ht="15.75" customHeight="1">
@@ -14291,7 +14291,7 @@
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C101" s="281">
         <f>BS!C4</f>
@@ -14348,7 +14348,7 @@
     <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C102" s="281">
         <f>BS!C6+BS!C7</f>
@@ -14405,7 +14405,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C103" s="280">
         <f>BS!G30</f>
@@ -14462,7 +14462,7 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C104" s="280">
         <f>BS!G27</f>
@@ -14523,14 +14523,14 @@
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C106" s="25"/>
       <c r="D106" s="25"/>
       <c r="E106" s="238"/>
       <c r="F106" s="25"/>
       <c r="G106" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
@@ -14546,7 +14546,7 @@
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C107" s="91">
         <f>C101/C$4</f>
@@ -14603,7 +14603,7 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C108" s="91">
         <f>C102/C$4</f>
@@ -14660,7 +14660,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C109" s="91">
         <f>BS!$G$38/C$4</f>
@@ -14691,18 +14691,18 @@
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E111" s="237"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C112" s="151"/>
       <c r="E112" s="451" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G112" s="251">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
@@ -14752,7 +14752,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C113" s="151"/>
       <c r="E113" s="459">
@@ -14811,10 +14811,10 @@
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C115" s="451" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D115" s="52"/>
       <c r="E115" s="451" t="str">
@@ -14870,7 +14870,7 @@
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C116" s="22">
         <f>C77</f>
@@ -14927,7 +14927,7 @@
     </row>
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="B117" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C117" s="452">
         <f>G117</f>
@@ -14984,7 +14984,7 @@
     </row>
     <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C118" s="15">
         <f>C100/C104</f>
@@ -15044,7 +15044,7 @@
     <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C119" s="62">
         <f>C11/C104</f>
@@ -15123,12 +15123,12 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C121" s="51"/>
       <c r="D121" s="53"/>
       <c r="E121" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F121" s="53"/>
       <c r="G121" s="35"/>
@@ -15146,7 +15146,7 @@
     <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C122" s="161"/>
       <c r="D122" s="26"/>
@@ -15225,22 +15225,22 @@
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.5038414144241389E-2</v>
+        <v>8.4270139369363992E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.2867044473311197E-2</v>
+        <v>8.2118386815731872E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.0144141329513405E-2</v>
+        <v>7.9420083587406001E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15281,16 +15281,16 @@
     </row>
     <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="B125" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7084977012949469E-2</v>
+        <v>8.6298212680816652E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5735785824040123E-2</v>
+        <v>8.4961210683901972E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16043,7 +16043,7 @@
   <sheetData>
     <row r="2" spans="2:15" ht="13.9">
       <c r="B2" s="34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -16058,22 +16058,22 @@
     </row>
     <row r="3" spans="2:15" ht="13.15">
       <c r="B3" s="106" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C3" s="104">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="106" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H3" s="106" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C4" s="275">
         <f>Normalized_FCF!C19</f>
@@ -16084,7 +16084,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="135" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F4" s="275">
         <f>-BS!G31</f>
@@ -16095,7 +16095,7 @@
         <v>CNY</v>
       </c>
       <c r="H4" s="308" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I4" s="305">
         <f>Normalized_FCF!C4</f>
@@ -16105,14 +16105,14 @@
     </row>
     <row r="5" spans="2:15">
       <c r="B5" s="187" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" s="188">
         <f>Equity_Cost</f>
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="E5" s="135" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F5" s="275">
         <f>BS!D66</f>
@@ -16123,7 +16123,7 @@
         <v>CNY</v>
       </c>
       <c r="H5" s="308" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I5" s="305">
         <f>Normalized_FCF!C7</f>
@@ -16133,7 +16133,7 @@
     </row>
     <row r="6" spans="2:15" ht="13.25" customHeight="1">
       <c r="B6" s="136" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C6" s="283">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -16144,7 +16144,7 @@
         <v>CNY</v>
       </c>
       <c r="E6" s="187" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F6" s="284">
         <f>BS!H42</f>
@@ -16155,7 +16155,7 @@
         <v>CNY</v>
       </c>
       <c r="H6" s="308" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I6" s="305">
         <f>I7+I8</f>
@@ -16166,14 +16166,14 @@
     </row>
     <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="318" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C7" s="275">
         <f>F7</f>
         <v>23890653552.916996</v>
       </c>
       <c r="E7" s="140" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F7" s="283">
         <f>SUM(F4:F6)</f>
@@ -16184,7 +16184,7 @@
         <v>CNY</v>
       </c>
       <c r="H7" s="312" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I7" s="313">
         <f>Normalized_FCF!C9</f>
@@ -16196,7 +16196,7 @@
     </row>
     <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="136" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C8" s="283">
         <f>C6+C7</f>
@@ -16207,7 +16207,7 @@
         <v>CNY</v>
       </c>
       <c r="E8" s="140" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
@@ -16257,7 +16257,7 @@
     </row>
     <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
@@ -16268,7 +16268,7 @@
         <v>CNY</v>
       </c>
       <c r="H10" s="308" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I10" s="306">
         <f>Normalized_FCF!C41</f>
@@ -16279,7 +16279,7 @@
     </row>
     <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="136" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
@@ -16295,7 +16295,7 @@
     </row>
     <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C13" s="35"/>
       <c r="D13" s="35"/>
@@ -16310,25 +16310,25 @@
     </row>
     <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C14" s="309" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E14" s="106" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F14" s="309" t="str">
         <f>IF(ROUND(F17,4)=ROUND(C17,4),"I","II")</f>
         <v>I</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15" spans="2:15">
       <c r="B15" s="139" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C15" s="148">
         <f>Scenarios!C45</f>
@@ -16343,7 +16343,7 @@
         <v>16</v>
       </c>
       <c r="H15" s="97" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I15" s="126">
         <f>Terminal_Growth</f>
@@ -16353,14 +16353,14 @@
     </row>
     <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C16" s="147">
         <f>Scenarios!C46</f>
         <v>2.38559171477595E-2</v>
       </c>
       <c r="E16" s="308" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F16" s="311">
         <f>Scenarios!C41</f>
@@ -16369,40 +16369,40 @@
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="308" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C17" s="306">
         <f>Normalized_FCF!C77</f>
         <v>0.56520395086535147</v>
       </c>
       <c r="E17" s="308" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F17" s="311">
         <f>Scenarios!C40</f>
         <v>0.56520395086535147</v>
       </c>
       <c r="H17" s="106" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="308" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C18" s="306">
         <f>Normalized_FCF!C81-Normalized_FCF!C82</f>
         <v>0</v>
       </c>
       <c r="E18" s="308" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F18" s="144">
         <f>IF(F14="II",C18/2,C18)</f>
         <v>0</v>
       </c>
       <c r="H18" s="140" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
@@ -16418,41 +16418,41 @@
     </row>
     <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="121" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B20" s="121" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C20" s="121" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D20" s="121" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E20" s="121" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F20" s="121" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G20" s="121" t="str">
         <f>B18</f>
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="H20" s="121" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I20" s="121" t="s">
+        <v>526</v>
+      </c>
+      <c r="J20" s="121" t="s">
+        <v>549</v>
+      </c>
+      <c r="K20" s="121" t="s">
         <v>527</v>
       </c>
-      <c r="J20" s="121" t="s">
-        <v>550</v>
-      </c>
-      <c r="K20" s="121" t="s">
-        <v>528</v>
-      </c>
       <c r="L20" s="122" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -18007,7 +18007,7 @@
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="315" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B51" s="316">
         <f>C15+1</f>
@@ -18055,10 +18055,10 @@
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
-      <c r="J52" s="469" t="s">
-        <v>418</v>
-      </c>
-      <c r="K52" s="469"/>
+      <c r="J52" s="468" t="s">
+        <v>417</v>
+      </c>
+      <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
         <v>231572593623.19797</v>
@@ -18069,7 +18069,7 @@
     </row>
     <row r="54" spans="1:21" ht="13.15">
       <c r="B54" s="115" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C54" s="128"/>
       <c r="D54" s="128"/>
@@ -18538,7 +18538,7 @@
     </row>
     <row r="71" spans="1:21" ht="13.15">
       <c r="B71" s="115" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C71" s="275"/>
       <c r="D71" s="111"/>
@@ -19062,19 +19062,19 @@
     </row>
     <row r="89" spans="1:12" ht="13.15">
       <c r="B89" s="153" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C89" s="153" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D89" s="153" t="s">
+        <v>98</v>
+      </c>
+      <c r="E89" s="154" t="s">
         <v>99</v>
       </c>
-      <c r="E89" s="154" t="s">
-        <v>100</v>
-      </c>
       <c r="F89" s="154" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G89" s="323"/>
       <c r="H89" s="323"/>
@@ -19342,7 +19342,7 @@
   <sheetData>
     <row r="2" spans="2:7" ht="13.9">
       <c r="B2" s="34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -19352,21 +19352,21 @@
     </row>
     <row r="3" spans="2:7" ht="13.15">
       <c r="B3" s="145" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D3" s="97" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E3" s="97"/>
     </row>
     <row r="4" spans="2:7" ht="12.75" customHeight="1">
       <c r="B4" s="139" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C4" s="449">
         <v>2</v>
       </c>
-      <c r="D4" s="460" t="str">
+      <c r="D4" s="469" t="str">
         <f>"DCF Model Inputs for " &amp; Thesis!C5 &amp; " – " &amp; Thesis!C4 &amp; ": Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. " &amp;
 "Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. " &amp;
 "Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. " &amp;
@@ -19376,128 +19376,128 @@
 "For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario."</f>
         <v>DCF Model Inputs for 000568.SZ – 泸州老窖: Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. Margins should remain constant within each stage and be identical across all scenarios; any variation in outlook should be reflected through adjustments to the growth rate, not the margin. Terminal growth is fixed at 0%, so modify the high-growth duration or rate accordingly to reflect long-term expectations. Specify the FCFE margin (stage-specific if applicable) for all scenarios. For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario.</v>
       </c>
-      <c r="E4" s="460"/>
-      <c r="F4" s="460"/>
-      <c r="G4" s="460"/>
+      <c r="E4" s="469"/>
+      <c r="F4" s="469"/>
+      <c r="G4" s="469"/>
     </row>
     <row r="5" spans="2:7">
       <c r="C5" s="445"/>
-      <c r="D5" s="460"/>
-      <c r="E5" s="460"/>
-      <c r="F5" s="460"/>
-      <c r="G5" s="460"/>
+      <c r="D5" s="469"/>
+      <c r="E5" s="469"/>
+      <c r="F5" s="469"/>
+      <c r="G5" s="469"/>
     </row>
     <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" s="446" t="str">
         <f>DCF!C3&amp;" "&amp;Reporting_currency</f>
         <v>1 CNY</v>
       </c>
-      <c r="D6" s="460"/>
-      <c r="E6" s="460"/>
-      <c r="F6" s="460"/>
-      <c r="G6" s="460"/>
+      <c r="D6" s="469"/>
+      <c r="E6" s="469"/>
+      <c r="F6" s="469"/>
+      <c r="G6" s="469"/>
     </row>
     <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C7" s="447">
         <f>Normalized_FCF!G8</f>
         <v>17654238551.57</v>
       </c>
-      <c r="D7" s="460"/>
-      <c r="E7" s="460"/>
-      <c r="F7" s="460"/>
-      <c r="G7" s="460"/>
+      <c r="D7" s="469"/>
+      <c r="E7" s="469"/>
+      <c r="F7" s="469"/>
+      <c r="G7" s="469"/>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="447">
         <f>Normalized_FCF!G19</f>
         <v>12844018055.588684</v>
       </c>
-      <c r="D8" s="460"/>
-      <c r="E8" s="460"/>
-      <c r="F8" s="460"/>
-      <c r="G8" s="460"/>
+      <c r="D8" s="469"/>
+      <c r="E8" s="469"/>
+      <c r="F8" s="469"/>
+      <c r="G8" s="469"/>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" s="447">
         <f>Normalized_FCF!C19</f>
         <v>13180570558.891336</v>
       </c>
-      <c r="D9" s="460"/>
-      <c r="E9" s="460"/>
-      <c r="F9" s="460"/>
-      <c r="G9" s="460"/>
+      <c r="D9" s="469"/>
+      <c r="E9" s="469"/>
+      <c r="F9" s="469"/>
+      <c r="G9" s="469"/>
     </row>
     <row r="10" spans="2:7">
       <c r="C10" s="448"/>
-      <c r="D10" s="460"/>
-      <c r="E10" s="460"/>
-      <c r="F10" s="460"/>
-      <c r="G10" s="460"/>
+      <c r="D10" s="469"/>
+      <c r="E10" s="469"/>
+      <c r="F10" s="469"/>
+      <c r="G10" s="469"/>
     </row>
     <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C11" s="448"/>
-      <c r="D11" s="460"/>
-      <c r="E11" s="460"/>
-      <c r="F11" s="460"/>
-      <c r="G11" s="460"/>
+      <c r="D11" s="469"/>
+      <c r="E11" s="469"/>
+      <c r="F11" s="469"/>
+      <c r="G11" s="469"/>
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C12" s="249" t="e">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
-      <c r="G12" s="460"/>
+      <c r="D12" s="469"/>
+      <c r="E12" s="469"/>
+      <c r="F12" s="469"/>
+      <c r="G12" s="469"/>
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C13" s="249" t="e">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D13" s="460"/>
-      <c r="E13" s="460"/>
-      <c r="F13" s="460"/>
-      <c r="G13" s="460"/>
+      <c r="D13" s="469"/>
+      <c r="E13" s="469"/>
+      <c r="F13" s="469"/>
+      <c r="G13" s="469"/>
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C14" s="249" t="e">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D14" s="460"/>
-      <c r="E14" s="460"/>
-      <c r="F14" s="460"/>
-      <c r="G14" s="460"/>
+      <c r="D14" s="469"/>
+      <c r="E14" s="469"/>
+      <c r="F14" s="469"/>
+      <c r="G14" s="469"/>
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C16" s="35"/>
       <c r="D16" s="35"/>
@@ -19507,21 +19507,21 @@
     </row>
     <row r="17" spans="2:7" ht="13.15">
       <c r="B17" s="106" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E17" s="222" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="12.75" customHeight="1">
       <c r="B18" s="139" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C18" s="137">
         <v>15</v>
       </c>
       <c r="E18" s="450" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F18" s="319"/>
     </row>
@@ -19531,35 +19531,35 @@
     </row>
     <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
     <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="153" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C21" s="153" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D21" s="153" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E21" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (CNY)</v>
       </c>
       <c r="F21" s="154" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G21" s="154" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="302" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C22" s="324">
         <v>0.03</v>
@@ -19583,7 +19583,7 @@
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="302" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C23" s="324">
         <v>0.02</v>
@@ -19606,7 +19606,7 @@
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="302" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C24" s="324">
         <v>0.01</v>
@@ -19629,7 +19629,7 @@
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="141" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
@@ -19643,33 +19643,33 @@
     </row>
     <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="153" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C28" s="153" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D28" s="153" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E28" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (CNY)</v>
       </c>
       <c r="F28" s="154" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G28" s="154" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="302" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C29" s="324">
         <v>0.05</v>
@@ -19692,7 +19692,7 @@
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="315" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C30" s="324">
         <v>0</v>
@@ -19719,12 +19719,12 @@
     </row>
     <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="145" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
@@ -19735,7 +19735,7 @@
         <v>CNY</v>
       </c>
       <c r="E33" s="97" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F33" s="219">
         <f>Holding_Period</f>
@@ -19744,27 +19744,27 @@
     </row>
     <row r="34" spans="2:7">
       <c r="B34" s="97" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>105.3</v>
+        <v>106.26</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E34" s="97" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.2160259300061575</v>
+        <v>0.21223826010541716</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
@@ -19775,7 +19775,7 @@
         <v>CNY</v>
       </c>
       <c r="E35" s="97" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
@@ -19784,7 +19784,7 @@
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
@@ -19795,15 +19795,15 @@
         <v>CNY</v>
       </c>
       <c r="E36" s="97" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F36" s="331" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
@@ -19817,24 +19817,24 @@
         <v>1-stage DCF</v>
       </c>
       <c r="E39" s="222" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="40" spans="2:7">
       <c r="B40" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C40" s="126">
         <f>Normalized_FCF!E116</f>
         <v>0.56520395086535147</v>
       </c>
       <c r="E40" s="97" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C41" s="455">
         <f>DCF!C16</f>
@@ -19844,7 +19844,7 @@
     </row>
     <row r="43" spans="2:7" ht="13.9">
       <c r="B43" s="34" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C43" s="35"/>
       <c r="D43" s="35"/>
@@ -19854,15 +19854,15 @@
     </row>
     <row r="44" spans="2:7" ht="13.15">
       <c r="B44" s="106" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E44" s="222" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" spans="2:7">
       <c r="B45" s="139" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C45" s="150">
         <f>C18</f>
@@ -19870,24 +19870,24 @@
       </c>
       <c r="D45" s="137"/>
       <c r="E45" s="221" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" spans="2:7">
       <c r="B46" s="114" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C46" s="138">
         <v>2.38559171477595E-2</v>
       </c>
       <c r="D46" s="138"/>
       <c r="E46" s="221" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="2:7">
       <c r="B47" s="97" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
@@ -19898,24 +19898,24 @@
         <v>CNY</v>
       </c>
       <c r="E47" s="221" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="49" spans="2:7" ht="13.15">
       <c r="B49" s="106" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C49" s="218" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
         <v xml:space="preserve">Negative Growth </v>
       </c>
       <c r="E49" s="222" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="50" spans="2:7">
       <c r="B50" s="97" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C50" s="218" t="str">
         <f>IF(C36&lt;C35,"Y","N")</f>
@@ -19925,19 +19925,19 @@
     </row>
     <row r="51" spans="2:7">
       <c r="B51" s="97" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C51" s="218" t="str">
         <f>IF(C50="Y","N",IF(C46&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
       <c r="E51" s="221" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="52" spans="2:7">
       <c r="B52" s="97" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C52" s="218" t="str">
         <f>IF(C46&gt;8%,"Y","N")</f>
@@ -19947,14 +19947,14 @@
     </row>
     <row r="53" spans="2:7">
       <c r="B53" s="97" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C53" s="217" t="str">
         <f>IF(F53&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E53" s="126" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
@@ -19963,7 +19963,7 @@
     </row>
     <row r="55" spans="2:7" ht="13.9">
       <c r="B55" s="34" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C55" s="35"/>
       <c r="D55" s="35"/>
@@ -19973,12 +19973,12 @@
     </row>
     <row r="56" spans="2:7" ht="13.15">
       <c r="B56" s="106" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="57" spans="2:7">
       <c r="B57" s="220" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C57" s="219">
         <f>Holding_Period</f>
@@ -19988,7 +19988,7 @@
     </row>
     <row r="58" spans="2:7">
       <c r="B58" s="97" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C58" s="155">
         <f>C33</f>
@@ -20001,34 +20001,34 @@
     </row>
     <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E60" s="413"/>
     </row>
     <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="153" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C61" s="153" t="s">
+        <v>102</v>
+      </c>
+      <c r="D61" s="153" t="s">
         <v>103</v>
-      </c>
-      <c r="D61" s="153" t="s">
-        <v>104</v>
       </c>
       <c r="E61" s="154" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (CNY)</v>
       </c>
       <c r="F61" s="154" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G61" s="154" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="13.15">
       <c r="B62" s="302" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
@@ -20053,7 +20053,7 @@
     </row>
     <row r="63" spans="2:7" ht="13.15">
       <c r="B63" s="302" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
@@ -20078,28 +20078,28 @@
     </row>
     <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="153" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C65" s="153" t="s">
+        <v>102</v>
+      </c>
+      <c r="D65" s="153" t="s">
         <v>103</v>
-      </c>
-      <c r="D65" s="153" t="s">
-        <v>104</v>
       </c>
       <c r="E65" s="154" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (CNY)</v>
       </c>
       <c r="F65" s="154" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G65" s="154" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="13.15">
       <c r="B66" s="302" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
@@ -20124,7 +20124,7 @@
     </row>
     <row r="67" spans="2:7" ht="13.15">
       <c r="B67" s="302" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
@@ -20174,7 +20174,7 @@
   <sheetData>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="345" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B2" s="345"/>
       <c r="C2" s="345"/>
@@ -20188,7 +20188,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="E3" s="435" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F3" s="436">
         <f>Thesis!F3</f>
@@ -20197,7 +20197,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="422" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C4" s="423" t="str">
         <f>Thesis!C4</f>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="D4" s="349"/>
       <c r="E4" s="434" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F4" s="437" t="str">
         <f>Thesis!F4</f>
@@ -20214,14 +20214,14 @@
     </row>
     <row r="5" spans="1:10">
       <c r="B5" s="343" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C5" s="355" t="str">
         <f>Thesis!C5</f>
         <v>000568.SZ</v>
       </c>
       <c r="E5" s="438" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F5" s="439" t="str">
         <f>Thesis!F5</f>
@@ -20230,7 +20230,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="350" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C6" s="352" t="str">
         <f>Thesis!C6</f>
@@ -20240,7 +20240,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="343" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C7" s="352" t="str">
         <f>Market_currency</f>
@@ -20251,16 +20251,16 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="351" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>105.3</v>
+        <v>106.26</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="351" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C9" s="353">
         <f>Common_Shares</f>
@@ -20269,18 +20269,18 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="351" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>154995.48870389999</v>
+        <v>156408.55298838002</v>
       </c>
       <c r="D10" s="343" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.2160259300061575</v>
+        <v>0.21223826010541716</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20289,7 +20289,7 @@
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
       <c r="B12" s="474" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C12" s="474"/>
       <c r="D12" s="474"/>
@@ -20298,21 +20298,21 @@
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="343" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C15" s="358" t="str">
         <f>Thesis!C15</f>
         <v>N</v>
       </c>
       <c r="D15" s="351" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E15" s="344" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -20321,14 +20321,14 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="343" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C16" s="358" t="str">
         <f>Thesis!C16</f>
         <v>N</v>
       </c>
       <c r="D16" s="351" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
@@ -20337,14 +20337,14 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="343" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C17" s="424">
         <f>Terminal_Growth</f>
         <v>0.02</v>
       </c>
       <c r="D17" s="351" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E17" s="344" t="str">
         <f>Reporting_currency</f>
@@ -20361,7 +20361,7 @@
         <v>174.07668204091138</v>
       </c>
       <c r="D18" s="350" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E18" s="426">
         <f>Thesis!E18</f>
@@ -20370,14 +20370,14 @@
     </row>
     <row r="19" spans="1:6">
       <c r="B19" s="350" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C19" s="352" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
         <v xml:space="preserve">Negative Growth </v>
       </c>
       <c r="D19" s="343" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E19" s="427">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -20390,14 +20390,14 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="347" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C21" s="361" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
         <v xml:space="preserve"> (CNY)</v>
       </c>
       <c r="D21" s="362" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E21" s="363">
         <f>Holding_Period</f>
@@ -20406,14 +20406,14 @@
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="343" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C22" s="364">
         <f>E140</f>
         <v>86.739441984939162</v>
       </c>
       <c r="D22" s="365" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
@@ -20422,14 +20422,14 @@
     </row>
     <row r="23" spans="1:6">
       <c r="B23" s="343" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C23" s="367">
         <f>E141</f>
         <v>109.4444872921941</v>
       </c>
       <c r="D23" s="365" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
@@ -20438,14 +20438,14 @@
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="343" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C24" s="367">
         <f>E144</f>
         <v>146.05268014903339</v>
       </c>
       <c r="D24" s="365" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E24" s="368">
         <f>Thesis!E24</f>
@@ -20454,14 +20454,14 @@
     </row>
     <row r="25" spans="1:6">
       <c r="B25" s="343" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C25" s="367">
         <f>E145</f>
         <v>151.90346952484109</v>
       </c>
       <c r="D25" s="365" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E25" s="368">
         <f>Thesis!E25</f>
@@ -20470,7 +20470,7 @@
     </row>
     <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="345" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B27" s="345"/>
       <c r="C27" s="345"/>
@@ -20480,7 +20480,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="B29" s="474" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C29" s="474"/>
       <c r="D29" s="474"/>
@@ -20489,7 +20489,7 @@
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
       <c r="B30" s="477" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C30" s="477"/>
       <c r="D30" s="477"/>
@@ -20498,7 +20498,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C32" s="370">
         <f>scaling_factor</f>
@@ -20507,7 +20507,7 @@
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="470" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C33" s="470"/>
       <c r="D33" s="470"/>
@@ -20516,7 +20516,7 @@
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="372" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C34" s="373">
         <f>Normalized_FCF!C8</f>
@@ -20533,7 +20533,7 @@
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="470" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C36" s="470"/>
       <c r="D36" s="470"/>
@@ -20542,7 +20542,7 @@
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="372" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C37" s="373">
         <f>Normalized_FCF!C15</f>
@@ -20555,7 +20555,7 @@
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="375" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C38" s="373">
         <f>Normalized_FCF!C16</f>
@@ -20568,7 +20568,7 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="470" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C40" s="470"/>
       <c r="D40" s="470"/>
@@ -20577,7 +20577,7 @@
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="372" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C41" s="373">
         <f>Normalized_FCF!C9</f>
@@ -20590,7 +20590,7 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="470" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C43" s="470"/>
       <c r="D43" s="470"/>
@@ -20599,7 +20599,7 @@
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="372" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C44" s="376">
         <f>Normalized_FCF!C46</f>
@@ -20614,7 +20614,7 @@
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="372" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C45" s="376">
         <f>Normalized_FCF!C45</f>
@@ -20629,7 +20629,7 @@
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="372" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C46" s="373">
         <f>Normalized_FCF!C10</f>
@@ -20642,12 +20642,12 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="343" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="372" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C49" s="373">
         <f>Normalized_FCF!C13</f>
@@ -20660,7 +20660,7 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="470" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C51" s="470"/>
       <c r="D51" s="470"/>
@@ -20669,7 +20669,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="372" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C52" s="373">
         <f>Normalized_FCF!C12</f>
@@ -20682,7 +20682,7 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="470" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C54" s="476"/>
       <c r="D54" s="476"/>
@@ -20691,7 +20691,7 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C55" s="373">
         <f>Normalized_FCF!C17</f>
@@ -20704,7 +20704,7 @@
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="474" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C57" s="474"/>
       <c r="D57" s="474"/>
@@ -20713,7 +20713,7 @@
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="474" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C58" s="474"/>
       <c r="D58" s="474"/>
@@ -20722,7 +20722,7 @@
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C60" s="373">
         <f>Normalized_FCF!G19</f>
@@ -20735,7 +20735,7 @@
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="372" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C61" s="373">
         <f>Normalized_FCF!C19</f>
@@ -20748,24 +20748,24 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="377" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.5038414144241389E-2</v>
+        <v>8.4270139369363992E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="377" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.9247863247863252E-2</v>
+        <v>3.889328063241107E-2</v>
       </c>
       <c r="E63" s="372" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F63" s="380">
         <f>Normalized_FCF!C90</f>
@@ -20774,18 +20774,18 @@
     </row>
     <row r="65" spans="1:6">
       <c r="B65" s="369" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C65" s="381" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D65" s="381" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="372" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C66" s="378">
         <f>Normalized_FCF!E119</f>
@@ -20840,7 +20840,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="345" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B71" s="345"/>
       <c r="C71" s="345"/>
@@ -20854,7 +20854,7 @@
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
       <c r="B73" s="474" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C73" s="474"/>
       <c r="D73" s="474"/>
@@ -20863,7 +20863,7 @@
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="477" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C74" s="477"/>
       <c r="D74" s="477"/>
@@ -20872,12 +20872,12 @@
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="474" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C77" s="474"/>
       <c r="D77" s="474"/>
@@ -20886,7 +20886,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C78" s="373">
         <f>DCF!F4</f>
@@ -20899,7 +20899,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="B79" s="372" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -20912,7 +20912,7 @@
     </row>
     <row r="80" spans="1:6">
       <c r="B80" s="382" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C80" s="388">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -20921,7 +20921,7 @@
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="382" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C81" s="389">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -20930,12 +20930,12 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="343" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="343" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C84" s="373">
         <f>DCF!F5</f>
@@ -20948,7 +20948,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="382" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C85" s="390">
         <f>BS!C66</f>
@@ -20961,7 +20961,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="372" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -20974,12 +20974,12 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="343" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="B89" s="343" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C89" s="373">
         <f>DCF!F6</f>
@@ -20992,7 +20992,7 @@
     </row>
     <row r="90" spans="1:6">
       <c r="B90" s="372" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -21005,7 +21005,7 @@
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="372" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
@@ -21018,7 +21018,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="345" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B94" s="345"/>
       <c r="C94" s="345"/>
@@ -21032,7 +21032,7 @@
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
       <c r="B96" s="474" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C96" s="474"/>
       <c r="D96" s="474"/>
@@ -21042,7 +21042,7 @@
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
       <c r="B97" s="477" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C97" s="477"/>
       <c r="D97" s="477"/>
@@ -21052,7 +21052,7 @@
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
       <c r="B98" s="477" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C98" s="477"/>
       <c r="D98" s="477"/>
@@ -21065,13 +21065,13 @@
     <row r="100" spans="1:6">
       <c r="A100" s="385"/>
       <c r="B100" s="369" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="385"/>
       <c r="B101" s="372" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C101" s="368">
         <f>E25+C103</f>
@@ -21081,7 +21081,7 @@
     <row r="102" spans="1:6">
       <c r="A102" s="385"/>
       <c r="B102" s="382" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C102" s="383">
         <f>E25</f>
@@ -21091,7 +21091,7 @@
     <row r="103" spans="1:6">
       <c r="A103" s="385"/>
       <c r="B103" s="382" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C103" s="383">
         <f>IF(C15="Y",1%,0)+IF(C16="Y",1%,0)</f>
@@ -21101,7 +21101,7 @@
     <row r="104" spans="1:6">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C104" s="368">
         <v>0</v>
@@ -21114,14 +21114,14 @@
     <row r="106" spans="1:6">
       <c r="A106" s="385"/>
       <c r="B106" s="393" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C106" s="392"/>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
       <c r="B107" s="474" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C107" s="474"/>
       <c r="D107" s="474"/>
@@ -21131,7 +21131,7 @@
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
       <c r="B108" s="474" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C108" s="474"/>
       <c r="D108" s="474"/>
@@ -21144,13 +21144,13 @@
     <row r="110" spans="1:6">
       <c r="A110" s="385"/>
       <c r="B110" s="369" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="385"/>
       <c r="B111" s="375" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
@@ -21164,7 +21164,7 @@
     <row r="112" spans="1:6">
       <c r="A112" s="385"/>
       <c r="B112" s="372" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
@@ -21181,7 +21181,7 @@
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
       <c r="B114" s="474" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C114" s="474"/>
       <c r="D114" s="474"/>
@@ -21194,25 +21194,25 @@
     <row r="116" spans="1:6">
       <c r="A116" s="385"/>
       <c r="B116" s="369" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="385"/>
       <c r="B117" s="342" t="s">
+        <v>375</v>
+      </c>
+      <c r="C117" s="342" t="s">
         <v>376</v>
       </c>
-      <c r="C117" s="342" t="s">
+      <c r="D117" s="342" t="s">
+        <v>98</v>
+      </c>
+      <c r="E117" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="D117" s="342" t="s">
-        <v>99</v>
-      </c>
-      <c r="E117" s="342" t="s">
+      <c r="F117" s="342" t="s">
         <v>378</v>
-      </c>
-      <c r="F117" s="342" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -21329,7 +21329,7 @@
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="470" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C124" s="470"/>
       <c r="D124" s="470"/>
@@ -21338,7 +21338,7 @@
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="372" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
@@ -21351,7 +21351,7 @@
     </row>
     <row r="127" spans="1:6">
       <c r="B127" s="472" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C127" s="472"/>
       <c r="D127" s="472"/>
@@ -21360,7 +21360,7 @@
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B129" s="345"/>
       <c r="C129" s="345"/>
@@ -21370,7 +21370,7 @@
     </row>
     <row r="131" spans="1:6">
       <c r="B131" s="473" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C131" s="473"/>
       <c r="D131" s="473"/>
@@ -21379,7 +21379,7 @@
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
       <c r="B132" s="474" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C132" s="474"/>
       <c r="D132" s="474"/>
@@ -21388,12 +21388,12 @@
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="343" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C135" s="405">
         <f>E21</f>
@@ -21402,7 +21402,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="343" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C136" s="406">
         <f>Scenarios!C58</f>
@@ -21415,33 +21415,33 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="369" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C138" s="407"/>
       <c r="D138" s="407"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="340" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C139" s="340" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="340" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E139" s="341" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (CNY)</v>
       </c>
       <c r="F139" s="341" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="408" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
@@ -21462,7 +21462,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="408" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
@@ -21483,26 +21483,26 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="340" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C143" s="340" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="340" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E143" s="341" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (CNY)</v>
       </c>
       <c r="F143" s="341" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="B144" s="408" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C144" s="409">
         <f>Scenarios!C66</f>
@@ -21523,7 +21523,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="B145" s="408" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C145" s="409">
         <f>Scenarios!C67</f>
@@ -21544,7 +21544,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="345" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B147" s="345"/>
       <c r="C147" s="345"/>
@@ -21554,7 +21554,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="B149" s="475" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C149" s="474"/>
       <c r="D149" s="474"/>
@@ -21563,12 +21563,12 @@
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="476" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C152" s="476"/>
       <c r="D152" s="476"/>
@@ -21577,27 +21577,27 @@
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="412" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="412" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="343" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="24.5" customHeight="1">
       <c r="B158" s="470" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C158" s="470"/>
       <c r="D158" s="470"/>
@@ -21606,12 +21606,12 @@
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="343" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="471" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C161" s="471"/>
       <c r="D161" s="471"/>
@@ -21620,7 +21620,7 @@
     </row>
     <row r="162" spans="2:6">
       <c r="B162" s="471" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C162" s="471"/>
       <c r="D162" s="471"/>
@@ -21629,22 +21629,22 @@
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="412" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="412" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="412" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73CEA6B3-BE3A-4756-86E4-322A0D8F0F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B3BFCE-55D7-42D4-828E-7DB10425705B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>347</v>
       </c>
       <c r="C8" s="47">
-        <v>106.26</v>
+        <v>102.51</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>156408.55298838002</v>
+        <v>150888.77062713</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>524</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.21223826010541716</v>
+        <v>0.22730609595401288</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>352</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>353</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.4270139369363992E-2</v>
+        <v>8.7352892492328735E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.889328063241107E-2</v>
+        <v>4.0316066725197545E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>320</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>475</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>482</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>481</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>480</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>488</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>354</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>357</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>435</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.889328063241107E-2</v>
+        <v>4.0316066725197545E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.889328063241107E-2</v>
+        <v>4.0316066725197545E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.5737532467532468E-2</v>
+        <v>4.7410693590869184E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.4270139369363992E-2</v>
+        <v>8.7352892492328735E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.2118386815731872E-2</v>
+        <v>8.5122424963805177E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.9420083587406001E-2</v>
+        <v>8.2325412954811827E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6298212680816652E-2</v>
+        <v>8.9455156369754929E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4961210683901972E-2</v>
+        <v>8.8069244437337074E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>106.26</v>
+        <v>102.51</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.21223826010541716</v>
+        <v>0.22730609595401288</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>106.26</v>
+        <v>102.51</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>156408.55298838002</v>
+        <v>150888.77062713</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.21223826010541716</v>
+        <v>0.22730609595401288</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>494</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>496</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>503</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>504</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.4270139369363992E-2</v>
+        <v>8.7352892492328735E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.889328063241107E-2</v>
+        <v>4.0316066725197545E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>370</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>476</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>532</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>516</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>517</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>519</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>385</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,12 +21649,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21669,15 +21672,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B3BFCE-55D7-42D4-828E-7DB10425705B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA3FF93D-9E45-4ECB-8964-FCB76A5F77A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>347</v>
       </c>
       <c r="C8" s="47">
-        <v>102.51</v>
+        <v>103.05</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>150888.77062713</v>
+        <v>151683.61928714998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>524</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.22730609595401288</v>
+        <v>0.22509044459126859</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>352</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.7352892492328735E-2</v>
+        <v>8.6895148077521772E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>4.0316066725197545E-2</v>
+        <v>4.0104803493449789E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>320</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>475</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>480</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>488</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>354</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>435</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.0316066725197545E-2</v>
+        <v>4.0104803493449789E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.0316066725197545E-2</v>
+        <v>4.0104803493449789E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.7410693590869184E-2</v>
+        <v>4.7162253275109173E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.7352892492328735E-2</v>
+        <v>8.6895148077521772E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.5122424963805177E-2</v>
+        <v>8.4676368588449E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.2325412954811827E-2</v>
+        <v>8.1894013410943836E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9455156369754929E-2</v>
+        <v>8.8986395725022593E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8069244437337074E-2</v>
+        <v>8.7607746213211296E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>102.51</v>
+        <v>103.05</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.22730609595401288</v>
+        <v>0.22509044459126859</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>102.51</v>
+        <v>103.05</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>150888.77062713</v>
+        <v>151683.61928714998</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.22730609595401288</v>
+        <v>0.22509044459126859</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>494</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>496</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>503</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>504</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.7352892492328735E-2</v>
+        <v>8.6895148077521772E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>4.0316066725197545E-2</v>
+        <v>4.0104803493449789E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>370</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>476</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>532</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>385</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,15 +21649,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21672,12 +21669,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA3FF93D-9E45-4ECB-8964-FCB76A5F77A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FDECE03-F4A2-4136-8ABB-133FC60D81B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>347</v>
       </c>
       <c r="C8" s="47">
-        <v>103.05</v>
+        <v>101.2</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>151683.61928714998</v>
+        <v>148960.5266556</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>524</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.22509044459126859</v>
+        <v>0.23274777931282981</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>352</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>353</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.6895148077521772E-2</v>
+        <v>8.8483646337832192E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>4.0104803493449789E-2</v>
+        <v>4.0837944664031622E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>320</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>475</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>482</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>481</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>480</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>488</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>354</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>357</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>435</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.0104803493449789E-2</v>
+        <v>4.0837944664031622E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.0104803493449789E-2</v>
+        <v>4.0837944664031622E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.7162253275109173E-2</v>
+        <v>4.802440909090909E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.6895148077521772E-2</v>
+        <v>8.8483646337832192E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.4676368588449E-2</v>
+        <v>8.6224306156518465E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.1894013410943836E-2</v>
+        <v>8.3391087766776298E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8986395725022593E-2</v>
+        <v>9.0613123314857491E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7607746213211296E-2</v>
+        <v>8.9209271218097075E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>103.05</v>
+        <v>101.2</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.22509044459126859</v>
+        <v>0.23274777931282981</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>103.05</v>
+        <v>101.2</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>151683.61928714998</v>
+        <v>148960.5266556</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.22509044459126859</v>
+        <v>0.23274777931282981</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>494</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>496</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>503</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>504</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.6895148077521772E-2</v>
+        <v>8.8483646337832192E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>4.0104803493449789E-2</v>
+        <v>4.0837944664031622E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>370</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>476</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>532</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>516</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>517</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>519</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>385</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,12 +21649,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21669,15 +21672,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FDECE03-F4A2-4136-8ABB-133FC60D81B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85CA9EEB-2AE4-4734-ACBC-3D1516A0D02E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>347</v>
       </c>
       <c r="C8" s="47">
-        <v>101.2</v>
+        <v>100.61</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>148960.5266556</v>
+        <v>148092.08089742999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>524</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.23274777931282981</v>
+        <v>0.23523004608014461</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>352</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.8483646337832192E-2</v>
+        <v>8.9002534632627167E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>4.0837944664031622E-2</v>
+        <v>4.1077427691084391E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>320</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>475</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>480</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>488</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>354</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>435</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.0837944664031622E-2</v>
+        <v>4.1077427691084391E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.0837944664031622E-2</v>
+        <v>4.1077427691084391E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.802440909090909E-2</v>
+        <v>4.8306035185369245E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.8483646337832192E-2</v>
+        <v>8.9002534632627167E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.6224306156518465E-2</v>
+        <v>8.6729945164890854E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.3391087766776298E-2</v>
+        <v>8.3880112135948329E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0613123314857491E-2</v>
+        <v>9.114449934860927E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9209271218097075E-2</v>
+        <v>8.9732414742783262E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>101.2</v>
+        <v>100.61</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.23274777931282981</v>
+        <v>0.23523004608014461</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>101.2</v>
+        <v>100.61</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>148960.5266556</v>
+        <v>148092.08089742999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.23274777931282981</v>
+        <v>0.23523004608014461</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>494</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>496</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>503</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>504</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.8483646337832192E-2</v>
+        <v>8.9002534632627167E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>4.0837944664031622E-2</v>
+        <v>4.1077427691084391E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>370</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>476</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>532</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>385</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,15 +21649,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21672,12 +21669,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85CA9EEB-2AE4-4734-ACBC-3D1516A0D02E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B8A43D-B852-42DF-8D60-9E4DAA576F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>347</v>
       </c>
       <c r="C8" s="47">
-        <v>100.61</v>
+        <v>100.24</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>148092.08089742999</v>
+        <v>147547.46237112</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>524</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.23523004608014461</v>
+        <v>0.23679685964756761</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>352</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>353</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.9002534632627167E-2</v>
+        <v>8.9331055560540884E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>4.1077427691084391E-2</v>
+        <v>4.1229050279329618E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>320</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>475</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>482</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>481</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>480</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>488</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>354</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>357</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>435</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.1077427691084391E-2</v>
+        <v>4.1229050279329618E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.1077427691084391E-2</v>
+        <v>4.1229050279329618E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.8306035185369245E-2</v>
+        <v>4.8484339584996011E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.9002534632627167E-2</v>
+        <v>8.9331055560540884E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.6729945164890854E-2</v>
+        <v>8.7050077644050969E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.3880112135948329E-2</v>
+        <v>8.4189725478828428E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.114449934860927E-2</v>
+        <v>9.1480926570865706E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9732414742783262E-2</v>
+        <v>9.0063629761287151E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>100.61</v>
+        <v>100.24</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.23523004608014461</v>
+        <v>0.23679685964756761</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>100.61</v>
+        <v>100.24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>148092.08089742999</v>
+        <v>147547.46237112</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.23523004608014461</v>
+        <v>0.23679685964756761</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>494</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>496</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>503</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>504</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.9002534632627167E-2</v>
+        <v>8.9331055560540884E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>4.1077427691084391E-2</v>
+        <v>4.1229050279329618E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>370</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>476</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>532</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>516</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>517</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>519</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>385</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,12 +21649,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21669,15 +21672,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B8A43D-B852-42DF-8D60-9E4DAA576F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE08396-E0DD-4AA3-8CCD-399AF5B06BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>347</v>
       </c>
       <c r="C8" s="47">
-        <v>100.24</v>
+        <v>102.63</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>147547.46237112</v>
+        <v>151065.40366268999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>524</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.23679685964756761</v>
+        <v>0.22681235763738272</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>352</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.9331055560540884E-2</v>
+        <v>8.7250755231302921E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>4.1229050279329618E-2</v>
+        <v>4.0268927214264838E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>320</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>475</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>480</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>488</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>354</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>435</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.1229050279329618E-2</v>
+        <v>4.0268927214264838E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.1229050279329618E-2</v>
+        <v>4.0268927214264838E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.8484339584996011E-2</v>
+        <v>4.7355258696287636E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.9331055560540884E-2</v>
+        <v>8.7250755231302921E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.7050077644050969E-2</v>
+        <v>8.5022895674166127E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.4189725478828428E-2</v>
+        <v>8.2229154067989502E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1480926570865706E-2</v>
+        <v>8.935056103930214E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0063629761287151E-2</v>
+        <v>8.7966269582689507E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>100.24</v>
+        <v>102.63</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.23679685964756761</v>
+        <v>0.22681235763738272</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>100.24</v>
+        <v>102.63</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>147547.46237112</v>
+        <v>151065.40366268999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.23679685964756761</v>
+        <v>0.22681235763738272</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>494</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>496</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>503</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>504</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.9331055560540884E-2</v>
+        <v>8.7250755231302921E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>4.1229050279329618E-2</v>
+        <v>4.0268927214264838E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>370</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>476</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>532</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>385</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,15 +21649,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21672,12 +21669,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE08396-E0DD-4AA3-8CCD-399AF5B06BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F3118D-091C-4E5F-9DF7-EF22EC2F3897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>352</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>353</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>475</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>482</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>481</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>480</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>488</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>354</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>357</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>435</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>494</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>496</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>503</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>504</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>476</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>532</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>516</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>517</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>519</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>385</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,12 +21649,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21669,15 +21672,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000568.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000568.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F3118D-091C-4E5F-9DF7-EF22EC2F3897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF82C741-D1E4-43FF-AEB7-FC5AC18E57E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>347</v>
       </c>
       <c r="C8" s="47">
-        <v>102.63</v>
+        <v>101.73</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>151065.40366268999</v>
+        <v>149740.65589599003</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>524</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.22681235763738272</v>
+        <v>0.23053469174181579</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>352</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.7250755231302921E-2</v>
+        <v>8.8022658108607266E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>4.0268927214264838E-2</v>
+        <v>4.0625184311412564E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>320</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>475</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>480</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>488</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>354</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>435</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.0268927214264838E-2</v>
+        <v>4.0625184311412564E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.0268927214264838E-2</v>
+        <v>4.0625184311412564E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.7355258696287636E-2</v>
+        <v>4.777420819817163E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.7250755231302921E-2</v>
+        <v>8.8022658108607266E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.5022895674166127E-2</v>
+        <v>8.5775088794256049E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.2229154067989502E-2</v>
+        <v>8.2956631101914494E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.935056103930214E-2</v>
+        <v>9.0141040788986312E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7966269582689507E-2</v>
+        <v>8.874450257811288E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>102.63</v>
+        <v>101.73</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.22681235763738272</v>
+        <v>0.23053469174181579</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>102.63</v>
+        <v>101.73</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>151065.40366268999</v>
+        <v>149740.65589599003</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.22681235763738272</v>
+        <v>0.23053469174181579</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>494</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>496</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>503</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>504</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.7250755231302921E-2</v>
+        <v>8.8022658108607266E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>4.0268927214264838E-2</v>
+        <v>4.0625184311412564E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>370</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>476</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>532</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>385</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,15 +21649,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21672,12 +21669,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
